--- a/Data/National Accounts/PSA-02HFCE_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-02HFCE_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87714BFD-036D-42D6-B781-3E56F7E41181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109C37CB-0206-4D93-9F2F-F0CD23AD5279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="HFCE" sheetId="2" r:id="rId1"/>
@@ -707,10 +707,10 @@
     <t>Percent Share, at Constant 2018 Prices</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -759,10 +759,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1258,7 +1260,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1268,7 +1270,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2048,28 +2050,28 @@
         <v>2063576.9033315014</v>
       </c>
       <c r="CT12" s="25">
-        <v>1613679.3446519671</v>
+        <v>1613761.424676501</v>
       </c>
       <c r="CU12" s="25">
-        <v>1796715.8690888041</v>
+        <v>1796718.7201527846</v>
       </c>
       <c r="CV12" s="25">
-        <v>1681121.5797413471</v>
+        <v>1681388.6351362076</v>
       </c>
       <c r="CW12" s="25">
-        <v>2162044.6171398368</v>
+        <v>2160294.5385831534</v>
       </c>
       <c r="CX12" s="25">
-        <v>1739032.9216468222</v>
+        <v>1739445.3453346388</v>
       </c>
       <c r="CY12" s="25">
-        <v>1904204.7181403043</v>
+        <v>1901040.0360778528</v>
       </c>
       <c r="CZ12" s="25">
-        <v>1765934.6198938952</v>
+        <v>1761848.38771784</v>
       </c>
       <c r="DA12" s="25">
-        <v>2258935.0972477864</v>
+        <v>2257594.2514206418</v>
       </c>
       <c r="DB12" s="8"/>
       <c r="DC12" s="8"/>
@@ -2442,25 +2444,25 @@
         <v>83199.948119052526</v>
       </c>
       <c r="CU13" s="25">
-        <v>84674.894468189217</v>
+        <v>85524.075078097478</v>
       </c>
       <c r="CV13" s="25">
-        <v>87247.480556130249</v>
+        <v>85724.372197064164</v>
       </c>
       <c r="CW13" s="25">
-        <v>124543.37838654699</v>
+        <v>123572.92839157737</v>
       </c>
       <c r="CX13" s="25">
-        <v>92362.791113174331</v>
+        <v>92365.800447744245</v>
       </c>
       <c r="CY13" s="25">
-        <v>85929.223846171997</v>
+        <v>85635.932636063255</v>
       </c>
       <c r="CZ13" s="25">
-        <v>83864.81380027144</v>
+        <v>83953.08077514061</v>
       </c>
       <c r="DA13" s="25">
-        <v>120021.52332214467</v>
+        <v>120252.82278633314</v>
       </c>
       <c r="DB13" s="8"/>
       <c r="DC13" s="8"/>
@@ -2836,22 +2838,22 @@
         <v>49496.130101982024</v>
       </c>
       <c r="CV14" s="25">
-        <v>71705.208034403724</v>
+        <v>71710.25985709115</v>
       </c>
       <c r="CW14" s="25">
-        <v>93902.795225128575</v>
+        <v>93938.971574998242</v>
       </c>
       <c r="CX14" s="25">
-        <v>65079.664639905059</v>
+        <v>65216.951480931537</v>
       </c>
       <c r="CY14" s="25">
-        <v>52186.522878765434</v>
+        <v>52194.182892534664</v>
       </c>
       <c r="CZ14" s="25">
-        <v>72239.201053636498</v>
+        <v>72156.420033725197</v>
       </c>
       <c r="DA14" s="25">
-        <v>94438.209695695768</v>
+        <v>94741.452218738676</v>
       </c>
       <c r="DB14" s="8"/>
       <c r="DC14" s="8"/>
@@ -3230,19 +3232,19 @@
         <v>602521.12423501338</v>
       </c>
       <c r="CW15" s="25">
-        <v>614054.36448713182</v>
+        <v>614257.78237452835</v>
       </c>
       <c r="CX15" s="25">
-        <v>560592.39430115058</v>
+        <v>560592.73035324307</v>
       </c>
       <c r="CY15" s="25">
-        <v>714199.96412782709</v>
+        <v>714177.01714997587</v>
       </c>
       <c r="CZ15" s="25">
-        <v>620464.31194890186</v>
+        <v>620446.02365413809</v>
       </c>
       <c r="DA15" s="25">
-        <v>630269.28691325232</v>
+        <v>631565.8971390489</v>
       </c>
       <c r="DB15" s="8"/>
       <c r="DC15" s="8"/>
@@ -3612,28 +3614,28 @@
         <v>137855.60433990852</v>
       </c>
       <c r="CT16" s="25">
-        <v>118094.06265215231</v>
+        <v>117911.50571755297</v>
       </c>
       <c r="CU16" s="25">
-        <v>111901.91873284035</v>
+        <v>111889.41054828421</v>
       </c>
       <c r="CV16" s="25">
-        <v>135005.70809260488</v>
+        <v>134989.10361861638</v>
       </c>
       <c r="CW16" s="25">
-        <v>147767.90231364404</v>
+        <v>147395.27684413307</v>
       </c>
       <c r="CX16" s="25">
-        <v>122290.55596765227</v>
+        <v>122248.6724768618</v>
       </c>
       <c r="CY16" s="25">
-        <v>119361.02313784561</v>
+        <v>120288.15665465748</v>
       </c>
       <c r="CZ16" s="25">
-        <v>137036.92412561775</v>
+        <v>137708.40956885545</v>
       </c>
       <c r="DA16" s="25">
-        <v>146732.2533202646</v>
+        <v>147486.66570831661</v>
       </c>
       <c r="DB16" s="8"/>
       <c r="DC16" s="8"/>
@@ -4003,28 +4005,28 @@
         <v>216430.41763548076</v>
       </c>
       <c r="CT17" s="25">
-        <v>203800.00187438441</v>
+        <v>203367.02506145558</v>
       </c>
       <c r="CU17" s="25">
-        <v>176633.20283022212</v>
+        <v>176662.81467871502</v>
       </c>
       <c r="CV17" s="25">
-        <v>274946.5909907649</v>
+        <v>275282.36388536001</v>
       </c>
       <c r="CW17" s="25">
-        <v>247318.81060222766</v>
+        <v>248324.79580781164</v>
       </c>
       <c r="CX17" s="25">
-        <v>229434.65337623964</v>
+        <v>229617.31228166303</v>
       </c>
       <c r="CY17" s="25">
-        <v>198672.3485332249</v>
+        <v>198417.26782688496</v>
       </c>
       <c r="CZ17" s="25">
-        <v>314468.77157686598</v>
+        <v>314926.41392172797</v>
       </c>
       <c r="DA17" s="25">
-        <v>270234.56241433549</v>
+        <v>269475.82895237411</v>
       </c>
       <c r="DB17" s="8"/>
       <c r="DC17" s="8"/>
@@ -4403,19 +4405,19 @@
         <v>559286.6211915852</v>
       </c>
       <c r="CW18" s="25">
-        <v>464043.1526550423</v>
+        <v>463966.42675833718</v>
       </c>
       <c r="CX18" s="25">
-        <v>557556.77390960406</v>
+        <v>557835.49104781833</v>
       </c>
       <c r="CY18" s="25">
-        <v>483502.37137420999</v>
+        <v>483534.83658837702</v>
       </c>
       <c r="CZ18" s="25">
-        <v>582323.4513120011</v>
+        <v>579337.63194990519</v>
       </c>
       <c r="DA18" s="25">
-        <v>496239.42776139575</v>
+        <v>496667.21270987199</v>
       </c>
       <c r="DB18" s="8"/>
       <c r="DC18" s="8"/>
@@ -4785,28 +4787,28 @@
         <v>133865.14827610209</v>
       </c>
       <c r="CT19" s="25">
-        <v>134459.08881603429</v>
+        <v>134522.50339071965</v>
       </c>
       <c r="CU19" s="25">
-        <v>143844.77852686387</v>
+        <v>144066.67265576616</v>
       </c>
       <c r="CV19" s="25">
-        <v>106701.46684118427</v>
+        <v>106850.4502009595</v>
       </c>
       <c r="CW19" s="25">
-        <v>139247.27733421652</v>
+        <v>139735.3643260673</v>
       </c>
       <c r="CX19" s="25">
-        <v>142284.7414504984</v>
+        <v>142557.55249291722</v>
       </c>
       <c r="CY19" s="25">
-        <v>151352.14981695212</v>
+        <v>150787.31440530758</v>
       </c>
       <c r="CZ19" s="25">
-        <v>111806.5767061981</v>
+        <v>111953.81712330545</v>
       </c>
       <c r="DA19" s="25">
-        <v>144437.64685551997</v>
+        <v>145667.37342405706</v>
       </c>
       <c r="DB19" s="8"/>
       <c r="DC19" s="8"/>
@@ -5185,19 +5187,19 @@
         <v>67281.346426057717</v>
       </c>
       <c r="CW20" s="25">
-        <v>106868.69742001814</v>
+        <v>106416.39636943344</v>
       </c>
       <c r="CX20" s="25">
-        <v>95832.357670154655</v>
+        <v>95533.136326084204</v>
       </c>
       <c r="CY20" s="25">
-        <v>68850.348060416625</v>
+        <v>68460.117775589461</v>
       </c>
       <c r="CZ20" s="25">
-        <v>70498.102085925144</v>
+        <v>70520.405032551615</v>
       </c>
       <c r="DA20" s="25">
-        <v>115438.8207375631</v>
+        <v>116085.0135024778</v>
       </c>
       <c r="DB20" s="8"/>
       <c r="DC20" s="8"/>
@@ -5567,28 +5569,28 @@
         <v>245349.10421328663</v>
       </c>
       <c r="CT21" s="25">
-        <v>246831.10313367649</v>
+        <v>248111.6292691023</v>
       </c>
       <c r="CU21" s="25">
-        <v>215427.03914205509</v>
+        <v>216136.75353857584</v>
       </c>
       <c r="CV21" s="25">
-        <v>261559.71512130322</v>
+        <v>262173.387196225</v>
       </c>
       <c r="CW21" s="25">
-        <v>271497.04271244386</v>
+        <v>273161.26626962546</v>
       </c>
       <c r="CX21" s="25">
-        <v>274487.10755094176</v>
+        <v>274426.90267776645</v>
       </c>
       <c r="CY21" s="25">
-        <v>247937.09436536278</v>
+        <v>248037.37450262456</v>
       </c>
       <c r="CZ21" s="25">
-        <v>287772.97859496146</v>
+        <v>287687.79307470075</v>
       </c>
       <c r="DA21" s="25">
-        <v>299693.12215944222</v>
+        <v>300009.49537248426</v>
       </c>
       <c r="DB21" s="8"/>
       <c r="DC21" s="8"/>
@@ -5961,25 +5963,25 @@
         <v>501360.99492956884</v>
       </c>
       <c r="CU22" s="25">
-        <v>284918.88654920907</v>
+        <v>284991.48245812824</v>
       </c>
       <c r="CV22" s="25">
-        <v>407007.63858099887</v>
+        <v>407061.26230670203</v>
       </c>
       <c r="CW22" s="25">
-        <v>499380.11673069955</v>
+        <v>501332.91981947469</v>
       </c>
       <c r="CX22" s="25">
-        <v>543358.73903827975</v>
+        <v>543082.98656744789</v>
       </c>
       <c r="CY22" s="25">
-        <v>311779.71241481096</v>
+        <v>311922.17149607488</v>
       </c>
       <c r="CZ22" s="25">
-        <v>438266.17175300012</v>
+        <v>438239.43011700979</v>
       </c>
       <c r="DA22" s="25">
-        <v>550115.42127886356</v>
+        <v>550139.20937379065</v>
       </c>
       <c r="DB22" s="8"/>
       <c r="DC22" s="8"/>
@@ -6349,28 +6351,28 @@
         <v>776162.06674813747</v>
       </c>
       <c r="CT23" s="25">
-        <v>681032.57527187024</v>
+        <v>680726.92183083761</v>
       </c>
       <c r="CU23" s="25">
-        <v>645757.90468213288</v>
+        <v>645331.90623637545</v>
       </c>
       <c r="CV23" s="25">
-        <v>664227.87068587961</v>
+        <v>663725.05440476409</v>
       </c>
       <c r="CW23" s="25">
-        <v>858697.14329350879</v>
+        <v>858846.26695316972</v>
       </c>
       <c r="CX23" s="25">
-        <v>729278.39016381756</v>
+        <v>728607.48507854564</v>
       </c>
       <c r="CY23" s="25">
-        <v>688512.16862456792</v>
+        <v>687796.29070025368</v>
       </c>
       <c r="CZ23" s="25">
-        <v>705543.50752265961</v>
+        <v>705937.62939993793</v>
       </c>
       <c r="DA23" s="25">
-        <v>913427.79441605438</v>
+        <v>913942.70429242158</v>
       </c>
       <c r="DB23" s="8"/>
       <c r="DC23" s="8"/>
@@ -6920,28 +6922,28 @@
         <v>5330878.5300679235</v>
       </c>
       <c r="CT25" s="10">
-        <v>4782609.1617980804</v>
+        <v>4783113.9953441638</v>
       </c>
       <c r="CU25" s="10">
-        <v>4707105.2868563132</v>
+        <v>4708552.6281827232</v>
       </c>
       <c r="CV25" s="10">
-        <v>4918612.3504972719</v>
+        <v>4917993.980655646</v>
       </c>
       <c r="CW25" s="10">
-        <v>5729365.2983004451</v>
+        <v>5731242.9340723092</v>
       </c>
       <c r="CX25" s="10">
-        <v>5151591.0908282408</v>
+        <v>5151530.3665656615</v>
       </c>
       <c r="CY25" s="10">
-        <v>5026487.6453204593</v>
+        <v>5022290.6987061966</v>
       </c>
       <c r="CZ25" s="10">
-        <v>5190219.4303739341</v>
+        <v>5184715.442368838</v>
       </c>
       <c r="DA25" s="10">
-        <v>6039983.1661223182</v>
+        <v>6043627.9269005563</v>
       </c>
       <c r="DB25" s="8"/>
       <c r="DC25" s="8"/>
@@ -7502,7 +7504,7 @@
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:179" x14ac:dyDescent="0.2">
@@ -7512,7 +7514,7 @@
     </row>
     <row r="35" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:179" x14ac:dyDescent="0.2">
@@ -8292,28 +8294,28 @@
         <v>1626806.0754117006</v>
       </c>
       <c r="CT41" s="25">
-        <v>1271433.1682090887</v>
+        <v>1271497.8398342079</v>
       </c>
       <c r="CU41" s="25">
-        <v>1370268.1492589575</v>
+        <v>1370270.323627332</v>
       </c>
       <c r="CV41" s="25">
-        <v>1270361.5334978893</v>
+        <v>1270563.3374037056</v>
       </c>
       <c r="CW41" s="25">
-        <v>1650790.3578221325</v>
+        <v>1649454.1167548108</v>
       </c>
       <c r="CX41" s="25">
-        <v>1332005.494013116</v>
+        <v>1332321.3883306959</v>
       </c>
       <c r="CY41" s="25">
-        <v>1441810.2884296912</v>
+        <v>1439414.0801261493</v>
       </c>
       <c r="CZ41" s="25">
-        <v>1326977.6015995066</v>
+        <v>1323907.0810312615</v>
       </c>
       <c r="DA41" s="25">
-        <v>1713030.3045264485</v>
+        <v>1712013.4937564556</v>
       </c>
       <c r="DB41" s="18"/>
       <c r="DC41" s="18"/>
@@ -8686,25 +8688,25 @@
         <v>49480.286910551149</v>
       </c>
       <c r="CU42" s="25">
-        <v>46554.193541044449</v>
+        <v>47021.072404174571</v>
       </c>
       <c r="CV42" s="25">
-        <v>45987.974795824841</v>
+        <v>45185.147386006647</v>
       </c>
       <c r="CW42" s="25">
-        <v>71876.742738170637</v>
+        <v>71316.67454721313</v>
       </c>
       <c r="CX42" s="25">
-        <v>53066.356110361332</v>
+        <v>53068.08510120296</v>
       </c>
       <c r="CY42" s="25">
-        <v>45518.530669208143</v>
+        <v>45363.168100517396</v>
       </c>
       <c r="CZ42" s="25">
-        <v>42433.267213849045</v>
+        <v>42477.927852334476</v>
       </c>
       <c r="DA42" s="25">
-        <v>66811.507797379236</v>
+        <v>66940.263586569476</v>
       </c>
       <c r="DB42" s="18"/>
       <c r="DC42" s="18"/>
@@ -9080,22 +9082,22 @@
         <v>39263.09269115288</v>
       </c>
       <c r="CV43" s="25">
-        <v>62338.742384439618</v>
+        <v>62343.134314701259</v>
       </c>
       <c r="CW43" s="25">
-        <v>81272.634446154829</v>
+        <v>81303.944986501418</v>
       </c>
       <c r="CX43" s="25">
-        <v>55499.490956783491</v>
+        <v>55616.56823175399</v>
       </c>
       <c r="CY43" s="25">
-        <v>40731.969725539631</v>
+        <v>40737.948423328533</v>
       </c>
       <c r="CZ43" s="25">
-        <v>61747.325024861515</v>
+        <v>61676.566953512447</v>
       </c>
       <c r="DA43" s="25">
-        <v>80190.040261113027</v>
+        <v>80447.531696095204</v>
       </c>
       <c r="DB43" s="18"/>
       <c r="DC43" s="18"/>
@@ -9474,19 +9476,19 @@
         <v>476721.03954355739</v>
       </c>
       <c r="CW44" s="25">
-        <v>501036.80901641428</v>
+        <v>501202.78756015957</v>
       </c>
       <c r="CX44" s="25">
-        <v>484091.32546900056</v>
+        <v>484091.61566184752</v>
       </c>
       <c r="CY44" s="25">
-        <v>590367.88918947638</v>
+        <v>590348.9208898996</v>
       </c>
       <c r="CZ44" s="25">
-        <v>480695.9536052742</v>
+        <v>480681.78500746447</v>
       </c>
       <c r="DA44" s="25">
-        <v>500741.26542923891</v>
+        <v>501771.40644787182</v>
       </c>
       <c r="DB44" s="18"/>
       <c r="DC44" s="18"/>
@@ -9856,28 +9858,28 @@
         <v>117556.60613118888</v>
       </c>
       <c r="CT45" s="25">
-        <v>96377.069517745331</v>
+        <v>96228.084022778901</v>
       </c>
       <c r="CU45" s="25">
-        <v>91406.582589863261</v>
+        <v>91396.365335167124</v>
       </c>
       <c r="CV45" s="25">
-        <v>110511.9898351297</v>
+        <v>110498.39786567478</v>
       </c>
       <c r="CW45" s="25">
-        <v>122824.86039783062</v>
+        <v>122515.13365368142</v>
       </c>
       <c r="CX45" s="25">
-        <v>97512.194677345411</v>
+        <v>97478.797567687929</v>
       </c>
       <c r="CY45" s="25">
-        <v>95507.057453543966</v>
+        <v>96248.905937491669</v>
       </c>
       <c r="CZ45" s="25">
-        <v>109685.91505743204</v>
+        <v>110223.37965508863</v>
       </c>
       <c r="DA45" s="25">
-        <v>119496.17196760121</v>
+        <v>120110.55217656854</v>
       </c>
       <c r="DB45" s="18"/>
       <c r="DC45" s="18"/>
@@ -10247,28 +10249,28 @@
         <v>182360.82351197329</v>
       </c>
       <c r="CT46" s="25">
-        <v>175292.47114031261</v>
+        <v>174920.05909523554</v>
       </c>
       <c r="CU46" s="25">
-        <v>151039.02105366523</v>
+        <v>151064.34214016705</v>
       </c>
       <c r="CV46" s="25">
-        <v>225159.81942963353</v>
+        <v>225434.79124886566</v>
       </c>
       <c r="CW46" s="25">
-        <v>203231.85149515138</v>
+        <v>204058.51015249218</v>
       </c>
       <c r="CX46" s="25">
-        <v>192861.11032540922</v>
+        <v>193014.65208029404</v>
       </c>
       <c r="CY46" s="25">
-        <v>165874.15027150017</v>
+        <v>165661.1800432466</v>
       </c>
       <c r="CZ46" s="25">
-        <v>250546.94624124377</v>
+        <v>250911.56397864548</v>
       </c>
       <c r="DA46" s="25">
-        <v>216191.35996159544</v>
+        <v>215584.36277543131</v>
       </c>
       <c r="DB46" s="18"/>
       <c r="DC46" s="18"/>
@@ -10647,19 +10649,19 @@
         <v>397003.9699898003</v>
       </c>
       <c r="CW47" s="25">
-        <v>369251.48516124854</v>
+        <v>369190.43232349714</v>
       </c>
       <c r="CX47" s="25">
-        <v>417147.98113027698</v>
+        <v>417356.50929629174</v>
       </c>
       <c r="CY47" s="25">
-        <v>385104.38864896621</v>
+        <v>385130.24683952401</v>
       </c>
       <c r="CZ47" s="25">
-        <v>415170.80273819854</v>
+        <v>413042.04591310472</v>
       </c>
       <c r="DA47" s="25">
-        <v>391026.41511731246</v>
+        <v>391363.50081725052</v>
       </c>
       <c r="DB47" s="18"/>
       <c r="DC47" s="18"/>
@@ -11029,28 +11031,28 @@
         <v>136075.29476404996</v>
       </c>
       <c r="CT48" s="25">
-        <v>126704.29476575697</v>
+        <v>126764.05196799693</v>
       </c>
       <c r="CU48" s="25">
-        <v>139282.16569470346</v>
+        <v>139497.02156326515</v>
       </c>
       <c r="CV48" s="25">
-        <v>105274.14855638427</v>
+        <v>105421.139003786</v>
       </c>
       <c r="CW48" s="25">
-        <v>141271.96959121188</v>
+        <v>141767.15349707103</v>
       </c>
       <c r="CX48" s="25">
-        <v>133689.60116874235</v>
+        <v>133945.93223476945</v>
       </c>
       <c r="CY48" s="25">
-        <v>146032.56112021251</v>
+        <v>145487.57803359235</v>
       </c>
       <c r="CZ48" s="25">
-        <v>109708.56376549187</v>
+        <v>109853.04126551877</v>
       </c>
       <c r="DA48" s="25">
-        <v>145550.54699653084</v>
+        <v>146789.74867700256</v>
       </c>
       <c r="DB48" s="18"/>
       <c r="DC48" s="18"/>
@@ -11429,19 +11431,19 @@
         <v>61064.848026934618</v>
       </c>
       <c r="CW49" s="25">
-        <v>92738.684566163356</v>
+        <v>92346.186056573933</v>
       </c>
       <c r="CX49" s="25">
-        <v>82672.47987679478</v>
+        <v>82414.348164836731</v>
       </c>
       <c r="CY49" s="25">
-        <v>60148.608125969782</v>
+        <v>59807.697598395425</v>
       </c>
       <c r="CZ49" s="25">
-        <v>62656.242492046302</v>
+        <v>62676.064569389775</v>
       </c>
       <c r="DA49" s="25">
-        <v>98243.299900233003</v>
+        <v>98793.237167360829</v>
       </c>
       <c r="DB49" s="18"/>
       <c r="DC49" s="18"/>
@@ -11811,28 +11813,28 @@
         <v>230919.68030107941</v>
       </c>
       <c r="CT50" s="25">
-        <v>219970.3295580204</v>
+        <v>221111.50565957811</v>
       </c>
       <c r="CU50" s="25">
-        <v>187916.10142949261</v>
+        <v>188535.18231670948</v>
       </c>
       <c r="CV50" s="25">
-        <v>220808.29256710614</v>
+        <v>221326.35354984098</v>
       </c>
       <c r="CW50" s="25">
-        <v>244891.60101847848</v>
+        <v>246392.73844266223</v>
       </c>
       <c r="CX50" s="25">
-        <v>234653.13108019371</v>
+        <v>234601.66322757609</v>
       </c>
       <c r="CY50" s="25">
-        <v>206720.6710999356</v>
+        <v>206804.28092574974</v>
       </c>
       <c r="CZ50" s="25">
-        <v>234874.53267463742</v>
+        <v>234805.00596174184</v>
       </c>
       <c r="DA50" s="25">
-        <v>262457.42950502015</v>
+        <v>262734.49458966724</v>
       </c>
       <c r="DB50" s="18"/>
       <c r="DC50" s="18"/>
@@ -12205,25 +12207,25 @@
         <v>393382.53130462539</v>
       </c>
       <c r="CU51" s="25">
-        <v>230233.36938277504</v>
+        <v>230292.03169511346</v>
       </c>
       <c r="CV51" s="25">
-        <v>310323.71405957354</v>
+        <v>310364.59956673486</v>
       </c>
       <c r="CW51" s="25">
-        <v>390876.52060471731</v>
+        <v>392405.02534728439</v>
       </c>
       <c r="CX51" s="25">
-        <v>417861.11692254274</v>
+        <v>417649.05401239265</v>
       </c>
       <c r="CY51" s="25">
-        <v>246676.60730027495</v>
+        <v>246789.31932561207</v>
       </c>
       <c r="CZ51" s="25">
-        <v>326543.13937024307</v>
+        <v>326523.21472551575</v>
       </c>
       <c r="DA51" s="25">
-        <v>420170.77524600504</v>
+        <v>420188.94427363185</v>
       </c>
       <c r="DB51" s="18"/>
       <c r="DC51" s="18"/>
@@ -12593,28 +12595,28 @@
         <v>705407.28925418388</v>
       </c>
       <c r="CT52" s="25">
-        <v>545156.12572248222</v>
+        <v>544911.45483333932</v>
       </c>
       <c r="CU52" s="25">
-        <v>508422.53169132647</v>
+        <v>508087.13168039639</v>
       </c>
       <c r="CV52" s="25">
-        <v>590373.55782571109</v>
+        <v>589926.64879055077</v>
       </c>
       <c r="CW52" s="25">
-        <v>758934.00048357504</v>
+        <v>759065.79900704417</v>
       </c>
       <c r="CX52" s="25">
-        <v>568742.97307786741</v>
+        <v>568219.75374489778</v>
       </c>
       <c r="CY52" s="25">
-        <v>529080.96075821272</v>
+        <v>528530.85082952632</v>
       </c>
       <c r="CZ52" s="25">
-        <v>612466.60998009739</v>
+        <v>612808.73840665352</v>
       </c>
       <c r="DA52" s="25">
-        <v>788789.92321897426</v>
+        <v>789234.57327706018</v>
       </c>
       <c r="DB52" s="18"/>
       <c r="DC52" s="18"/>
@@ -13164,28 +13166,28 @@
         <v>4419486.9323978228</v>
       </c>
       <c r="CT54" s="10">
-        <v>3865193.805108537</v>
+        <v>3865693.3416082673</v>
       </c>
       <c r="CU54" s="10">
-        <v>3754005.1109577147</v>
+        <v>3755046.4670782122</v>
       </c>
       <c r="CV54" s="10">
-        <v>3875929.6305119842</v>
+        <v>3875853.4066901584</v>
       </c>
       <c r="CW54" s="10">
-        <v>4628997.5173412496</v>
+        <v>4631018.5023289919</v>
       </c>
       <c r="CX54" s="10">
-        <v>4069803.2548084343</v>
+        <v>4069778.3676542481</v>
       </c>
       <c r="CY54" s="10">
-        <v>3953573.6827925313</v>
+        <v>3950324.1770730326</v>
       </c>
       <c r="CZ54" s="10">
-        <v>4033506.8997628824</v>
+        <v>4029586.4153202316</v>
       </c>
       <c r="DA54" s="10">
-        <v>4802699.0399274528</v>
+        <v>4805972.1092409659</v>
       </c>
       <c r="DB54" s="8"/>
       <c r="DC54" s="8"/>
@@ -13746,7 +13748,7 @@
     </row>
     <row r="61" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CT61" s="28"/>
       <c r="CU61" s="28"/>
@@ -13779,7 +13781,7 @@
     </row>
     <row r="64" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="CX64" s="28"/>
       <c r="CY64" s="28"/>
@@ -14555,28 +14557,28 @@
         <v>6.8814672046695762</v>
       </c>
       <c r="CP70" s="32">
-        <v>5.0207955133494835</v>
+        <v>5.0261374107350321</v>
       </c>
       <c r="CQ70" s="32">
-        <v>6.6207819682570204</v>
+        <v>6.6209511562050238</v>
       </c>
       <c r="CR70" s="32">
-        <v>7.1943513367446457</v>
+        <v>7.2113797481147657</v>
       </c>
       <c r="CS70" s="32">
-        <v>4.7717007129400457</v>
+        <v>4.6868927005098868</v>
       </c>
       <c r="CT70" s="32">
-        <v>7.7681837727117369</v>
+        <v>7.7882590782173793</v>
       </c>
       <c r="CU70" s="32">
-        <v>5.9825179317869868</v>
+        <v>5.8062130012313418</v>
       </c>
       <c r="CV70" s="32">
-        <v>5.0450271517897818</v>
+        <v>4.785315595707857</v>
       </c>
       <c r="CW70" s="32">
-        <v>4.4814283359297917</v>
+        <v>4.5040021672833319</v>
       </c>
       <c r="CX70" s="33"/>
       <c r="CY70" s="33"/>
@@ -14937,25 +14939,25 @@
         <v>6.1650038638633333</v>
       </c>
       <c r="CQ71" s="32">
-        <v>9.2879833847110689</v>
+        <v>10.384001714218854</v>
       </c>
       <c r="CR71" s="32">
-        <v>6.8020390520198077</v>
+        <v>4.9375602451987817</v>
       </c>
       <c r="CS71" s="32">
-        <v>6.7352233138463475</v>
+        <v>5.9035356057570709</v>
       </c>
       <c r="CT71" s="32">
-        <v>11.013039312248736</v>
+        <v>11.016656303169952</v>
       </c>
       <c r="CU71" s="32">
-        <v>1.4813474358140581</v>
+        <v>0.13079072514217671</v>
       </c>
       <c r="CV71" s="32">
-        <v>-3.877093910674688</v>
+        <v>-2.0662635100455304</v>
       </c>
       <c r="CW71" s="32">
-        <v>-3.6307470722110793</v>
+        <v>-2.6867580532877611</v>
       </c>
       <c r="CX71" s="33"/>
       <c r="CY71" s="33"/>
@@ -15319,22 +15321,22 @@
         <v>-1.3528503723858591</v>
       </c>
       <c r="CR72" s="32">
-        <v>8.3476647277245632</v>
+        <v>8.3552981089782605</v>
       </c>
       <c r="CS72" s="32">
-        <v>5.6974487057801042</v>
+        <v>5.7381689833346172</v>
       </c>
       <c r="CT72" s="32">
-        <v>6.0643715561258205</v>
+        <v>6.2881164478207836</v>
       </c>
       <c r="CU72" s="32">
-        <v>5.4355618737063054</v>
+        <v>5.4510378589064601</v>
       </c>
       <c r="CV72" s="32">
-        <v>0.74470604558676712</v>
+        <v>0.62217063154308505</v>
       </c>
       <c r="CW72" s="32">
-        <v>0.57017948111509043</v>
+        <v>0.85425742935640869</v>
       </c>
       <c r="CX72" s="33"/>
       <c r="CY72" s="33"/>
@@ -15701,19 +15703,19 @@
         <v>6.9571739447209779</v>
       </c>
       <c r="CS73" s="32">
-        <v>6.146743608712967</v>
+        <v>6.1819068574213247</v>
       </c>
       <c r="CT73" s="32">
-        <v>4.0206940382467167</v>
+        <v>4.0207563943761357</v>
       </c>
       <c r="CU73" s="32">
-        <v>3.3535983115463068</v>
+        <v>3.3502775990702247</v>
       </c>
       <c r="CV73" s="32">
-        <v>2.9780180299354413</v>
+        <v>2.9749827347353062</v>
       </c>
       <c r="CW73" s="32">
-        <v>2.6406330390084349</v>
+        <v>2.8177282016049929</v>
       </c>
       <c r="CX73" s="33"/>
       <c r="CY73" s="33"/>
@@ -16071,28 +16073,28 @@
         <v>5.4593178118927028</v>
       </c>
       <c r="CP74" s="32">
-        <v>6.5143115548516732</v>
+        <v>6.3496552988831638</v>
       </c>
       <c r="CQ74" s="32">
-        <v>5.3124233634322024</v>
+        <v>5.3006517401892808</v>
       </c>
       <c r="CR74" s="32">
-        <v>5.5365629710199471</v>
+        <v>5.5235829338093225</v>
       </c>
       <c r="CS74" s="32">
-        <v>7.1903482061526489</v>
+        <v>6.9200469214894866</v>
       </c>
       <c r="CT74" s="32">
-        <v>3.5535176123636205</v>
+        <v>3.6783236147438743</v>
       </c>
       <c r="CU74" s="32">
-        <v>6.6657520170082734</v>
+        <v>7.5062922087241617</v>
       </c>
       <c r="CV74" s="32">
-        <v>1.504540853650127</v>
+        <v>2.0144632991429461</v>
       </c>
       <c r="CW74" s="32">
-        <v>-0.70086194441687155</v>
+        <v>6.2002573040501829E-2</v>
       </c>
       <c r="CX74" s="33"/>
       <c r="CY74" s="33"/>
@@ -16450,28 +16452,28 @@
         <v>10.754431233513429</v>
       </c>
       <c r="CP75" s="32">
-        <v>10.81662078112862</v>
+        <v>10.581188853532609</v>
       </c>
       <c r="CQ75" s="32">
-        <v>12.665999060581058</v>
+        <v>12.684887063748221</v>
       </c>
       <c r="CR75" s="32">
-        <v>14.048458366043178</v>
+        <v>14.187737710630373</v>
       </c>
       <c r="CS75" s="32">
-        <v>14.271742994448289</v>
+        <v>14.736550675630284</v>
       </c>
       <c r="CT75" s="32">
-        <v>12.578337225755078</v>
+        <v>12.907838530988428</v>
       </c>
       <c r="CU75" s="32">
-        <v>12.477351568032518</v>
+        <v>12.314109897848795</v>
       </c>
       <c r="CV75" s="32">
-        <v>14.374493767565411</v>
+        <v>14.40123133092446</v>
       </c>
       <c r="CW75" s="32">
-        <v>9.2656728197533198</v>
+        <v>8.517487380089122</v>
       </c>
       <c r="CX75" s="33"/>
       <c r="CY75" s="33"/>
@@ -16838,19 +16840,19 @@
         <v>6.7902677120955275</v>
       </c>
       <c r="CS76" s="32">
-        <v>9.7737540474051912</v>
+        <v>9.7556038179151301</v>
       </c>
       <c r="CT76" s="32">
-        <v>8.4506815835195823</v>
+        <v>8.504895010784395</v>
       </c>
       <c r="CU76" s="32">
-        <v>9.105157176967154</v>
+        <v>9.1124831437135185</v>
       </c>
       <c r="CV76" s="32">
-        <v>4.1189667779527639</v>
+        <v>3.5851046670132121</v>
       </c>
       <c r="CW76" s="32">
-        <v>6.9382071305526409</v>
+        <v>7.0480931519140881</v>
       </c>
       <c r="CX76" s="33"/>
       <c r="CY76" s="33"/>
@@ -17208,28 +17210,28 @@
         <v>5.1199076712435101</v>
       </c>
       <c r="CP77" s="32">
-        <v>5.2898962431098511</v>
+        <v>5.3395538307650696</v>
       </c>
       <c r="CQ77" s="32">
-        <v>7.6768239142634371</v>
+        <v>7.8429255641815843</v>
       </c>
       <c r="CR77" s="32">
-        <v>4.7750074817832342</v>
+        <v>4.9213009967387933</v>
       </c>
       <c r="CS77" s="32">
-        <v>4.0205603380900641</v>
+        <v>4.3851712903329059</v>
       </c>
       <c r="CT77" s="32">
-        <v>5.8200994096956151</v>
+        <v>5.9730148485713386</v>
       </c>
       <c r="CU77" s="32">
-        <v>5.2190780694109122</v>
+        <v>4.6649524318506081</v>
       </c>
       <c r="CV77" s="32">
-        <v>4.7844795541680014</v>
+        <v>4.776177276509145</v>
       </c>
       <c r="CW77" s="32">
-        <v>3.7274477610400396</v>
+        <v>4.245173815947993</v>
       </c>
       <c r="CX77" s="33"/>
       <c r="CY77" s="33"/>
@@ -17596,19 +17598,19 @@
         <v>6.4090201084139977</v>
       </c>
       <c r="CS78" s="32">
-        <v>11.841800107850958</v>
+        <v>11.368451363931584</v>
       </c>
       <c r="CT78" s="32">
-        <v>11.746666958366106</v>
+        <v>11.397755706513536</v>
       </c>
       <c r="CU78" s="32">
-        <v>8.3297017599819583</v>
+        <v>7.715710232503497</v>
       </c>
       <c r="CV78" s="32">
-        <v>4.7810512582453271</v>
+        <v>4.8142000399079734</v>
       </c>
       <c r="CW78" s="32">
-        <v>8.0193017454516422</v>
+        <v>9.0856460685615872</v>
       </c>
       <c r="CX78" s="33"/>
       <c r="CY78" s="33"/>
@@ -17966,28 +17968,28 @@
         <v>11.602967362586554</v>
       </c>
       <c r="CP79" s="32">
-        <v>9.1121196783565068</v>
+        <v>9.6781784900945524</v>
       </c>
       <c r="CQ79" s="32">
-        <v>4.798762428933955</v>
+        <v>5.1440170948736608</v>
       </c>
       <c r="CR79" s="32">
-        <v>9.1057043873528016</v>
+        <v>9.361688471010865</v>
       </c>
       <c r="CS79" s="32">
-        <v>10.657442008195119</v>
+        <v>11.335750397589052</v>
       </c>
       <c r="CT79" s="32">
-        <v>11.204424428751025</v>
+        <v>10.606223289970245</v>
       </c>
       <c r="CU79" s="32">
-        <v>15.090981778694072</v>
+        <v>14.759461517661393</v>
       </c>
       <c r="CV79" s="32">
-        <v>10.021903969998334</v>
+        <v>9.7318824581456624</v>
       </c>
       <c r="CW79" s="32">
-        <v>10.385409419307095</v>
+        <v>9.8287101496879643</v>
       </c>
       <c r="CX79" s="33"/>
       <c r="CY79" s="33"/>
@@ -18348,25 +18350,25 @@
         <v>17.973086236168882</v>
       </c>
       <c r="CQ80" s="32">
-        <v>16.990578005336303</v>
+        <v>17.02038662016048</v>
       </c>
       <c r="CR80" s="32">
-        <v>14.965921148128842</v>
+        <v>14.981068040807216</v>
       </c>
       <c r="CS80" s="32">
-        <v>9.6724702139006098</v>
+        <v>10.101339388727595</v>
       </c>
       <c r="CT80" s="32">
-        <v>8.3767474002661118</v>
+        <v>8.3217466176722041</v>
       </c>
       <c r="CU80" s="32">
-        <v>9.4275343382554979</v>
+        <v>9.4496469879247655</v>
       </c>
       <c r="CV80" s="32">
-        <v>7.680085140657738</v>
+        <v>7.6593305964880614</v>
       </c>
       <c r="CW80" s="32">
-        <v>10.159656511819833</v>
+        <v>9.7353051485010553</v>
       </c>
       <c r="CX80" s="33"/>
       <c r="CY80" s="33"/>
@@ -18724,28 +18726,28 @@
         <v>13.095768102237358</v>
       </c>
       <c r="CP81" s="32">
-        <v>9.4159829858224668</v>
+        <v>9.3668761252728956</v>
       </c>
       <c r="CQ81" s="32">
-        <v>11.300564491975081</v>
+        <v>11.227140896008649</v>
       </c>
       <c r="CR81" s="32">
-        <v>10.342464574328304</v>
+        <v>10.258936029178443</v>
       </c>
       <c r="CS81" s="32">
-        <v>10.63374262686736</v>
+        <v>10.652955580714178</v>
       </c>
       <c r="CT81" s="32">
-        <v>7.0842154463297788</v>
+        <v>7.0337402139071656</v>
       </c>
       <c r="CU81" s="32">
-        <v>6.6207883221314034</v>
+        <v>6.5802394168814118</v>
       </c>
       <c r="CV81" s="32">
-        <v>6.2200998573151765</v>
+        <v>6.359949005244431</v>
       </c>
       <c r="CW81" s="32">
-        <v>6.3736850122300126</v>
+        <v>6.4151687512959938</v>
       </c>
       <c r="CX81" s="33"/>
       <c r="CY81" s="33"/>
@@ -19279,28 +19281,28 @@
         <v>9.6323382491798384</v>
       </c>
       <c r="CP83" s="32">
-        <v>8.2898809321827684</v>
+        <v>8.3013115891205587</v>
       </c>
       <c r="CQ83" s="32">
-        <v>8.8579835677905976</v>
+        <v>8.8914552342874771</v>
       </c>
       <c r="CR83" s="32">
-        <v>8.5064848256970862</v>
+        <v>8.4928433485779777</v>
       </c>
       <c r="CS83" s="32">
-        <v>7.4750674956280534</v>
+        <v>7.5102893781240425</v>
       </c>
       <c r="CT83" s="32">
-        <v>7.7150759459390343</v>
+        <v>7.7024376082215582</v>
       </c>
       <c r="CU83" s="32">
-        <v>6.7851118468915388</v>
+        <v>6.663153102412295</v>
       </c>
       <c r="CV83" s="32">
-        <v>5.5220265498093823</v>
+        <v>5.4233791818841155</v>
       </c>
       <c r="CW83" s="32">
-        <v>5.4215057279384098</v>
+        <v>5.4505627561364491</v>
       </c>
       <c r="CX83" s="33"/>
       <c r="CY83" s="33"/>
@@ -19865,7 +19867,7 @@
     </row>
     <row r="90" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CX90" s="29"/>
       <c r="CY90" s="29"/>
@@ -19889,7 +19891,7 @@
     </row>
     <row r="93" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="CX93" s="29"/>
       <c r="CY93" s="29"/>
@@ -20665,28 +20667,28 @@
         <v>0.80356406436210648</v>
       </c>
       <c r="CP99" s="32">
-        <v>0.46293097027468377</v>
+        <v>0.46804103124564733</v>
       </c>
       <c r="CQ99" s="32">
-        <v>0.58564336628019475</v>
+        <v>0.58580297755190713</v>
       </c>
       <c r="CR99" s="32">
-        <v>3.215042339348841</v>
+        <v>3.2314386156322712</v>
       </c>
       <c r="CS99" s="32">
-        <v>1.4743172387257033</v>
+        <v>1.3921783109507118</v>
       </c>
       <c r="CT99" s="32">
-        <v>4.7640982883392979</v>
+        <v>4.7836139858813169</v>
       </c>
       <c r="CU99" s="32">
-        <v>5.2210320446712331</v>
+        <v>5.0459938675299014</v>
       </c>
       <c r="CV99" s="32">
-        <v>4.4566894233429224</v>
+        <v>4.1984324635527202</v>
       </c>
       <c r="CW99" s="32">
-        <v>3.7703119847651863</v>
+        <v>3.7927321752196548</v>
       </c>
       <c r="CX99" s="33"/>
       <c r="CY99" s="33"/>
@@ -21047,25 +21049,25 @@
         <v>-1.5923554998845475</v>
       </c>
       <c r="CQ100" s="32">
-        <v>4.7540674230598086</v>
+        <v>5.8046163894728124</v>
       </c>
       <c r="CR100" s="32">
-        <v>3.4274401126292986</v>
+        <v>1.621872804688465</v>
       </c>
       <c r="CS100" s="32">
-        <v>3.569010532707992</v>
+        <v>2.7619941577504648</v>
       </c>
       <c r="CT100" s="32">
-        <v>7.2474705053609796</v>
+        <v>7.2509648077379012</v>
       </c>
       <c r="CU100" s="32">
-        <v>-2.2246392710534479</v>
+        <v>-3.5258751425456296</v>
       </c>
       <c r="CV100" s="32">
-        <v>-7.7296458427617409</v>
+        <v>-5.99139250458785</v>
       </c>
       <c r="CW100" s="32">
-        <v>-7.0471125260124978</v>
+        <v>-6.1365886567613046</v>
       </c>
       <c r="CX100" s="33"/>
       <c r="CY100" s="33"/>
@@ -21429,22 +21431,22 @@
         <v>-4.6031225510484717</v>
       </c>
       <c r="CR101" s="32">
-        <v>5.1591824417349272</v>
+        <v>5.1665911859281692</v>
       </c>
       <c r="CS101" s="32">
-        <v>3.0690405094083673</v>
+        <v>3.1087481843637477</v>
       </c>
       <c r="CT101" s="32">
-        <v>3.9112294194191719</v>
+        <v>4.1304322151481045</v>
       </c>
       <c r="CU101" s="32">
-        <v>3.7411139411280629</v>
+        <v>3.7563412127949363</v>
       </c>
       <c r="CV101" s="32">
-        <v>-0.94871557711392995</v>
+        <v>-1.0691912886895523</v>
       </c>
       <c r="CW101" s="32">
-        <v>-1.3320525320968244</v>
+        <v>-1.0533477687317543</v>
       </c>
       <c r="CX101" s="33"/>
       <c r="CY101" s="33"/>
@@ -21811,19 +21813,19 @@
         <v>3.7079916376457618</v>
       </c>
       <c r="CS102" s="32">
-        <v>3.6598436068550342</v>
+        <v>3.6941830198025798</v>
       </c>
       <c r="CT102" s="32">
-        <v>2.1677630674365957</v>
+        <v>2.1678243128100831</v>
       </c>
       <c r="CU102" s="32">
-        <v>0.54049002870621621</v>
+        <v>0.53725970034761872</v>
       </c>
       <c r="CV102" s="32">
-        <v>0.83380294386054743</v>
+        <v>0.83083084977732824</v>
       </c>
       <c r="CW102" s="32">
-        <v>-5.8986402167846563E-2</v>
+        <v>0.11345086296911688</v>
       </c>
       <c r="CX102" s="33"/>
       <c r="CY102" s="33"/>
@@ -22181,28 +22183,28 @@
         <v>0.57884757024950773</v>
       </c>
       <c r="CP103" s="32">
-        <v>2.9540265553662692</v>
+        <v>2.7948740029812598</v>
       </c>
       <c r="CQ103" s="32">
-        <v>2.2770666647881512</v>
+        <v>2.2656343279686268</v>
       </c>
       <c r="CR103" s="32">
-        <v>2.7668773381008975</v>
+        <v>2.7542379470281162</v>
       </c>
       <c r="CS103" s="32">
-        <v>4.4814616889862862</v>
+        <v>4.2179913878757276</v>
       </c>
       <c r="CT103" s="32">
-        <v>1.1777958857641693</v>
+        <v>1.2997385925432923</v>
       </c>
       <c r="CU103" s="32">
-        <v>4.4859732718368122</v>
+        <v>5.3093365195972382</v>
       </c>
       <c r="CV103" s="32">
-        <v>-0.74749787686391755</v>
+        <v>-0.24888886707702795</v>
       </c>
       <c r="CW103" s="32">
-        <v>-2.710109679300885</v>
+        <v>-1.9626811850934303</v>
       </c>
       <c r="CX103" s="33"/>
       <c r="CY103" s="33"/>
@@ -22560,28 +22562,28 @@
         <v>6.6931300606275101</v>
       </c>
       <c r="CP104" s="32">
-        <v>7.3942982481230359</v>
+        <v>7.1661371070310622</v>
       </c>
       <c r="CQ104" s="32">
-        <v>9.4216100629114834</v>
+        <v>9.439954157266996</v>
       </c>
       <c r="CR104" s="32">
-        <v>11.118603432356267</v>
+        <v>11.25430475159574</v>
       </c>
       <c r="CS104" s="32">
-        <v>11.444907728116149</v>
+        <v>11.898217074619794</v>
       </c>
       <c r="CT104" s="32">
-        <v>10.02247219792676</v>
+        <v>10.344492837843646</v>
       </c>
       <c r="CU104" s="32">
-        <v>9.8220506954715461</v>
+        <v>9.6626627411091448</v>
       </c>
       <c r="CV104" s="32">
-        <v>11.275158629954475</v>
+        <v>11.301171655290361</v>
       </c>
       <c r="CW104" s="32">
-        <v>6.3767113132624473</v>
+        <v>5.6483077399349497</v>
       </c>
       <c r="CX104" s="33"/>
       <c r="CY104" s="33"/>
@@ -22948,19 +22950,19 @@
         <v>6.4608375803358626</v>
       </c>
       <c r="CS105" s="32">
-        <v>10.682618246504006</v>
+        <v>10.664317743445096</v>
       </c>
       <c r="CT105" s="32">
-        <v>8.50626881139425</v>
+        <v>8.5605100261665967</v>
       </c>
       <c r="CU105" s="32">
-        <v>11.398233910577531</v>
+        <v>11.405713848083224</v>
       </c>
       <c r="CV105" s="32">
-        <v>4.575982640391473</v>
+        <v>4.0397772152546594</v>
       </c>
       <c r="CW105" s="32">
-        <v>5.8970460055306262</v>
+        <v>6.0058621655516049</v>
       </c>
       <c r="CX105" s="33"/>
       <c r="CY105" s="33"/>
@@ -23318,28 +23320,28 @@
         <v>4.4735393069219072</v>
       </c>
       <c r="CP106" s="32">
-        <v>4.8473586901967423</v>
+        <v>4.8968075650684</v>
       </c>
       <c r="CQ106" s="32">
-        <v>7.1551338759191339</v>
+        <v>7.3204307697814812</v>
       </c>
       <c r="CR106" s="32">
-        <v>4.3012186882609598</v>
+        <v>4.4468506692341521</v>
       </c>
       <c r="CS106" s="32">
-        <v>3.818970104876712</v>
+        <v>4.1828744467469932</v>
       </c>
       <c r="CT106" s="32">
-        <v>5.5130778446771416</v>
+        <v>5.665549621737938</v>
       </c>
       <c r="CU106" s="32">
-        <v>4.8465612175398149</v>
+        <v>4.2943974023203992</v>
       </c>
       <c r="CV106" s="32">
-        <v>4.2122546417295865</v>
+        <v>4.2039977025609687</v>
       </c>
       <c r="CW106" s="32">
-        <v>3.028610288155221</v>
+        <v>3.5428482945700779</v>
       </c>
       <c r="CX106" s="33"/>
       <c r="CY106" s="33"/>
@@ -23706,19 +23708,19 @@
         <v>3.1475577332778215</v>
       </c>
       <c r="CS107" s="32">
-        <v>9.1318363082023524</v>
+        <v>8.6699569608716729</v>
       </c>
       <c r="CT107" s="32">
-        <v>9.1803272862289731</v>
+        <v>8.8394290231487531</v>
       </c>
       <c r="CU107" s="32">
-        <v>6.0352291160964455</v>
+        <v>5.4342422100697831</v>
       </c>
       <c r="CV107" s="32">
-        <v>2.6060729151569291</v>
+        <v>2.6385336155172041</v>
       </c>
       <c r="CW107" s="32">
-        <v>5.9356193802193218</v>
+        <v>6.9813940197132212</v>
       </c>
       <c r="CX107" s="33"/>
       <c r="CY107" s="33"/>
@@ -24076,28 +24078,28 @@
         <v>7.724497601940655</v>
       </c>
       <c r="CP108" s="32">
-        <v>5.1409680089535783</v>
+        <v>5.6864250268502161</v>
       </c>
       <c r="CQ108" s="32">
-        <v>0.98459603204031509</v>
+        <v>1.3172851035524218</v>
       </c>
       <c r="CR108" s="32">
-        <v>3.5940849360241174</v>
+        <v>3.837137643979645</v>
       </c>
       <c r="CS108" s="32">
-        <v>6.0505543309180609</v>
+        <v>6.7006234035178949</v>
       </c>
       <c r="CT108" s="32">
-        <v>6.6749009067154788</v>
+        <v>6.1010654003538605</v>
       </c>
       <c r="CU108" s="32">
-        <v>10.006896443356965</v>
+        <v>9.690020920525626</v>
       </c>
       <c r="CV108" s="32">
-        <v>6.3703405085007887</v>
+        <v>6.0899446431559028</v>
       </c>
       <c r="CW108" s="32">
-        <v>7.1728995251316263</v>
+        <v>6.6324016893898374</v>
       </c>
       <c r="CX108" s="33"/>
       <c r="CY108" s="33"/>
@@ -24458,25 +24460,25 @@
         <v>11.850668430972533</v>
       </c>
       <c r="CQ109" s="32">
-        <v>11.147136023800257</v>
+        <v>11.1754557587997</v>
       </c>
       <c r="CR109" s="32">
-        <v>9.962223025619636</v>
+        <v>9.9767106753005947</v>
       </c>
       <c r="CS109" s="32">
-        <v>5.5937419828051134</v>
+        <v>6.0066614775765572</v>
       </c>
       <c r="CT109" s="32">
-        <v>6.2225909057872713</v>
+        <v>6.1686833493315163</v>
       </c>
       <c r="CU109" s="32">
-        <v>7.141987263437116</v>
+        <v>7.1636380594963782</v>
       </c>
       <c r="CV109" s="32">
-        <v>5.2266148463136375</v>
+        <v>5.2063331904921313</v>
       </c>
       <c r="CW109" s="32">
-        <v>7.4945035316951589</v>
+        <v>7.0804187336179751</v>
       </c>
       <c r="CX109" s="33"/>
       <c r="CY109" s="33"/>
@@ -24834,28 +24836,28 @@
         <v>10.393262419852249</v>
       </c>
       <c r="CP110" s="32">
-        <v>5.4316108908588774</v>
+        <v>5.384292251732802</v>
       </c>
       <c r="CQ110" s="32">
-        <v>7.7086155107577952</v>
+        <v>7.6375614787907153</v>
       </c>
       <c r="CR110" s="32">
-        <v>7.1355713724413192</v>
+        <v>7.0544704250856398</v>
       </c>
       <c r="CS110" s="32">
-        <v>7.5880575725243915</v>
+        <v>7.6067416044980973</v>
       </c>
       <c r="CT110" s="32">
-        <v>4.3266224559296944</v>
+        <v>4.2774470429672391</v>
       </c>
       <c r="CU110" s="32">
-        <v>4.0632402734323421</v>
+        <v>4.0236640281591889</v>
       </c>
       <c r="CV110" s="32">
-        <v>3.7422157312994955</v>
+        <v>3.8788025024831398</v>
       </c>
       <c r="CW110" s="32">
-        <v>3.9339287364086601</v>
+        <v>3.9744610163546525</v>
       </c>
       <c r="CX110" s="33"/>
       <c r="CY110" s="33"/>
@@ -25389,28 +25391,28 @@
         <v>5.343704249867784</v>
       </c>
       <c r="CP112" s="32">
-        <v>4.6865772293330821</v>
+        <v>4.7001068914909609</v>
       </c>
       <c r="CQ112" s="32">
-        <v>4.8100315679690908</v>
+        <v>4.8391057339962629</v>
       </c>
       <c r="CR112" s="32">
-        <v>5.2145769719890609</v>
+        <v>5.2125078278267125</v>
       </c>
       <c r="CS112" s="32">
-        <v>4.740608766315674</v>
+        <v>4.7863377167267913</v>
       </c>
       <c r="CT112" s="32">
-        <v>5.2936401126761012</v>
+        <v>5.2793899570180258</v>
       </c>
       <c r="CU112" s="32">
-        <v>5.3161507759349718</v>
+        <v>5.2004072840878877</v>
       </c>
       <c r="CV112" s="32">
-        <v>4.0655348335125296</v>
+        <v>3.966429905855378</v>
       </c>
       <c r="CW112" s="32">
-        <v>3.7524652354095736</v>
+        <v>3.7778645631406675</v>
       </c>
       <c r="CX112" s="33"/>
       <c r="CY112" s="33"/>
@@ -25962,7 +25964,7 @@
     </row>
     <row r="118" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="120" spans="1:179" x14ac:dyDescent="0.2">
@@ -25972,7 +25974,7 @@
     </row>
     <row r="121" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
@@ -29498,7 +29500,7 @@
         <v>101.35581080861039</v>
       </c>
       <c r="CW134" s="32">
-        <v>98.566812466157259</v>
+        <v>98.566812466157245</v>
       </c>
       <c r="CX134" s="32">
         <v>106.42917639563254</v>
@@ -31053,7 +31055,7 @@
         <v>110.03034396890929</v>
       </c>
       <c r="CT138" s="32">
-        <v>124.92431858292233</v>
+        <v>124.9243185829223</v>
       </c>
       <c r="CU138" s="32">
         <v>127.01205482257924</v>
@@ -31065,7 +31067,7 @@
         <v>113.14516713526697</v>
       </c>
       <c r="CX138" s="32">
-        <v>128.22635613714581</v>
+        <v>128.22635613714584</v>
       </c>
       <c r="CY138" s="32">
         <v>130.13361275330686</v>
@@ -31624,28 +31626,28 @@
         <v>120.6221131912165</v>
       </c>
       <c r="CT140" s="32">
-        <v>123.73530029663758</v>
+        <v>123.73237017694261</v>
       </c>
       <c r="CU140" s="32">
-        <v>125.38888860637287</v>
+        <v>125.39265943748575</v>
       </c>
       <c r="CV140" s="32">
-        <v>126.90148736904587</v>
+        <v>126.88802863819969</v>
       </c>
       <c r="CW140" s="32">
-        <v>123.77118969792001</v>
+        <v>123.75772049258715</v>
       </c>
       <c r="CX140" s="32">
-        <v>126.5808386373883</v>
+        <v>126.58012061563238</v>
       </c>
       <c r="CY140" s="32">
-        <v>127.13782639735946</v>
+        <v>127.13616588366756</v>
       </c>
       <c r="CZ140" s="32">
-        <v>128.67758899034115</v>
+        <v>128.66619320178566</v>
       </c>
       <c r="DA140" s="32">
-        <v>125.76226650699218</v>
+        <v>125.75245526872317</v>
       </c>
       <c r="DB140" s="8"/>
       <c r="DC140" s="8"/>
@@ -31846,7 +31848,7 @@
     </row>
     <row r="147" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="149" spans="1:179" x14ac:dyDescent="0.2">
@@ -31856,7 +31858,7 @@
     </row>
     <row r="150" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="151" spans="1:179" x14ac:dyDescent="0.2">
@@ -32636,28 +32638,28 @@
         <v>38.709884153094897</v>
       </c>
       <c r="CT156" s="32">
-        <v>33.740564826862929</v>
+        <v>33.738719717893417</v>
       </c>
       <c r="CU156" s="32">
-        <v>38.170292772200945</v>
+        <v>38.158620324187233</v>
       </c>
       <c r="CV156" s="32">
-        <v>34.178777670319668</v>
+        <v>34.188505348923833</v>
       </c>
       <c r="CW156" s="32">
-        <v>37.736197721258655</v>
+        <v>37.693299052814112</v>
       </c>
       <c r="CX156" s="32">
-        <v>33.757200270474712</v>
+        <v>33.765604035335699</v>
       </c>
       <c r="CY156" s="32">
-        <v>37.883405918903904</v>
+        <v>37.852050988756666</v>
       </c>
       <c r="CZ156" s="32">
-        <v>34.024276691643976</v>
+        <v>33.981583122580616</v>
       </c>
       <c r="DA156" s="32">
-        <v>37.399691938181796</v>
+        <v>37.35495101165894</v>
       </c>
       <c r="DB156" s="8"/>
       <c r="DC156" s="8"/>
@@ -33027,28 +33029,28 @@
         <v>2.1888403822131446</v>
       </c>
       <c r="CT157" s="32">
-        <v>1.7396351092961251</v>
+        <v>1.7394514995887309</v>
       </c>
       <c r="CU157" s="32">
-        <v>1.7988740278367596</v>
+        <v>1.8163559342248596</v>
       </c>
       <c r="CV157" s="32">
-        <v>1.7738230691692856</v>
+        <v>1.7430759885890661</v>
       </c>
       <c r="CW157" s="32">
-        <v>2.1737726938704962</v>
+        <v>2.1561279082576452</v>
       </c>
       <c r="CX157" s="32">
-        <v>1.7928983392648274</v>
+        <v>1.7929778895843174</v>
       </c>
       <c r="CY157" s="32">
-        <v>1.7095282015896343</v>
+        <v>1.7051170028474081</v>
       </c>
       <c r="CZ157" s="32">
-        <v>1.6158240499328815</v>
+        <v>1.6192418216260562</v>
       </c>
       <c r="DA157" s="32">
-        <v>1.9871168515060407</v>
+        <v>1.9897456335966761</v>
       </c>
       <c r="DB157" s="8"/>
       <c r="DC157" s="8"/>
@@ -33418,28 +33420,28 @@
         <v>1.6665380310410645</v>
       </c>
       <c r="CT158" s="32">
-        <v>1.2829534288431415</v>
+        <v>1.2828180195826528</v>
       </c>
       <c r="CU158" s="32">
-        <v>1.0515195026588942</v>
+        <v>1.05119628069412</v>
       </c>
       <c r="CV158" s="32">
-        <v>1.4578340988216794</v>
+        <v>1.4581201225368527</v>
       </c>
       <c r="CW158" s="32">
-        <v>1.6389737839370069</v>
+        <v>1.6390680460695517</v>
       </c>
       <c r="CX158" s="32">
-        <v>1.2632925147295018</v>
+        <v>1.2659723779209577</v>
       </c>
       <c r="CY158" s="32">
-        <v>1.0382304018463042</v>
+        <v>1.0392505337451001</v>
       </c>
       <c r="CZ158" s="32">
-        <v>1.3918332745409949</v>
+        <v>1.3917141805714557</v>
       </c>
       <c r="DA158" s="32">
-        <v>1.5635508758598957</v>
+        <v>1.5676254952267776</v>
       </c>
       <c r="DB158" s="8"/>
       <c r="DC158" s="8"/>
@@ -33809,28 +33811,28 @@
         <v>10.851789489709063</v>
       </c>
       <c r="CT159" s="32">
-        <v>11.268407984878746</v>
+        <v>11.267218661277582</v>
       </c>
       <c r="CU159" s="32">
-        <v>14.680481837094286</v>
+        <v>14.67596926821542</v>
       </c>
       <c r="CV159" s="32">
-        <v>12.249819284378011</v>
+        <v>12.251359530023008</v>
       </c>
       <c r="CW159" s="32">
-        <v>10.717668232278442</v>
+        <v>10.717706253956857</v>
       </c>
       <c r="CX159" s="32">
-        <v>10.881927241842131</v>
+        <v>10.882062037168383</v>
       </c>
       <c r="CY159" s="32">
-        <v>14.20872813231184</v>
+        <v>14.220144949673196</v>
       </c>
       <c r="CZ159" s="32">
-        <v>11.954490947297</v>
+        <v>11.966828855908499</v>
       </c>
       <c r="DA159" s="32">
-        <v>10.434951051658087</v>
+        <v>10.450112164051506</v>
       </c>
       <c r="DB159" s="8"/>
       <c r="DC159" s="8"/>
@@ -34200,28 +34202,28 @@
         <v>2.5859828462111296</v>
       </c>
       <c r="CT160" s="32">
-        <v>2.4692392511487053</v>
+        <v>2.4651619391117765</v>
       </c>
       <c r="CU160" s="32">
-        <v>2.377297976429483</v>
+        <v>2.3763015810543928</v>
       </c>
       <c r="CV160" s="32">
-        <v>2.7447926055598955</v>
+        <v>2.744800098364907</v>
       </c>
       <c r="CW160" s="32">
-        <v>2.5791321485030427</v>
+        <v>2.5717855365694997</v>
       </c>
       <c r="CX160" s="32">
-        <v>2.3738405050310609</v>
+        <v>2.3730554568847579</v>
       </c>
       <c r="CY160" s="32">
-        <v>2.3746407344493901</v>
+        <v>2.395085507209791</v>
       </c>
       <c r="CZ160" s="32">
-        <v>2.6402915322550209</v>
+        <v>2.6560456615134509</v>
       </c>
       <c r="DA160" s="32">
-        <v>2.4293487131433018</v>
+        <v>2.4403664072674704</v>
       </c>
       <c r="DB160" s="8"/>
       <c r="DC160" s="8"/>
@@ -34591,28 +34593,28 @@
         <v>4.0599390215841797</v>
       </c>
       <c r="CT161" s="32">
-        <v>4.2612723511315176</v>
+        <v>4.2517704001914032</v>
       </c>
       <c r="CU161" s="32">
-        <v>3.7524803900910482</v>
+        <v>3.7519558265381105</v>
       </c>
       <c r="CV161" s="32">
-        <v>5.5899219413574608</v>
+        <v>5.5974522329256811</v>
       </c>
       <c r="CW161" s="32">
-        <v>4.3166877607820213</v>
+        <v>4.3328262065374625</v>
       </c>
       <c r="CX161" s="32">
-        <v>4.4536658545108354</v>
+        <v>4.4572640738356082</v>
       </c>
       <c r="CY161" s="32">
-        <v>3.9525084423152648</v>
+        <v>3.9507324392433056</v>
       </c>
       <c r="CZ161" s="32">
-        <v>6.0588723809353429</v>
+        <v>6.074131115242877</v>
       </c>
       <c r="DA161" s="32">
-        <v>4.4740946287740506</v>
+        <v>4.4588421426957927</v>
       </c>
       <c r="DB161" s="8"/>
       <c r="DC161" s="8"/>
@@ -34982,28 +34984,28 @@
         <v>7.9297786635876166</v>
       </c>
       <c r="CT162" s="32">
-        <v>10.749590473904172</v>
+        <v>10.748455908873281</v>
       </c>
       <c r="CU162" s="32">
-        <v>9.4145467553759961</v>
+        <v>9.4116528591695676</v>
       </c>
       <c r="CV162" s="32">
-        <v>11.370821307660917</v>
+        <v>11.372251031446433</v>
       </c>
       <c r="CW162" s="32">
-        <v>8.0993814933164714</v>
+        <v>8.0953892915627623</v>
       </c>
       <c r="CX162" s="32">
-        <v>10.823001361700925</v>
+        <v>10.828539314613552</v>
       </c>
       <c r="CY162" s="32">
-        <v>9.6190900185408648</v>
+        <v>9.6277747664614779</v>
       </c>
       <c r="CZ162" s="32">
-        <v>11.219630675037703</v>
+        <v>11.173952329488161</v>
       </c>
       <c r="DA162" s="32">
-        <v>8.2159074638610701</v>
+        <v>8.2180309363383532</v>
       </c>
       <c r="DB162" s="8"/>
       <c r="DC162" s="8"/>
@@ -35373,28 +35375,28 @@
         <v>2.511127340851198</v>
       </c>
       <c r="CT163" s="32">
-        <v>2.811417037587967</v>
+        <v>2.8124461077378151</v>
       </c>
       <c r="CU163" s="32">
-        <v>3.0559073944770847</v>
+        <v>3.0596806286811966</v>
       </c>
       <c r="CV163" s="32">
-        <v>2.169340847330584</v>
+        <v>2.1726429642094569</v>
       </c>
       <c r="CW163" s="32">
-        <v>2.4304136686051896</v>
+        <v>2.438133681183515</v>
       </c>
       <c r="CX163" s="32">
-        <v>2.7619572078191235</v>
+        <v>2.7672854928341453</v>
       </c>
       <c r="CY163" s="32">
-        <v>3.0110916508042629</v>
+        <v>3.0023613416911976</v>
       </c>
       <c r="CZ163" s="32">
-        <v>2.1541782232151774</v>
+        <v>2.1593049487042824</v>
       </c>
       <c r="DA163" s="32">
-        <v>2.3913584340045313</v>
+        <v>2.4102637552467896</v>
       </c>
       <c r="DB163" s="8"/>
       <c r="DC163" s="8"/>
@@ -35764,28 +35766,28 @@
         <v>1.7924521906668685</v>
       </c>
       <c r="CT164" s="32">
-        <v>1.7931338247461133</v>
+        <v>1.792944568519264</v>
       </c>
       <c r="CU164" s="32">
-        <v>1.350220445796573</v>
+        <v>1.3498054074598944</v>
       </c>
       <c r="CV164" s="32">
-        <v>1.3678928452097994</v>
+        <v>1.3680648388489498</v>
       </c>
       <c r="CW164" s="32">
-        <v>1.865279867068689</v>
+        <v>1.8567769259402118</v>
       </c>
       <c r="CX164" s="32">
-        <v>1.8602477560917461</v>
+        <v>1.8544612868073356</v>
       </c>
       <c r="CY164" s="32">
-        <v>1.3697506672380795</v>
+        <v>1.3631253522068252</v>
       </c>
       <c r="CZ164" s="32">
-        <v>1.3582875065620499</v>
+        <v>1.3601596040598063</v>
       </c>
       <c r="DA164" s="32">
-        <v>1.9112440806962556</v>
+        <v>1.9207835906935355</v>
       </c>
       <c r="DB164" s="8"/>
       <c r="DC164" s="8"/>
@@ -36155,28 +36157,28 @@
         <v>4.6024140829590525</v>
       </c>
       <c r="CT165" s="32">
-        <v>5.1610134715853997</v>
+        <v>5.1872405614963748</v>
       </c>
       <c r="CU165" s="32">
-        <v>4.5766352357486815</v>
+        <v>4.5903013220008182</v>
       </c>
       <c r="CV165" s="32">
-        <v>5.3177542055100062</v>
+        <v>5.3309009369969411</v>
       </c>
       <c r="CW165" s="32">
-        <v>4.7386931811274202</v>
+        <v>4.7661784609701048</v>
       </c>
       <c r="CX165" s="32">
-        <v>5.3282006027153725</v>
+        <v>5.3270947301183611</v>
       </c>
       <c r="CY165" s="32">
-        <v>4.9326112359230869</v>
+        <v>4.9387299418275816</v>
       </c>
       <c r="CZ165" s="32">
-        <v>5.5445243203181604</v>
+        <v>5.5487672616273702</v>
       </c>
       <c r="DA165" s="32">
-        <v>4.9618204871893017</v>
+        <v>4.9640629602150677</v>
       </c>
       <c r="DB165" s="8"/>
       <c r="DC165" s="8"/>
@@ -36546,28 +36548,28 @@
         <v>8.5415135531985786</v>
       </c>
       <c r="CT166" s="32">
-        <v>10.483001599509253</v>
+        <v>10.481895171588816</v>
       </c>
       <c r="CU166" s="32">
-        <v>6.052953337262081</v>
+        <v>6.0526345347045929</v>
       </c>
       <c r="CV166" s="32">
-        <v>8.2748468384553693</v>
+        <v>8.276977643889559</v>
       </c>
       <c r="CW166" s="32">
-        <v>8.7161507554568978</v>
+        <v>8.7473681640511938</v>
       </c>
       <c r="CX166" s="32">
-        <v>10.547396512228262</v>
+        <v>10.54216801461857</v>
       </c>
       <c r="CY166" s="32">
-        <v>6.2027350789386793</v>
+        <v>6.2107550161608494</v>
       </c>
       <c r="CZ166" s="32">
-        <v>8.4440778975201223</v>
+        <v>8.4525261798511195</v>
       </c>
       <c r="DA166" s="32">
-        <v>9.1078965975337116</v>
+        <v>9.1027974592063732</v>
       </c>
       <c r="DB166" s="8"/>
       <c r="DC166" s="8"/>
@@ -36937,28 +36939,28 @@
         <v>14.559740244883201</v>
       </c>
       <c r="CT167" s="32">
-        <v>14.239770640505938</v>
+        <v>14.231877444138913</v>
       </c>
       <c r="CU167" s="32">
-        <v>13.718790325028159</v>
+        <v>13.7055260330698</v>
       </c>
       <c r="CV167" s="32">
-        <v>13.504375286227347</v>
+        <v>13.495849263245319</v>
       </c>
       <c r="CW167" s="32">
-        <v>14.987648693795666</v>
+        <v>14.985340472087097</v>
       </c>
       <c r="CX167" s="32">
-        <v>14.156371833591489</v>
+        <v>14.14351529027833</v>
       </c>
       <c r="CY167" s="32">
-        <v>13.697679517138701</v>
+        <v>13.694872160176599</v>
       </c>
       <c r="CZ167" s="32">
-        <v>13.593712500741576</v>
+        <v>13.615744918826305</v>
       </c>
       <c r="DA167" s="32">
-        <v>15.123018877591953</v>
+        <v>15.122418443802719</v>
       </c>
       <c r="DB167" s="8"/>
       <c r="DC167" s="8"/>
@@ -38090,7 +38092,7 @@
     </row>
     <row r="176" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="178" spans="1:179" x14ac:dyDescent="0.2">
@@ -38100,7 +38102,7 @@
     </row>
     <row r="179" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" spans="1:179" x14ac:dyDescent="0.2">
@@ -38880,28 +38882,28 @@
         <v>36.80984015330182</v>
       </c>
       <c r="CT185" s="32">
-        <v>32.894422176933666</v>
+        <v>32.89184442409028</v>
       </c>
       <c r="CU185" s="32">
-        <v>36.501499298954798</v>
+        <v>36.491434543912163</v>
       </c>
       <c r="CV185" s="32">
-        <v>32.775660411824433</v>
+        <v>32.781511684899392</v>
       </c>
       <c r="CW185" s="32">
-        <v>35.66194087678609</v>
+        <v>35.617523789319385</v>
       </c>
       <c r="CX185" s="32">
-        <v>32.728989845869428</v>
+        <v>32.736951941159973</v>
       </c>
       <c r="CY185" s="32">
-        <v>36.46853212082533</v>
+        <v>36.437872326535839</v>
       </c>
       <c r="CZ185" s="32">
-        <v>32.898855377624756</v>
+        <v>32.854664091526885</v>
       </c>
       <c r="DA185" s="32">
-        <v>35.668075186162916</v>
+        <v>35.622626491414316</v>
       </c>
       <c r="DB185" s="8"/>
       <c r="DC185" s="8"/>
@@ -39271,28 +39273,28 @@
         <v>1.57031473740653</v>
       </c>
       <c r="CT186" s="32">
-        <v>1.2801502176981192</v>
+        <v>1.2799847928435413</v>
       </c>
       <c r="CU186" s="32">
-        <v>1.2401206755194756</v>
+        <v>1.2522101341867413</v>
       </c>
       <c r="CV186" s="32">
-        <v>1.1865017990471138</v>
+        <v>1.1658115683119492</v>
       </c>
       <c r="CW186" s="32">
-        <v>1.5527496497655149</v>
+        <v>1.5399781821503664</v>
       </c>
       <c r="CX186" s="32">
-        <v>1.3039047046724908</v>
+        <v>1.3039551618578806</v>
       </c>
       <c r="CY186" s="32">
-        <v>1.1513262258731194</v>
+        <v>1.1483403909936563</v>
       </c>
       <c r="CZ186" s="32">
-        <v>1.0520192048349679</v>
+        <v>1.0541510585512224</v>
       </c>
       <c r="DA186" s="32">
-        <v>1.3911241833381351</v>
+        <v>1.3928558482030335</v>
       </c>
       <c r="DB186" s="8"/>
       <c r="DC186" s="8"/>
@@ -39662,28 +39664,28 @@
         <v>1.7842029387784624</v>
       </c>
       <c r="CT187" s="32">
-        <v>1.3818319875220162</v>
+        <v>1.3816534230438584</v>
       </c>
       <c r="CU187" s="32">
-        <v>1.0458987542810285</v>
+        <v>1.0456087037906445</v>
       </c>
       <c r="CV187" s="32">
-        <v>1.6083558868999666</v>
+        <v>1.6085008325415509</v>
       </c>
       <c r="CW187" s="32">
-        <v>1.7557286246469035</v>
+        <v>1.7556385262899024</v>
       </c>
       <c r="CX187" s="32">
-        <v>1.3636897776621355</v>
+        <v>1.3665748649553722</v>
       </c>
       <c r="CY187" s="32">
-        <v>1.0302570027421212</v>
+        <v>1.0312558310977165</v>
       </c>
       <c r="CZ187" s="32">
-        <v>1.5308595363625497</v>
+        <v>1.530592983910757</v>
       </c>
       <c r="DA187" s="32">
-        <v>1.6696869738130486</v>
+        <v>1.6739075855519421</v>
       </c>
       <c r="DB187" s="8"/>
       <c r="DC187" s="8"/>
@@ -40053,28 +40055,28 @@
         <v>10.93672342165039</v>
       </c>
       <c r="CT188" s="32">
-        <v>12.258635756619379</v>
+        <v>12.257051658902309</v>
       </c>
       <c r="CU188" s="32">
-        <v>15.641805110328081</v>
+        <v>15.637467297299645</v>
       </c>
       <c r="CV188" s="32">
-        <v>12.299527725960951</v>
+        <v>12.299769612562832</v>
       </c>
       <c r="CW188" s="32">
-        <v>10.823872925820751</v>
+        <v>10.822733429117138</v>
       </c>
       <c r="CX188" s="32">
-        <v>11.894710755293913</v>
+        <v>11.894790623226733</v>
       </c>
       <c r="CY188" s="32">
-        <v>14.932512621656297</v>
+        <v>14.944315818842869</v>
       </c>
       <c r="CZ188" s="32">
-        <v>11.917568645625295</v>
+        <v>11.928811929183174</v>
       </c>
       <c r="DA188" s="32">
-        <v>10.426247017901893</v>
+        <v>10.440580907306169</v>
       </c>
       <c r="DB188" s="8"/>
       <c r="DC188" s="8"/>
@@ -40444,28 +40446,28 @@
         <v>2.6599604870289264</v>
       </c>
       <c r="CT189" s="32">
-        <v>2.4934602086541169</v>
+        <v>2.4892839529465771</v>
       </c>
       <c r="CU189" s="32">
-        <v>2.434908314936838</v>
+        <v>2.4339609678993481</v>
       </c>
       <c r="CV189" s="32">
-        <v>2.8512382930061557</v>
+        <v>2.8509436831367805</v>
       </c>
       <c r="CW189" s="32">
-        <v>2.6533792670594769</v>
+        <v>2.645533236199924</v>
       </c>
       <c r="CX189" s="32">
-        <v>2.3959928422125976</v>
+        <v>2.3951868814879242</v>
       </c>
       <c r="CY189" s="32">
-        <v>2.4157146196421557</v>
+        <v>2.4364812006088745</v>
       </c>
       <c r="CZ189" s="32">
-        <v>2.7193684747106825</v>
+        <v>2.735352175003031</v>
       </c>
       <c r="DA189" s="32">
-        <v>2.4881045215235114</v>
+        <v>2.4991936999721429</v>
       </c>
       <c r="DB189" s="8"/>
       <c r="DC189" s="8"/>
@@ -40835,28 +40837,28 @@
         <v>4.1262894607775698</v>
       </c>
       <c r="CT190" s="32">
-        <v>4.5351534742871786</v>
+        <v>4.524933657113694</v>
       </c>
       <c r="CU190" s="32">
-        <v>4.0234101070558328</v>
+        <v>4.0229686493789156</v>
       </c>
       <c r="CV190" s="32">
-        <v>5.8091823354360388</v>
+        <v>5.8163910652487498</v>
       </c>
       <c r="CW190" s="32">
-        <v>4.3904074420822194</v>
+        <v>4.4063419321228974</v>
       </c>
       <c r="CX190" s="32">
-        <v>4.7388312960226182</v>
+        <v>4.7426330046455192</v>
       </c>
       <c r="CY190" s="32">
-        <v>4.1955497375310866</v>
+        <v>4.1936097549845179</v>
       </c>
       <c r="CZ190" s="32">
-        <v>6.2116404525296005</v>
+        <v>6.2267324265511634</v>
       </c>
       <c r="DA190" s="32">
-        <v>4.5014554975083572</v>
+        <v>4.4857597563020342</v>
       </c>
       <c r="DB190" s="8"/>
       <c r="DC190" s="8"/>
@@ -41226,28 +41228,28 @@
         <v>7.5486792572813401</v>
       </c>
       <c r="CT191" s="32">
-        <v>9.9463569641964966</v>
+        <v>9.945071666087232</v>
       </c>
       <c r="CU191" s="32">
-        <v>9.2088479581205629</v>
+        <v>9.2062941441350379</v>
       </c>
       <c r="CV191" s="32">
-        <v>10.242806444794994</v>
+        <v>10.243007883232293</v>
       </c>
       <c r="CW191" s="32">
-        <v>7.9769212184268996</v>
+        <v>7.9721217295466866</v>
       </c>
       <c r="CX191" s="32">
-        <v>10.249831626072355</v>
+        <v>10.255018126130761</v>
       </c>
       <c r="CY191" s="32">
-        <v>9.7406655230706374</v>
+        <v>9.7493327022311327</v>
       </c>
       <c r="CZ191" s="32">
-        <v>10.293048036253643</v>
+        <v>10.250234226091916</v>
       </c>
       <c r="DA191" s="32">
-        <v>8.141805511161472</v>
+        <v>8.1432744910178165</v>
       </c>
       <c r="DB191" s="8"/>
       <c r="DC191" s="8"/>
@@ -41617,28 +41619,28 @@
         <v>3.078983982654778</v>
       </c>
       <c r="CT192" s="32">
-        <v>3.2780838724902965</v>
+        <v>3.2792061026563095</v>
       </c>
       <c r="CU192" s="32">
-        <v>3.7102284514250452</v>
+        <v>3.7149213141910136</v>
       </c>
       <c r="CV192" s="32">
-        <v>2.7161006156470973</v>
+        <v>2.7199464980233068</v>
       </c>
       <c r="CW192" s="32">
-        <v>3.051891236968173</v>
+        <v>3.0612521505965637</v>
       </c>
       <c r="CX192" s="32">
-        <v>3.2849155794150326</v>
+        <v>3.2912340706153396</v>
       </c>
       <c r="CY192" s="32">
-        <v>3.6936850767649085</v>
+        <v>3.6829275652356821</v>
       </c>
       <c r="CZ192" s="32">
-        <v>2.7199299887634085</v>
+        <v>2.7261616936136295</v>
       </c>
       <c r="DA192" s="32">
-        <v>3.0305989566801892</v>
+        <v>3.0543196119418572</v>
       </c>
       <c r="DB192" s="8"/>
       <c r="DC192" s="8"/>
@@ -42008,28 +42010,28 @@
         <v>1.922815500189377</v>
       </c>
       <c r="CT193" s="32">
-        <v>1.9590489985622244</v>
+        <v>1.958795844368898</v>
       </c>
       <c r="CU193" s="32">
-        <v>1.5110559429774044</v>
+        <v>1.5106368942736321</v>
       </c>
       <c r="CV193" s="32">
-        <v>1.5754890787031228</v>
+        <v>1.5755200627951982</v>
       </c>
       <c r="CW193" s="32">
-        <v>2.003429127337911</v>
+        <v>1.9940794019745762</v>
       </c>
       <c r="CX193" s="32">
-        <v>2.0313630586225027</v>
+        <v>2.0250328327421667</v>
       </c>
       <c r="CY193" s="32">
-        <v>1.521373141159847</v>
+        <v>1.5139946727792237</v>
       </c>
       <c r="CZ193" s="32">
-        <v>1.5533937104639557</v>
+        <v>1.555396959129586</v>
       </c>
       <c r="DA193" s="32">
-        <v>2.0455851820712261</v>
+        <v>2.0556348418543737</v>
       </c>
       <c r="DB193" s="8"/>
       <c r="DC193" s="8"/>
@@ -42399,28 +42401,28 @@
         <v>5.2250336709513103</v>
       </c>
       <c r="CT194" s="32">
-        <v>5.6910556274640287</v>
+        <v>5.7198408181955731</v>
       </c>
       <c r="CU194" s="32">
-        <v>5.0057497492738312</v>
+        <v>5.0208481830960672</v>
       </c>
       <c r="CV194" s="32">
-        <v>5.6969118022387537</v>
+        <v>5.7103902115546177</v>
       </c>
       <c r="CW194" s="32">
-        <v>5.2903809107924626</v>
+        <v>5.3204870228600587</v>
       </c>
       <c r="CX194" s="32">
-        <v>5.7657119125587517</v>
+        <v>5.7644825352687823</v>
       </c>
       <c r="CY194" s="32">
-        <v>5.2287041468245103</v>
+        <v>5.2351217686387459</v>
       </c>
       <c r="CZ194" s="32">
-        <v>5.8230849360501891</v>
+        <v>5.827024953951307</v>
       </c>
       <c r="DA194" s="32">
-        <v>5.4647902632055141</v>
+        <v>5.4668335274871662</v>
       </c>
       <c r="DB194" s="8"/>
       <c r="DC194" s="8"/>
@@ -42790,28 +42792,28 @@
         <v>8.3758626913134364</v>
       </c>
       <c r="CT195" s="32">
-        <v>10.177562915078173</v>
+        <v>10.176247739841777</v>
       </c>
       <c r="CU195" s="32">
-        <v>6.133006284694118</v>
+        <v>6.1328676945588603</v>
       </c>
       <c r="CV195" s="32">
-        <v>8.0064331306908141</v>
+        <v>8.0076454654092615</v>
       </c>
       <c r="CW195" s="32">
-        <v>8.4440857689036832</v>
+        <v>8.4734065551657682</v>
       </c>
       <c r="CX195" s="32">
-        <v>10.267354237059095</v>
+        <v>10.262206348428712</v>
       </c>
       <c r="CY195" s="32">
-        <v>6.2393324898409288</v>
+        <v>6.2473181506959019</v>
       </c>
       <c r="CZ195" s="32">
-        <v>8.0957625085366658</v>
+        <v>8.1031446176236663</v>
       </c>
       <c r="DA195" s="32">
-        <v>8.7486384583522003</v>
+        <v>8.7430583183304122</v>
       </c>
       <c r="DB195" s="8"/>
       <c r="DC195" s="8"/>
@@ -43181,28 +43183,28 @@
         <v>15.961293698666065</v>
       </c>
       <c r="CT196" s="32">
-        <v>14.104237800494298</v>
+        <v>14.096085919909948</v>
       </c>
       <c r="CU196" s="32">
-        <v>13.543469352432998</v>
+        <v>13.530781473277937</v>
       </c>
       <c r="CV196" s="32">
-        <v>15.231792475750566</v>
+        <v>15.220561432284077</v>
       </c>
       <c r="CW196" s="32">
-        <v>16.395212951409896</v>
+        <v>16.390904044656729</v>
       </c>
       <c r="CX196" s="32">
-        <v>13.97470436453907</v>
+        <v>13.961933609480806</v>
       </c>
       <c r="CY196" s="32">
-        <v>13.382347294069058</v>
+        <v>13.379429817355849</v>
       </c>
       <c r="CZ196" s="32">
-        <v>15.184469128244269</v>
+        <v>15.20773288486366</v>
       </c>
       <c r="DA196" s="32">
-        <v>16.423888248281518</v>
+        <v>16.421954920618724</v>
       </c>
       <c r="DB196" s="8"/>
       <c r="DC196" s="8"/>

--- a/Data/National Accounts/PSA-02HFCE_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-02HFCE_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109C37CB-0206-4D93-9F2F-F0CD23AD5279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E40A17C-6613-41F7-A73A-5E7AE0B57C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="HFCE" sheetId="2" r:id="rId1"/>
@@ -521,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="64">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -707,10 +707,13 @@
     <t>Percent Share, at Constant 2018 Prices</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1244,8 +1247,8 @@
     <col min="75" max="77" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="78" max="78" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="79" max="93" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="94" max="105" width="16.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="1"/>
+    <col min="94" max="106" width="16.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1436,6 +1439,9 @@
       <c r="CY9" s="23"/>
       <c r="CZ9" s="23"/>
       <c r="DA9" s="23"/>
+      <c r="DB9" s="23">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
@@ -1752,6 +1758,9 @@
       </c>
       <c r="DA10" s="24" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2073,7 +2082,9 @@
       <c r="DA12" s="25">
         <v>2257594.2514206418</v>
       </c>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="25">
+        <v>1778620.7258560532</v>
+      </c>
       <c r="DC12" s="8"/>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
@@ -2464,7 +2475,9 @@
       <c r="DA13" s="25">
         <v>120252.82278633314</v>
       </c>
-      <c r="DB13" s="8"/>
+      <c r="DB13" s="25">
+        <v>98345.741683448505</v>
+      </c>
       <c r="DC13" s="8"/>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
@@ -2855,7 +2868,9 @@
       <c r="DA14" s="25">
         <v>94741.452218738676</v>
       </c>
-      <c r="DB14" s="8"/>
+      <c r="DB14" s="25">
+        <v>75003.247061091388</v>
+      </c>
       <c r="DC14" s="8"/>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
@@ -3246,7 +3261,9 @@
       <c r="DA15" s="25">
         <v>631565.8971390489</v>
       </c>
-      <c r="DB15" s="8"/>
+      <c r="DB15" s="25">
+        <v>597623.12105468463</v>
+      </c>
       <c r="DC15" s="8"/>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
@@ -3637,7 +3654,9 @@
       <c r="DA16" s="25">
         <v>147486.66570831661</v>
       </c>
-      <c r="DB16" s="8"/>
+      <c r="DB16" s="25">
+        <v>129497.11240136674</v>
+      </c>
       <c r="DC16" s="8"/>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
@@ -4028,7 +4047,9 @@
       <c r="DA17" s="25">
         <v>269475.82895237411</v>
       </c>
-      <c r="DB17" s="8"/>
+      <c r="DB17" s="25">
+        <v>250472.03487425239</v>
+      </c>
       <c r="DC17" s="8"/>
       <c r="DD17" s="8"/>
       <c r="DE17" s="8"/>
@@ -4419,7 +4440,9 @@
       <c r="DA18" s="25">
         <v>496667.21270987199</v>
       </c>
-      <c r="DB18" s="8"/>
+      <c r="DB18" s="25">
+        <v>595479.16807577095</v>
+      </c>
       <c r="DC18" s="8"/>
       <c r="DD18" s="8"/>
       <c r="DE18" s="8"/>
@@ -4810,7 +4833,9 @@
       <c r="DA19" s="25">
         <v>145667.37342405706</v>
       </c>
-      <c r="DB19" s="8"/>
+      <c r="DB19" s="25">
+        <v>151721.68295889723</v>
+      </c>
       <c r="DC19" s="8"/>
       <c r="DD19" s="8"/>
       <c r="DE19" s="8"/>
@@ -5201,7 +5226,9 @@
       <c r="DA20" s="25">
         <v>116085.0135024778</v>
       </c>
-      <c r="DB20" s="8"/>
+      <c r="DB20" s="25">
+        <v>104579.21517266936</v>
+      </c>
       <c r="DC20" s="8"/>
       <c r="DD20" s="8"/>
       <c r="DE20" s="8"/>
@@ -5592,7 +5619,9 @@
       <c r="DA21" s="25">
         <v>300009.49537248426</v>
       </c>
-      <c r="DB21" s="8"/>
+      <c r="DB21" s="25">
+        <v>301333.79849671648</v>
+      </c>
       <c r="DC21" s="8"/>
       <c r="DD21" s="8"/>
       <c r="DE21" s="8"/>
@@ -5983,7 +6012,9 @@
       <c r="DA22" s="25">
         <v>550139.20937379065</v>
       </c>
-      <c r="DB22" s="8"/>
+      <c r="DB22" s="25">
+        <v>591401.75434679841</v>
+      </c>
       <c r="DC22" s="8"/>
       <c r="DD22" s="8"/>
       <c r="DE22" s="8"/>
@@ -6374,7 +6405,9 @@
       <c r="DA23" s="25">
         <v>913942.70429242158</v>
       </c>
-      <c r="DB23" s="8"/>
+      <c r="DB23" s="25">
+        <v>778827.55687577662</v>
+      </c>
       <c r="DC23" s="8"/>
       <c r="DD23" s="8"/>
       <c r="DE23" s="8"/>
@@ -6554,7 +6587,7 @@
       <c r="CY24" s="26"/>
       <c r="CZ24" s="26"/>
       <c r="DA24" s="26"/>
-      <c r="DB24" s="8"/>
+      <c r="DB24" s="26"/>
       <c r="DC24" s="8"/>
       <c r="DD24" s="8"/>
       <c r="DE24" s="8"/>
@@ -6945,7 +6978,9 @@
       <c r="DA25" s="10">
         <v>6043627.9269005563</v>
       </c>
-      <c r="DB25" s="8"/>
+      <c r="DB25" s="10">
+        <v>5452905.1588575263</v>
+      </c>
       <c r="DC25" s="8"/>
       <c r="DD25" s="8"/>
       <c r="DE25" s="8"/>
@@ -7126,6 +7161,7 @@
       <c r="CY26" s="27"/>
       <c r="CZ26" s="27"/>
       <c r="DA26" s="27"/>
+      <c r="DB26" s="27"/>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
@@ -7237,7 +7273,7 @@
       <c r="CY28" s="15"/>
       <c r="CZ28" s="15"/>
       <c r="DA28" s="15"/>
-      <c r="DB28" s="8"/>
+      <c r="DB28" s="15"/>
       <c r="DC28" s="8"/>
       <c r="DD28" s="8"/>
       <c r="DE28" s="8"/>
@@ -7417,7 +7453,7 @@
       <c r="CY29" s="17"/>
       <c r="CZ29" s="17"/>
       <c r="DA29" s="17"/>
-      <c r="DB29" s="8"/>
+      <c r="DB29" s="17"/>
       <c r="DC29" s="8"/>
       <c r="DD29" s="8"/>
       <c r="DE29" s="8"/>
@@ -7680,6 +7716,9 @@
       <c r="CY38" s="23"/>
       <c r="CZ38" s="23"/>
       <c r="DA38" s="23"/>
+      <c r="DB38" s="23">
+        <v>2026</v>
+      </c>
     </row>
     <row r="39" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
@@ -7996,6 +8035,9 @@
       </c>
       <c r="DA39" s="24" t="s">
         <v>5</v>
+      </c>
+      <c r="DB39" s="24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -8317,7 +8359,9 @@
       <c r="DA41" s="25">
         <v>1712013.4937564556</v>
       </c>
-      <c r="DB41" s="18"/>
+      <c r="DB41" s="25">
+        <v>1336154.8218690488</v>
+      </c>
       <c r="DC41" s="18"/>
       <c r="DD41" s="18"/>
       <c r="DE41" s="8"/>
@@ -8708,7 +8752,9 @@
       <c r="DA42" s="25">
         <v>66940.263586569476</v>
       </c>
-      <c r="DB42" s="18"/>
+      <c r="DB42" s="25">
+        <v>54688.87528240637</v>
+      </c>
       <c r="DC42" s="18"/>
       <c r="DD42" s="18"/>
       <c r="DE42" s="8"/>
@@ -9099,7 +9145,9 @@
       <c r="DA43" s="25">
         <v>80447.531696095204</v>
       </c>
-      <c r="DB43" s="18"/>
+      <c r="DB43" s="25">
+        <v>62434.382449917008</v>
+      </c>
       <c r="DC43" s="18"/>
       <c r="DD43" s="18"/>
       <c r="DE43" s="8"/>
@@ -9490,7 +9538,9 @@
       <c r="DA44" s="25">
         <v>501771.40644787182</v>
       </c>
-      <c r="DB44" s="18"/>
+      <c r="DB44" s="25">
+        <v>497262.88891400094</v>
+      </c>
       <c r="DC44" s="18"/>
       <c r="DD44" s="18"/>
       <c r="DE44" s="8"/>
@@ -9881,7 +9931,9 @@
       <c r="DA45" s="25">
         <v>120110.55217656854</v>
       </c>
-      <c r="DB45" s="18"/>
+      <c r="DB45" s="25">
+        <v>100491.98654809655</v>
+      </c>
       <c r="DC45" s="18"/>
       <c r="DD45" s="18"/>
       <c r="DE45" s="8"/>
@@ -10272,7 +10324,9 @@
       <c r="DA46" s="25">
         <v>215584.36277543131</v>
       </c>
-      <c r="DB46" s="18"/>
+      <c r="DB46" s="25">
+        <v>204006.31705912558</v>
+      </c>
       <c r="DC46" s="18"/>
       <c r="DD46" s="18"/>
       <c r="DE46" s="8"/>
@@ -10663,7 +10717,9 @@
       <c r="DA47" s="25">
         <v>391363.50081725052</v>
       </c>
-      <c r="DB47" s="18"/>
+      <c r="DB47" s="25">
+        <v>432120.48511203448</v>
+      </c>
       <c r="DC47" s="18"/>
       <c r="DD47" s="18"/>
       <c r="DE47" s="8"/>
@@ -11054,7 +11110,9 @@
       <c r="DA48" s="25">
         <v>146789.74867700256</v>
       </c>
-      <c r="DB48" s="18"/>
+      <c r="DB48" s="25">
+        <v>141552.55683161606</v>
+      </c>
       <c r="DC48" s="18"/>
       <c r="DD48" s="18"/>
       <c r="DE48" s="8"/>
@@ -11445,7 +11503,9 @@
       <c r="DA49" s="25">
         <v>98793.237167360829</v>
       </c>
-      <c r="DB49" s="18"/>
+      <c r="DB49" s="25">
+        <v>86892.299465529941</v>
+      </c>
       <c r="DC49" s="18"/>
       <c r="DD49" s="18"/>
       <c r="DE49" s="8"/>
@@ -11836,7 +11896,9 @@
       <c r="DA50" s="25">
         <v>262734.49458966724</v>
       </c>
-      <c r="DB50" s="18"/>
+      <c r="DB50" s="25">
+        <v>250320.96917270299</v>
+      </c>
       <c r="DC50" s="18"/>
       <c r="DD50" s="18"/>
       <c r="DE50" s="8"/>
@@ -12227,7 +12289,9 @@
       <c r="DA51" s="25">
         <v>420188.94427363185</v>
       </c>
-      <c r="DB51" s="18"/>
+      <c r="DB51" s="25">
+        <v>435387.79461113992</v>
+      </c>
       <c r="DC51" s="18"/>
       <c r="DD51" s="18"/>
       <c r="DE51" s="8"/>
@@ -12618,7 +12682,9 @@
       <c r="DA52" s="25">
         <v>789234.57327706018</v>
       </c>
-      <c r="DB52" s="18"/>
+      <c r="DB52" s="25">
+        <v>591202.12934509362</v>
+      </c>
       <c r="DC52" s="18"/>
       <c r="DD52" s="18"/>
       <c r="DE52" s="8"/>
@@ -12798,7 +12864,7 @@
       <c r="CY53" s="26"/>
       <c r="CZ53" s="26"/>
       <c r="DA53" s="26"/>
-      <c r="DB53" s="8"/>
+      <c r="DB53" s="26"/>
       <c r="DC53" s="8"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
@@ -13189,7 +13255,9 @@
       <c r="DA54" s="10">
         <v>4805972.1092409659</v>
       </c>
-      <c r="DB54" s="8"/>
+      <c r="DB54" s="10">
+        <v>4192515.5066607129</v>
+      </c>
       <c r="DC54" s="8"/>
       <c r="DD54" s="8"/>
       <c r="DE54" s="8"/>
@@ -13370,6 +13438,7 @@
       <c r="CY55" s="27"/>
       <c r="CZ55" s="27"/>
       <c r="DA55" s="27"/>
+      <c r="DB55" s="27"/>
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
@@ -13481,7 +13550,7 @@
       <c r="CY57" s="26"/>
       <c r="CZ57" s="26"/>
       <c r="DA57" s="26"/>
-      <c r="DB57" s="8"/>
+      <c r="DB57" s="26"/>
       <c r="DC57" s="8"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
@@ -13661,7 +13730,7 @@
       <c r="CY58" s="17"/>
       <c r="CZ58" s="17"/>
       <c r="DA58" s="17"/>
-      <c r="DB58" s="8"/>
+      <c r="DB58" s="17"/>
       <c r="DC58" s="8"/>
       <c r="DD58" s="8"/>
       <c r="DE58" s="8"/>
@@ -13757,6 +13826,7 @@
       <c r="CY61" s="28"/>
       <c r="CZ61" s="28"/>
       <c r="DA61" s="28"/>
+      <c r="DB61" s="28"/>
     </row>
     <row r="62" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT62" s="28"/>
@@ -13766,6 +13836,7 @@
       <c r="CY62" s="28"/>
       <c r="CZ62" s="28"/>
       <c r="DA62" s="28"/>
+      <c r="DB62" s="28"/>
     </row>
     <row r="63" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
@@ -13778,6 +13849,7 @@
       <c r="CY63" s="28"/>
       <c r="CZ63" s="28"/>
       <c r="DA63" s="28"/>
+      <c r="DB63" s="28"/>
     </row>
     <row r="64" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
@@ -13787,6 +13859,7 @@
       <c r="CY64" s="28"/>
       <c r="CZ64" s="28"/>
       <c r="DA64" s="28"/>
+      <c r="DB64" s="28"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
@@ -13796,12 +13869,13 @@
       <c r="CY65" s="29"/>
       <c r="CZ65" s="29"/>
       <c r="DA65" s="29"/>
+      <c r="DB65" s="29"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX66" s="29"/>
       <c r="CY66" s="29"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
+      <c r="DB66" s="29"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
@@ -13955,10 +14029,13 @@
       <c r="CU67" s="23"/>
       <c r="CV67" s="23"/>
       <c r="CW67" s="23"/>
-      <c r="CX67" s="30"/>
+      <c r="CX67" s="23" t="s">
+        <v>63</v>
+      </c>
       <c r="CY67" s="30"/>
       <c r="CZ67" s="30"/>
       <c r="DA67" s="30"/>
+      <c r="DB67" s="30"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
@@ -14264,17 +14341,20 @@
       <c r="CW68" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="CX68" s="31"/>
+      <c r="CX68" s="24" t="s">
+        <v>2</v>
+      </c>
       <c r="CY68" s="31"/>
       <c r="CZ68" s="31"/>
       <c r="DA68" s="31"/>
+      <c r="DB68" s="31"/>
     </row>
     <row r="69" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
-      <c r="CX69" s="29"/>
       <c r="CY69" s="29"/>
       <c r="CZ69" s="29"/>
       <c r="DA69" s="29"/>
+      <c r="DB69" s="29"/>
     </row>
     <row r="70" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
@@ -14580,11 +14660,13 @@
       <c r="CW70" s="32">
         <v>4.5040021672833319</v>
       </c>
-      <c r="CX70" s="33"/>
+      <c r="CX70" s="32">
+        <v>2.2521765703352798</v>
+      </c>
       <c r="CY70" s="33"/>
       <c r="CZ70" s="33"/>
       <c r="DA70" s="33"/>
-      <c r="DB70" s="8"/>
+      <c r="DB70" s="33"/>
       <c r="DC70" s="8"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
@@ -14959,11 +15041,13 @@
       <c r="CW71" s="32">
         <v>-2.6867580532877611</v>
       </c>
-      <c r="CX71" s="33"/>
+      <c r="CX71" s="32">
+        <v>6.4741941354012198</v>
+      </c>
       <c r="CY71" s="33"/>
       <c r="CZ71" s="33"/>
       <c r="DA71" s="33"/>
-      <c r="DB71" s="8"/>
+      <c r="DB71" s="33"/>
       <c r="DC71" s="8"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
@@ -15338,11 +15422,13 @@
       <c r="CW72" s="32">
         <v>0.85425742935640869</v>
       </c>
-      <c r="CX72" s="33"/>
+      <c r="CX72" s="32">
+        <v>15.005754421105095</v>
+      </c>
       <c r="CY72" s="33"/>
       <c r="CZ72" s="33"/>
       <c r="DA72" s="33"/>
-      <c r="DB72" s="8"/>
+      <c r="DB72" s="33"/>
       <c r="DC72" s="8"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
@@ -15717,11 +15803,13 @@
       <c r="CW73" s="32">
         <v>2.8177282016049929</v>
       </c>
-      <c r="CX73" s="33"/>
+      <c r="CX73" s="32">
+        <v>6.6055781133850644</v>
+      </c>
       <c r="CY73" s="33"/>
       <c r="CZ73" s="33"/>
       <c r="DA73" s="33"/>
-      <c r="DB73" s="8"/>
+      <c r="DB73" s="33"/>
       <c r="DC73" s="8"/>
       <c r="DD73" s="8"/>
       <c r="DE73" s="8"/>
@@ -16096,11 +16184,13 @@
       <c r="CW74" s="32">
         <v>6.2002573040501829E-2</v>
       </c>
-      <c r="CX74" s="33"/>
+      <c r="CX74" s="32">
+        <v>5.9292585985969453</v>
+      </c>
       <c r="CY74" s="33"/>
       <c r="CZ74" s="33"/>
       <c r="DA74" s="33"/>
-      <c r="DB74" s="8"/>
+      <c r="DB74" s="33"/>
       <c r="DC74" s="8"/>
       <c r="DD74" s="8"/>
       <c r="DE74" s="8"/>
@@ -16475,11 +16565,13 @@
       <c r="CW75" s="32">
         <v>8.517487380089122</v>
       </c>
-      <c r="CX75" s="33"/>
+      <c r="CX75" s="32">
+        <v>9.0823825021554256</v>
+      </c>
       <c r="CY75" s="33"/>
       <c r="CZ75" s="33"/>
       <c r="DA75" s="33"/>
-      <c r="DB75" s="8"/>
+      <c r="DB75" s="33"/>
       <c r="DC75" s="8"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
@@ -16854,11 +16946,13 @@
       <c r="CW76" s="32">
         <v>7.0480931519140881</v>
       </c>
-      <c r="CX76" s="33"/>
+      <c r="CX76" s="32">
+        <v>6.748168166432734</v>
+      </c>
       <c r="CY76" s="33"/>
       <c r="CZ76" s="33"/>
       <c r="DA76" s="33"/>
-      <c r="DB76" s="8"/>
+      <c r="DB76" s="33"/>
       <c r="DC76" s="8"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
@@ -17233,11 +17327,13 @@
       <c r="CW77" s="32">
         <v>4.245173815947993</v>
       </c>
-      <c r="CX77" s="33"/>
+      <c r="CX77" s="32">
+        <v>6.4283724753448723</v>
+      </c>
       <c r="CY77" s="33"/>
       <c r="CZ77" s="33"/>
       <c r="DA77" s="33"/>
-      <c r="DB77" s="8"/>
+      <c r="DB77" s="33"/>
       <c r="DC77" s="8"/>
       <c r="DD77" s="8"/>
       <c r="DE77" s="8"/>
@@ -17612,11 +17708,13 @@
       <c r="CW78" s="32">
         <v>9.0856460685615872</v>
       </c>
-      <c r="CX78" s="33"/>
+      <c r="CX78" s="32">
+        <v>9.4690483265493128</v>
+      </c>
       <c r="CY78" s="33"/>
       <c r="CZ78" s="33"/>
       <c r="DA78" s="33"/>
-      <c r="DB78" s="8"/>
+      <c r="DB78" s="33"/>
       <c r="DC78" s="8"/>
       <c r="DD78" s="8"/>
       <c r="DE78" s="8"/>
@@ -17991,11 +18089,13 @@
       <c r="CW79" s="32">
         <v>9.8287101496879643</v>
       </c>
-      <c r="CX79" s="33"/>
+      <c r="CX79" s="32">
+        <v>9.8047587741586</v>
+      </c>
       <c r="CY79" s="33"/>
       <c r="CZ79" s="33"/>
       <c r="DA79" s="33"/>
-      <c r="DB79" s="8"/>
+      <c r="DB79" s="33"/>
       <c r="DC79" s="8"/>
       <c r="DD79" s="8"/>
       <c r="DE79" s="8"/>
@@ -18370,11 +18470,13 @@
       <c r="CW80" s="32">
         <v>9.7353051485010553</v>
       </c>
-      <c r="CX80" s="33"/>
+      <c r="CX80" s="32">
+        <v>8.8971241917830781</v>
+      </c>
       <c r="CY80" s="33"/>
       <c r="CZ80" s="33"/>
       <c r="DA80" s="33"/>
-      <c r="DB80" s="8"/>
+      <c r="DB80" s="33"/>
       <c r="DC80" s="8"/>
       <c r="DD80" s="8"/>
       <c r="DE80" s="8"/>
@@ -18749,11 +18851,13 @@
       <c r="CW81" s="32">
         <v>6.4151687512959938</v>
       </c>
-      <c r="CX81" s="33"/>
+      <c r="CX81" s="32">
+        <v>6.8926099203904272</v>
+      </c>
       <c r="CY81" s="33"/>
       <c r="CZ81" s="33"/>
       <c r="DA81" s="33"/>
-      <c r="DB81" s="8"/>
+      <c r="DB81" s="33"/>
       <c r="DC81" s="8"/>
       <c r="DD81" s="8"/>
       <c r="DE81" s="8"/>
@@ -18925,11 +19029,11 @@
       <c r="CU82" s="26"/>
       <c r="CV82" s="26"/>
       <c r="CW82" s="26"/>
-      <c r="CX82" s="34"/>
+      <c r="CX82" s="26"/>
       <c r="CY82" s="34"/>
       <c r="CZ82" s="34"/>
       <c r="DA82" s="34"/>
-      <c r="DB82" s="8"/>
+      <c r="DB82" s="34"/>
       <c r="DC82" s="8"/>
       <c r="DD82" s="8"/>
       <c r="DE82" s="8"/>
@@ -19304,11 +19408,13 @@
       <c r="CW83" s="32">
         <v>5.4505627561364491</v>
       </c>
-      <c r="CX83" s="33"/>
+      <c r="CX83" s="32">
+        <v>5.8501992776329246</v>
+      </c>
       <c r="CY83" s="33"/>
       <c r="CZ83" s="33"/>
       <c r="DA83" s="33"/>
-      <c r="DB83" s="8"/>
+      <c r="DB83" s="33"/>
       <c r="DC83" s="8"/>
       <c r="DD83" s="8"/>
       <c r="DE83" s="8"/>
@@ -19481,19 +19587,20 @@
       <c r="CU84" s="27"/>
       <c r="CV84" s="27"/>
       <c r="CW84" s="27"/>
-      <c r="CX84" s="31"/>
+      <c r="CX84" s="27"/>
       <c r="CY84" s="31"/>
       <c r="CZ84" s="31"/>
       <c r="DA84" s="31"/>
+      <c r="DB84" s="31"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="CX85" s="29"/>
       <c r="CY85" s="29"/>
       <c r="CZ85" s="29"/>
       <c r="DA85" s="29"/>
+      <c r="DB85" s="29"/>
     </row>
     <row r="86" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="8"/>
@@ -19596,11 +19703,11 @@
       <c r="CU86" s="26"/>
       <c r="CV86" s="26"/>
       <c r="CW86" s="26"/>
-      <c r="CX86" s="34"/>
+      <c r="CX86" s="26"/>
       <c r="CY86" s="34"/>
       <c r="CZ86" s="34"/>
       <c r="DA86" s="34"/>
-      <c r="DB86" s="8"/>
+      <c r="DB86" s="34"/>
       <c r="DC86" s="8"/>
       <c r="DD86" s="8"/>
       <c r="DE86" s="8"/>
@@ -19772,11 +19879,11 @@
       <c r="CU87" s="26"/>
       <c r="CV87" s="26"/>
       <c r="CW87" s="26"/>
-      <c r="CX87" s="34"/>
+      <c r="CX87" s="26"/>
       <c r="CY87" s="34"/>
       <c r="CZ87" s="34"/>
       <c r="DA87" s="34"/>
-      <c r="DB87" s="8"/>
+      <c r="DB87" s="34"/>
       <c r="DC87" s="8"/>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
@@ -19851,67 +19958,67 @@
       <c r="A88" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CX88" s="29"/>
       <c r="CY88" s="29"/>
       <c r="CZ88" s="29"/>
       <c r="DA88" s="29"/>
+      <c r="DB88" s="29"/>
     </row>
     <row r="89" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CX89" s="29"/>
       <c r="CY89" s="29"/>
       <c r="CZ89" s="29"/>
       <c r="DA89" s="29"/>
+      <c r="DB89" s="29"/>
     </row>
     <row r="90" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CX90" s="29"/>
       <c r="CY90" s="29"/>
       <c r="CZ90" s="29"/>
       <c r="DA90" s="29"/>
+      <c r="DB90" s="29"/>
     </row>
     <row r="91" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX91" s="29"/>
       <c r="CY91" s="29"/>
       <c r="CZ91" s="29"/>
       <c r="DA91" s="29"/>
+      <c r="DB91" s="29"/>
     </row>
     <row r="92" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CX92" s="29"/>
       <c r="CY92" s="29"/>
       <c r="CZ92" s="29"/>
       <c r="DA92" s="29"/>
+      <c r="DB92" s="29"/>
     </row>
     <row r="93" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CX93" s="29"/>
       <c r="CY93" s="29"/>
       <c r="CZ93" s="29"/>
       <c r="DA93" s="29"/>
+      <c r="DB93" s="29"/>
     </row>
     <row r="94" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CX94" s="29"/>
       <c r="CY94" s="29"/>
       <c r="CZ94" s="29"/>
       <c r="DA94" s="29"/>
+      <c r="DB94" s="29"/>
     </row>
     <row r="95" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX95" s="29"/>
       <c r="CY95" s="29"/>
       <c r="CZ95" s="29"/>
       <c r="DA95" s="29"/>
+      <c r="DB95" s="29"/>
     </row>
     <row r="96" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
@@ -20065,10 +20172,13 @@
       <c r="CU96" s="23"/>
       <c r="CV96" s="23"/>
       <c r="CW96" s="23"/>
-      <c r="CX96" s="30"/>
+      <c r="CX96" s="23" t="s">
+        <v>63</v>
+      </c>
       <c r="CY96" s="30"/>
       <c r="CZ96" s="30"/>
       <c r="DA96" s="30"/>
+      <c r="DB96" s="30"/>
     </row>
     <row r="97" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
@@ -20374,17 +20484,20 @@
       <c r="CW97" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="CX97" s="31"/>
+      <c r="CX97" s="24" t="s">
+        <v>2</v>
+      </c>
       <c r="CY97" s="31"/>
       <c r="CZ97" s="31"/>
       <c r="DA97" s="31"/>
+      <c r="DB97" s="31"/>
     </row>
     <row r="98" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
-      <c r="CX98" s="29"/>
       <c r="CY98" s="29"/>
       <c r="CZ98" s="29"/>
       <c r="DA98" s="29"/>
+      <c r="DB98" s="29"/>
     </row>
     <row r="99" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
@@ -20690,11 +20803,13 @@
       <c r="CW99" s="32">
         <v>3.7927321752196548</v>
       </c>
-      <c r="CX99" s="33"/>
+      <c r="CX99" s="32">
+        <v>0.28772588745691507</v>
+      </c>
       <c r="CY99" s="33"/>
       <c r="CZ99" s="33"/>
       <c r="DA99" s="33"/>
-      <c r="DB99" s="8"/>
+      <c r="DB99" s="33"/>
       <c r="DC99" s="8"/>
       <c r="DD99" s="8"/>
       <c r="DE99" s="8"/>
@@ -21069,11 +21184,13 @@
       <c r="CW100" s="32">
         <v>-6.1365886567613046</v>
       </c>
-      <c r="CX100" s="33"/>
+      <c r="CX100" s="32">
+        <v>3.0541712181860277</v>
+      </c>
       <c r="CY100" s="33"/>
       <c r="CZ100" s="33"/>
       <c r="DA100" s="33"/>
-      <c r="DB100" s="8"/>
+      <c r="DB100" s="33"/>
       <c r="DC100" s="8"/>
       <c r="DD100" s="8"/>
       <c r="DE100" s="8"/>
@@ -21448,11 +21565,13 @@
       <c r="CW101" s="32">
         <v>-1.0533477687317543</v>
       </c>
-      <c r="CX101" s="33"/>
+      <c r="CX101" s="32">
+        <v>12.25860284969977</v>
+      </c>
       <c r="CY101" s="33"/>
       <c r="CZ101" s="33"/>
       <c r="DA101" s="33"/>
-      <c r="DB101" s="8"/>
+      <c r="DB101" s="33"/>
       <c r="DC101" s="8"/>
       <c r="DD101" s="8"/>
       <c r="DE101" s="8"/>
@@ -21827,11 +21946,13 @@
       <c r="CW102" s="32">
         <v>0.11345086296911688</v>
       </c>
-      <c r="CX102" s="33"/>
+      <c r="CX102" s="32">
+        <v>2.7208224282392734</v>
+      </c>
       <c r="CY102" s="33"/>
       <c r="CZ102" s="33"/>
       <c r="DA102" s="33"/>
-      <c r="DB102" s="8"/>
+      <c r="DB102" s="33"/>
       <c r="DC102" s="8"/>
       <c r="DD102" s="8"/>
       <c r="DE102" s="8"/>
@@ -22206,11 +22327,13 @@
       <c r="CW103" s="32">
         <v>-1.9626811850934303</v>
       </c>
-      <c r="CX103" s="33"/>
+      <c r="CX103" s="32">
+        <v>3.0911224344107495</v>
+      </c>
       <c r="CY103" s="33"/>
       <c r="CZ103" s="33"/>
       <c r="DA103" s="33"/>
-      <c r="DB103" s="8"/>
+      <c r="DB103" s="33"/>
       <c r="DC103" s="8"/>
       <c r="DD103" s="8"/>
       <c r="DE103" s="8"/>
@@ -22585,11 +22708,13 @@
       <c r="CW104" s="32">
         <v>5.6483077399349497</v>
       </c>
-      <c r="CX104" s="33"/>
+      <c r="CX104" s="32">
+        <v>5.6947308716537322</v>
+      </c>
       <c r="CY104" s="33"/>
       <c r="CZ104" s="33"/>
       <c r="DA104" s="33"/>
-      <c r="DB104" s="8"/>
+      <c r="DB104" s="33"/>
       <c r="DC104" s="8"/>
       <c r="DD104" s="8"/>
       <c r="DE104" s="8"/>
@@ -22964,11 +23089,13 @@
       <c r="CW105" s="32">
         <v>6.0058621655516049</v>
       </c>
-      <c r="CX105" s="33"/>
+      <c r="CX105" s="32">
+        <v>3.5374974360975955</v>
+      </c>
       <c r="CY105" s="33"/>
       <c r="CZ105" s="33"/>
       <c r="DA105" s="33"/>
-      <c r="DB105" s="8"/>
+      <c r="DB105" s="33"/>
       <c r="DC105" s="8"/>
       <c r="DD105" s="8"/>
       <c r="DE105" s="8"/>
@@ -23343,11 +23470,13 @@
       <c r="CW106" s="32">
         <v>3.5428482945700779</v>
       </c>
-      <c r="CX106" s="33"/>
+      <c r="CX106" s="32">
+        <v>5.6788768945325927</v>
+      </c>
       <c r="CY106" s="33"/>
       <c r="CZ106" s="33"/>
       <c r="DA106" s="33"/>
-      <c r="DB106" s="8"/>
+      <c r="DB106" s="33"/>
       <c r="DC106" s="8"/>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
@@ -23722,11 +23851,13 @@
       <c r="CW107" s="32">
         <v>6.9813940197132212</v>
       </c>
-      <c r="CX107" s="33"/>
+      <c r="CX107" s="32">
+        <v>5.4334607994919395</v>
+      </c>
       <c r="CY107" s="33"/>
       <c r="CZ107" s="33"/>
       <c r="DA107" s="33"/>
-      <c r="DB107" s="8"/>
+      <c r="DB107" s="33"/>
       <c r="DC107" s="8"/>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
@@ -24101,11 +24232,13 @@
       <c r="CW108" s="32">
         <v>6.6324016893898374</v>
       </c>
-      <c r="CX108" s="33"/>
+      <c r="CX108" s="32">
+        <v>6.7004239138229451</v>
+      </c>
       <c r="CY108" s="33"/>
       <c r="CZ108" s="33"/>
       <c r="DA108" s="33"/>
-      <c r="DB108" s="8"/>
+      <c r="DB108" s="33"/>
       <c r="DC108" s="8"/>
       <c r="DD108" s="8"/>
       <c r="DE108" s="8"/>
@@ -24480,11 +24613,13 @@
       <c r="CW109" s="32">
         <v>7.0804187336179751</v>
       </c>
-      <c r="CX109" s="33"/>
+      <c r="CX109" s="32">
+        <v>4.2472837968456076</v>
+      </c>
       <c r="CY109" s="33"/>
       <c r="CZ109" s="33"/>
       <c r="DA109" s="33"/>
-      <c r="DB109" s="8"/>
+      <c r="DB109" s="33"/>
       <c r="DC109" s="8"/>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
@@ -24859,11 +24994,13 @@
       <c r="CW110" s="32">
         <v>3.9744610163546525</v>
       </c>
-      <c r="CX110" s="33"/>
+      <c r="CX110" s="32">
+        <v>4.0446280596069926</v>
+      </c>
       <c r="CY110" s="33"/>
       <c r="CZ110" s="33"/>
       <c r="DA110" s="33"/>
-      <c r="DB110" s="8"/>
+      <c r="DB110" s="33"/>
       <c r="DC110" s="8"/>
       <c r="DD110" s="8"/>
       <c r="DE110" s="8"/>
@@ -25035,11 +25172,11 @@
       <c r="CU111" s="26"/>
       <c r="CV111" s="26"/>
       <c r="CW111" s="26"/>
-      <c r="CX111" s="34"/>
+      <c r="CX111" s="26"/>
       <c r="CY111" s="34"/>
       <c r="CZ111" s="34"/>
       <c r="DA111" s="34"/>
-      <c r="DB111" s="8"/>
+      <c r="DB111" s="34"/>
       <c r="DC111" s="8"/>
       <c r="DD111" s="8"/>
       <c r="DE111" s="8"/>
@@ -25414,11 +25551,13 @@
       <c r="CW112" s="32">
         <v>3.7778645631406675</v>
       </c>
-      <c r="CX112" s="33"/>
+      <c r="CX112" s="32">
+        <v>3.0158187478206173</v>
+      </c>
       <c r="CY112" s="33"/>
       <c r="CZ112" s="33"/>
       <c r="DA112" s="33"/>
-      <c r="DB112" s="8"/>
+      <c r="DB112" s="33"/>
       <c r="DC112" s="8"/>
       <c r="DD112" s="8"/>
       <c r="DE112" s="8"/>
@@ -25591,19 +25730,20 @@
       <c r="CU113" s="27"/>
       <c r="CV113" s="27"/>
       <c r="CW113" s="27"/>
-      <c r="CX113" s="31"/>
+      <c r="CX113" s="27"/>
       <c r="CY113" s="31"/>
       <c r="CZ113" s="31"/>
       <c r="DA113" s="31"/>
+      <c r="DB113" s="31"/>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A114" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="CX114" s="29"/>
       <c r="CY114" s="29"/>
       <c r="CZ114" s="29"/>
       <c r="DA114" s="29"/>
+      <c r="DB114" s="29"/>
     </row>
     <row r="115" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="8"/>
@@ -25710,7 +25850,7 @@
       <c r="CY115" s="26"/>
       <c r="CZ115" s="35"/>
       <c r="DA115" s="35"/>
-      <c r="DB115" s="8"/>
+      <c r="DB115" s="26"/>
       <c r="DC115" s="8"/>
       <c r="DD115" s="8"/>
       <c r="DE115" s="8"/>
@@ -25886,7 +26026,7 @@
       <c r="CY116" s="26"/>
       <c r="CZ116" s="35"/>
       <c r="DA116" s="35"/>
-      <c r="DB116" s="8"/>
+      <c r="DB116" s="26"/>
       <c r="DC116" s="8"/>
       <c r="DD116" s="8"/>
       <c r="DE116" s="8"/>
@@ -26140,6 +26280,9 @@
       <c r="CY124" s="23"/>
       <c r="CZ124" s="23"/>
       <c r="DA124" s="23"/>
+      <c r="DB124" s="23">
+        <v>2026</v>
+      </c>
     </row>
     <row r="125" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
@@ -26456,6 +26599,9 @@
       </c>
       <c r="DA125" s="24" t="s">
         <v>5</v>
+      </c>
+      <c r="DB125" s="24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -26777,7 +26923,9 @@
       <c r="DA127" s="32">
         <v>131.86778373265545</v>
       </c>
-      <c r="DB127" s="8"/>
+      <c r="DB127" s="32">
+        <v>133.11486788395311</v>
+      </c>
       <c r="DC127" s="8"/>
       <c r="DD127" s="8"/>
       <c r="DE127" s="8"/>
@@ -27168,7 +27316,9 @@
       <c r="DA128" s="32">
         <v>179.64199174509974</v>
       </c>
-      <c r="DB128" s="8"/>
+      <c r="DB128" s="32">
+        <v>179.82769105344306</v>
+      </c>
       <c r="DC128" s="8"/>
       <c r="DD128" s="8"/>
       <c r="DE128" s="8"/>
@@ -27559,7 +27709,9 @@
       <c r="DA129" s="32">
         <v>117.76800384210829</v>
       </c>
-      <c r="DB129" s="8"/>
+      <c r="DB129" s="32">
+        <v>120.13131886305874</v>
+      </c>
       <c r="DC129" s="8"/>
       <c r="DD129" s="8"/>
       <c r="DE129" s="8"/>
@@ -27950,7 +28102,9 @@
       <c r="DA130" s="32">
         <v>125.86725529260727</v>
       </c>
-      <c r="DB130" s="8"/>
+      <c r="DB130" s="32">
+        <v>120.18253008179754</v>
+      </c>
       <c r="DC130" s="8"/>
       <c r="DD130" s="8"/>
       <c r="DE130" s="8"/>
@@ -28341,7 +28495,9 @@
       <c r="DA131" s="32">
         <v>122.79243000357187</v>
       </c>
-      <c r="DB131" s="8"/>
+      <c r="DB131" s="32">
+        <v>128.86312316991368</v>
+      </c>
       <c r="DC131" s="8"/>
       <c r="DD131" s="8"/>
       <c r="DE131" s="8"/>
@@ -28732,7 +28888,9 @@
       <c r="DA132" s="32">
         <v>124.99785489223083</v>
       </c>
-      <c r="DB132" s="8"/>
+      <c r="DB132" s="32">
+        <v>122.77660735459482</v>
+      </c>
       <c r="DC132" s="8"/>
       <c r="DD132" s="8"/>
       <c r="DE132" s="8"/>
@@ -29123,7 +29281,9 @@
       <c r="DA133" s="32">
         <v>126.90688111505668</v>
       </c>
-      <c r="DB133" s="8"/>
+      <c r="DB133" s="32">
+        <v>137.80396639177681</v>
+      </c>
       <c r="DC133" s="8"/>
       <c r="DD133" s="8"/>
       <c r="DE133" s="8"/>
@@ -29514,7 +29674,9 @@
       <c r="DA134" s="32">
         <v>99.235385806528512</v>
       </c>
-      <c r="DB134" s="8"/>
+      <c r="DB134" s="32">
+        <v>107.18399324950228</v>
+      </c>
       <c r="DC134" s="8"/>
       <c r="DD134" s="8"/>
       <c r="DE134" s="8"/>
@@ -29905,7 +30067,9 @@
       <c r="DA135" s="32">
         <v>117.50299598526549</v>
       </c>
-      <c r="DB135" s="8"/>
+      <c r="DB135" s="32">
+        <v>120.35498636349908</v>
+      </c>
       <c r="DC135" s="8"/>
       <c r="DD135" s="8"/>
       <c r="DE135" s="8"/>
@@ -30296,7 +30460,9 @@
       <c r="DA136" s="32">
         <v>114.18732657888424</v>
       </c>
-      <c r="DB136" s="8"/>
+      <c r="DB136" s="32">
+        <v>120.37896764805924</v>
+      </c>
       <c r="DC136" s="8"/>
       <c r="DD136" s="8"/>
       <c r="DE136" s="8"/>
@@ -30687,7 +30853,9 @@
       <c r="DA137" s="32">
         <v>130.926626431069</v>
       </c>
-      <c r="DB137" s="8"/>
+      <c r="DB137" s="32">
+        <v>135.83333333333334</v>
+      </c>
       <c r="DC137" s="8"/>
       <c r="DD137" s="8"/>
       <c r="DE137" s="8"/>
@@ -31078,7 +31246,9 @@
       <c r="DA138" s="32">
         <v>115.80114901676801</v>
       </c>
-      <c r="DB138" s="8"/>
+      <c r="DB138" s="32">
+        <v>131.73625706296522</v>
+      </c>
       <c r="DC138" s="8"/>
       <c r="DD138" s="8"/>
       <c r="DE138" s="8"/>
@@ -31258,7 +31428,7 @@
       <c r="CY139" s="26"/>
       <c r="CZ139" s="26"/>
       <c r="DA139" s="26"/>
-      <c r="DB139" s="8"/>
+      <c r="DB139" s="26"/>
       <c r="DC139" s="8"/>
       <c r="DD139" s="8"/>
       <c r="DE139" s="8"/>
@@ -31649,7 +31819,9 @@
       <c r="DA140" s="32">
         <v>125.75245526872317</v>
       </c>
-      <c r="DB140" s="8"/>
+      <c r="DB140" s="32">
+        <v>130.06285010024203</v>
+      </c>
       <c r="DC140" s="8"/>
       <c r="DD140" s="8"/>
       <c r="DE140" s="8"/>
@@ -31830,6 +32002,7 @@
       <c r="CY141" s="27"/>
       <c r="CZ141" s="27"/>
       <c r="DA141" s="27"/>
+      <c r="DB141" s="27"/>
     </row>
     <row r="142" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A142" s="12" t="s">
@@ -32024,6 +32197,9 @@
       <c r="CY153" s="23"/>
       <c r="CZ153" s="23"/>
       <c r="DA153" s="23"/>
+      <c r="DB153" s="23">
+        <v>2026</v>
+      </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
@@ -32340,6 +32516,9 @@
       </c>
       <c r="DA154" s="24" t="s">
         <v>5</v>
+      </c>
+      <c r="DB154" s="24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -32661,7 +32840,9 @@
       <c r="DA156" s="32">
         <v>37.35495101165894</v>
       </c>
-      <c r="DB156" s="8"/>
+      <c r="DB156" s="32">
+        <v>32.617855510780672</v>
+      </c>
       <c r="DC156" s="8"/>
       <c r="DD156" s="8"/>
       <c r="DE156" s="8"/>
@@ -33052,7 +33233,9 @@
       <c r="DA157" s="32">
         <v>1.9897456335966761</v>
       </c>
-      <c r="DB157" s="8"/>
+      <c r="DB157" s="32">
+        <v>1.8035476286195591</v>
+      </c>
       <c r="DC157" s="8"/>
       <c r="DD157" s="8"/>
       <c r="DE157" s="8"/>
@@ -33443,7 +33626,9 @@
       <c r="DA158" s="32">
         <v>1.5676254952267776</v>
       </c>
-      <c r="DB158" s="8"/>
+      <c r="DB158" s="32">
+        <v>1.3754731629479835</v>
+      </c>
       <c r="DC158" s="8"/>
       <c r="DD158" s="8"/>
       <c r="DE158" s="8"/>
@@ -33834,7 +34019,9 @@
       <c r="DA159" s="32">
         <v>10.450112164051506</v>
       </c>
-      <c r="DB159" s="8"/>
+      <c r="DB159" s="32">
+        <v>10.959719702513523</v>
+      </c>
       <c r="DC159" s="8"/>
       <c r="DD159" s="8"/>
       <c r="DE159" s="8"/>
@@ -34225,7 +34412,9 @@
       <c r="DA160" s="32">
         <v>2.4403664072674704</v>
       </c>
-      <c r="DB160" s="8"/>
+      <c r="DB160" s="32">
+        <v>2.3748278876814086</v>
+      </c>
       <c r="DC160" s="8"/>
       <c r="DD160" s="8"/>
       <c r="DE160" s="8"/>
@@ -34616,7 +34805,9 @@
       <c r="DA161" s="32">
         <v>4.4588421426957927</v>
       </c>
-      <c r="DB161" s="8"/>
+      <c r="DB161" s="32">
+        <v>4.5933686278660755</v>
+      </c>
       <c r="DC161" s="8"/>
       <c r="DD161" s="8"/>
       <c r="DE161" s="8"/>
@@ -35007,7 +35198,9 @@
       <c r="DA162" s="32">
         <v>8.2180309363383532</v>
       </c>
-      <c r="DB162" s="8"/>
+      <c r="DB162" s="32">
+        <v>10.920402074268493</v>
+      </c>
       <c r="DC162" s="8"/>
       <c r="DD162" s="8"/>
       <c r="DE162" s="8"/>
@@ -35398,7 +35591,9 @@
       <c r="DA163" s="32">
         <v>2.4102637552467896</v>
       </c>
-      <c r="DB163" s="8"/>
+      <c r="DB163" s="32">
+        <v>2.7824009136202443</v>
+      </c>
       <c r="DC163" s="8"/>
       <c r="DD163" s="8"/>
       <c r="DE163" s="8"/>
@@ -35789,7 +35984,9 @@
       <c r="DA164" s="32">
         <v>1.9207835906935355</v>
       </c>
-      <c r="DB164" s="8"/>
+      <c r="DB164" s="32">
+        <v>1.917862352745934</v>
+      </c>
       <c r="DC164" s="8"/>
       <c r="DD164" s="8"/>
       <c r="DE164" s="8"/>
@@ -36180,7 +36377,9 @@
       <c r="DA165" s="32">
         <v>4.9640629602150677</v>
       </c>
-      <c r="DB165" s="8"/>
+      <c r="DB165" s="32">
+        <v>5.5261147905211487</v>
+      </c>
       <c r="DC165" s="8"/>
       <c r="DD165" s="8"/>
       <c r="DE165" s="8"/>
@@ -36571,7 +36770,9 @@
       <c r="DA166" s="32">
         <v>9.1027974592063732</v>
       </c>
-      <c r="DB166" s="8"/>
+      <c r="DB166" s="32">
+        <v>10.845627002812328</v>
+      </c>
       <c r="DC166" s="8"/>
       <c r="DD166" s="8"/>
       <c r="DE166" s="8"/>
@@ -36962,7 +37163,9 @@
       <c r="DA167" s="32">
         <v>15.122418443802719</v>
       </c>
-      <c r="DB167" s="8"/>
+      <c r="DB167" s="32">
+        <v>14.282800345622624</v>
+      </c>
       <c r="DC167" s="8"/>
       <c r="DD167" s="8"/>
       <c r="DE167" s="8"/>
@@ -37142,7 +37345,7 @@
       <c r="CY168" s="26"/>
       <c r="CZ168" s="26"/>
       <c r="DA168" s="26"/>
-      <c r="DB168" s="8"/>
+      <c r="DB168" s="26"/>
       <c r="DC168" s="8"/>
       <c r="DD168" s="8"/>
       <c r="DE168" s="8"/>
@@ -37533,7 +37736,9 @@
       <c r="DA169" s="32">
         <v>100</v>
       </c>
-      <c r="DB169" s="8"/>
+      <c r="DB169" s="32">
+        <v>100</v>
+      </c>
       <c r="DC169" s="8"/>
       <c r="DD169" s="8"/>
       <c r="DE169" s="8"/>
@@ -37714,6 +37919,7 @@
       <c r="CY170" s="27"/>
       <c r="CZ170" s="27"/>
       <c r="DA170" s="27"/>
+      <c r="DB170" s="27"/>
     </row>
     <row r="171" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A171" s="12" t="s">
@@ -37825,7 +38031,7 @@
       <c r="CY172" s="26"/>
       <c r="CZ172" s="26"/>
       <c r="DA172" s="26"/>
-      <c r="DB172" s="8"/>
+      <c r="DB172" s="26"/>
       <c r="DC172" s="8"/>
       <c r="DD172" s="8"/>
       <c r="DE172" s="8"/>
@@ -38005,7 +38211,7 @@
       <c r="CY173" s="26"/>
       <c r="CZ173" s="26"/>
       <c r="DA173" s="26"/>
-      <c r="DB173" s="8"/>
+      <c r="DB173" s="26"/>
       <c r="DC173" s="8"/>
       <c r="DD173" s="8"/>
       <c r="DE173" s="8"/>
@@ -38268,6 +38474,9 @@
       <c r="CY182" s="23"/>
       <c r="CZ182" s="23"/>
       <c r="DA182" s="23"/>
+      <c r="DB182" s="23">
+        <v>2026</v>
+      </c>
     </row>
     <row r="183" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
@@ -38584,6 +38793,9 @@
       </c>
       <c r="DA183" s="24" t="s">
         <v>5</v>
+      </c>
+      <c r="DB183" s="24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -38905,7 +39117,9 @@
       <c r="DA185" s="32">
         <v>35.622626491414316</v>
       </c>
-      <c r="DB185" s="8"/>
+      <c r="DB185" s="32">
+        <v>31.870003098289786</v>
+      </c>
       <c r="DC185" s="8"/>
       <c r="DD185" s="8"/>
       <c r="DE185" s="8"/>
@@ -39296,7 +39510,9 @@
       <c r="DA186" s="32">
         <v>1.3928558482030335</v>
       </c>
-      <c r="DB186" s="8"/>
+      <c r="DB186" s="32">
+        <v>1.3044406203273744</v>
+      </c>
       <c r="DC186" s="8"/>
       <c r="DD186" s="8"/>
       <c r="DE186" s="8"/>
@@ -39687,7 +39903,9 @@
       <c r="DA187" s="32">
         <v>1.6739075855519421</v>
       </c>
-      <c r="DB187" s="8"/>
+      <c r="DB187" s="32">
+        <v>1.4891866792317539</v>
+      </c>
       <c r="DC187" s="8"/>
       <c r="DD187" s="8"/>
       <c r="DE187" s="8"/>
@@ -40078,7 +40296,9 @@
       <c r="DA188" s="32">
         <v>10.440580907306169</v>
       </c>
-      <c r="DB188" s="8"/>
+      <c r="DB188" s="32">
+        <v>11.860728675278406</v>
+      </c>
       <c r="DC188" s="8"/>
       <c r="DD188" s="8"/>
       <c r="DE188" s="8"/>
@@ -40469,7 +40689,9 @@
       <c r="DA189" s="32">
         <v>2.4991936999721429</v>
       </c>
-      <c r="DB189" s="8"/>
+      <c r="DB189" s="32">
+        <v>2.3969377427094405</v>
+      </c>
       <c r="DC189" s="8"/>
       <c r="DD189" s="8"/>
       <c r="DE189" s="8"/>
@@ -40860,7 +41082,9 @@
       <c r="DA190" s="32">
         <v>4.4857597563020342</v>
       </c>
-      <c r="DB190" s="8"/>
+      <c r="DB190" s="32">
+        <v>4.865964520227001</v>
+      </c>
       <c r="DC190" s="8"/>
       <c r="DD190" s="8"/>
       <c r="DE190" s="8"/>
@@ -41251,7 +41475,9 @@
       <c r="DA191" s="32">
         <v>8.1432744910178165</v>
       </c>
-      <c r="DB191" s="8"/>
+      <c r="DB191" s="32">
+        <v>10.306950193160123</v>
+      </c>
       <c r="DC191" s="8"/>
       <c r="DD191" s="8"/>
       <c r="DE191" s="8"/>
@@ -41642,7 +41868,9 @@
       <c r="DA192" s="32">
         <v>3.0543196119418572</v>
       </c>
-      <c r="DB192" s="8"/>
+      <c r="DB192" s="32">
+        <v>3.3763156416888469</v>
+      </c>
       <c r="DC192" s="8"/>
       <c r="DD192" s="8"/>
       <c r="DE192" s="8"/>
@@ -42033,7 +42261,9 @@
       <c r="DA193" s="32">
         <v>2.0556348418543737</v>
       </c>
-      <c r="DB193" s="8"/>
+      <c r="DB193" s="32">
+        <v>2.0725576167215798</v>
+      </c>
       <c r="DC193" s="8"/>
       <c r="DD193" s="8"/>
       <c r="DE193" s="8"/>
@@ -42424,7 +42654,9 @@
       <c r="DA194" s="32">
         <v>5.4668335274871662</v>
       </c>
-      <c r="DB194" s="8"/>
+      <c r="DB194" s="32">
+        <v>5.9706629295709055</v>
+      </c>
       <c r="DC194" s="8"/>
       <c r="DD194" s="8"/>
       <c r="DE194" s="8"/>
@@ -42815,7 +43047,9 @@
       <c r="DA195" s="32">
         <v>8.7430583183304122</v>
       </c>
-      <c r="DB195" s="8"/>
+      <c r="DB195" s="32">
+        <v>10.384882152956447</v>
+      </c>
       <c r="DC195" s="8"/>
       <c r="DD195" s="8"/>
       <c r="DE195" s="8"/>
@@ -43206,7 +43440,9 @@
       <c r="DA196" s="32">
         <v>16.421954920618724</v>
       </c>
-      <c r="DB196" s="8"/>
+      <c r="DB196" s="32">
+        <v>14.101370129838322</v>
+      </c>
       <c r="DC196" s="8"/>
       <c r="DD196" s="8"/>
       <c r="DE196" s="8"/>
@@ -43386,7 +43622,7 @@
       <c r="CY197" s="26"/>
       <c r="CZ197" s="26"/>
       <c r="DA197" s="26"/>
-      <c r="DB197" s="8"/>
+      <c r="DB197" s="26"/>
       <c r="DC197" s="8"/>
       <c r="DD197" s="8"/>
       <c r="DE197" s="8"/>
@@ -43777,7 +44013,9 @@
       <c r="DA198" s="32">
         <v>100</v>
       </c>
-      <c r="DB198" s="8"/>
+      <c r="DB198" s="32">
+        <v>100</v>
+      </c>
       <c r="DC198" s="8"/>
       <c r="DD198" s="8"/>
       <c r="DE198" s="8"/>
@@ -43958,6 +44196,7 @@
       <c r="CY199" s="27"/>
       <c r="CZ199" s="27"/>
       <c r="DA199" s="27"/>
+      <c r="DB199" s="27"/>
     </row>
     <row r="200" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A200" s="12" t="s">
@@ -44070,7 +44309,7 @@
       <c r="CY201" s="36"/>
       <c r="CZ201" s="36"/>
       <c r="DA201" s="36"/>
-      <c r="DB201" s="20"/>
+      <c r="DB201" s="36"/>
       <c r="DC201" s="20"/>
       <c r="DD201" s="20"/>
       <c r="DE201" s="20"/>
@@ -44150,6 +44389,7 @@
       <c r="CY202" s="29"/>
       <c r="CZ202" s="29"/>
       <c r="DA202" s="29"/>
+      <c r="DB202" s="28"/>
     </row>
     <row r="203" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT203" s="28"/>

--- a/Data/National Accounts/PSA-02HFCE_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-02HFCE_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E40A17C-6613-41F7-A73A-5E7AE0B57C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B520A11-6354-4D71-BABC-0AE46CD90C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -521,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="64">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -707,13 +707,13 @@
     <t>Percent Share, at Constant 2018 Prices</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1247,8 +1247,8 @@
     <col min="75" max="77" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="78" max="78" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="79" max="93" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="94" max="106" width="16.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="1"/>
+    <col min="94" max="107" width="16.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1263,7 +1263,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1273,7 +1273,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1442,6 +1442,7 @@
       <c r="DB9" s="23">
         <v>2026</v>
       </c>
+      <c r="DC9" s="23"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
@@ -1761,6 +1762,9 @@
       </c>
       <c r="DB10" s="24" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2083,9 +2087,11 @@
         <v>2257594.2514206418</v>
       </c>
       <c r="DB12" s="25">
-        <v>1778620.7258560532</v>
-      </c>
-      <c r="DC12" s="8"/>
+        <v>1780849.5021926407</v>
+      </c>
+      <c r="DC12" s="25">
+        <v>2058217.46614084</v>
+      </c>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
       <c r="DF12" s="8"/>
@@ -2476,9 +2482,11 @@
         <v>120252.82278633314</v>
       </c>
       <c r="DB13" s="25">
-        <v>98345.741683448505</v>
-      </c>
-      <c r="DC13" s="8"/>
+        <v>98404.506053292906</v>
+      </c>
+      <c r="DC13" s="25">
+        <v>88583.220711925562</v>
+      </c>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
       <c r="DF13" s="8"/>
@@ -2869,9 +2877,11 @@
         <v>94741.452218738676</v>
       </c>
       <c r="DB14" s="25">
-        <v>75003.247061091388</v>
-      </c>
-      <c r="DC14" s="8"/>
+        <v>74660.902374091107</v>
+      </c>
+      <c r="DC14" s="25">
+        <v>57970.71664216894</v>
+      </c>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
       <c r="DF14" s="8"/>
@@ -3262,9 +3272,11 @@
         <v>631565.8971390489</v>
       </c>
       <c r="DB15" s="25">
-        <v>597623.12105468463</v>
-      </c>
-      <c r="DC15" s="8"/>
+        <v>596954.41877003794</v>
+      </c>
+      <c r="DC15" s="25">
+        <v>796194.96285803744</v>
+      </c>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
       <c r="DF15" s="8"/>
@@ -3655,9 +3667,11 @@
         <v>147486.66570831661</v>
       </c>
       <c r="DB16" s="25">
-        <v>129497.11240136674</v>
-      </c>
-      <c r="DC16" s="8"/>
+        <v>129990.33583773799</v>
+      </c>
+      <c r="DC16" s="25">
+        <v>129638.87097918091</v>
+      </c>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
       <c r="DF16" s="8"/>
@@ -4048,9 +4062,11 @@
         <v>269475.82895237411</v>
       </c>
       <c r="DB17" s="25">
-        <v>250472.03487425239</v>
-      </c>
-      <c r="DC17" s="8"/>
+        <v>251185.654706598</v>
+      </c>
+      <c r="DC17" s="25">
+        <v>226844.92785009029</v>
+      </c>
       <c r="DD17" s="8"/>
       <c r="DE17" s="8"/>
       <c r="DF17" s="8"/>
@@ -4441,9 +4457,11 @@
         <v>496667.21270987199</v>
       </c>
       <c r="DB18" s="25">
-        <v>595479.16807577095</v>
-      </c>
-      <c r="DC18" s="8"/>
+        <v>593895.94045136345</v>
+      </c>
+      <c r="DC18" s="25">
+        <v>522412.1896321784</v>
+      </c>
       <c r="DD18" s="8"/>
       <c r="DE18" s="8"/>
       <c r="DF18" s="8"/>
@@ -4834,9 +4852,11 @@
         <v>145667.37342405706</v>
       </c>
       <c r="DB19" s="25">
-        <v>151721.68295889723</v>
-      </c>
-      <c r="DC19" s="8"/>
+        <v>151503.80112033547</v>
+      </c>
+      <c r="DC19" s="25">
+        <v>160555.98892234967</v>
+      </c>
       <c r="DD19" s="8"/>
       <c r="DE19" s="8"/>
       <c r="DF19" s="8"/>
@@ -5227,9 +5247,11 @@
         <v>116085.0135024778</v>
       </c>
       <c r="DB20" s="25">
-        <v>104579.21517266936</v>
-      </c>
-      <c r="DC20" s="8"/>
+        <v>104659.88991530363</v>
+      </c>
+      <c r="DC20" s="25">
+        <v>71377.365557757425</v>
+      </c>
       <c r="DD20" s="8"/>
       <c r="DE20" s="8"/>
       <c r="DF20" s="8"/>
@@ -5620,9 +5642,11 @@
         <v>300009.49537248426</v>
       </c>
       <c r="DB21" s="25">
-        <v>301333.79849671648</v>
-      </c>
-      <c r="DC21" s="8"/>
+        <v>300578.64207675576</v>
+      </c>
+      <c r="DC21" s="25">
+        <v>289228.62662580737</v>
+      </c>
       <c r="DD21" s="8"/>
       <c r="DE21" s="8"/>
       <c r="DF21" s="8"/>
@@ -6013,9 +6037,11 @@
         <v>550139.20937379065</v>
       </c>
       <c r="DB22" s="25">
-        <v>591401.75434679841</v>
-      </c>
-      <c r="DC22" s="8"/>
+        <v>592865.6798324649</v>
+      </c>
+      <c r="DC22" s="25">
+        <v>331836.13911109738</v>
+      </c>
       <c r="DD22" s="8"/>
       <c r="DE22" s="8"/>
       <c r="DF22" s="8"/>
@@ -6406,9 +6432,11 @@
         <v>913942.70429242158</v>
       </c>
       <c r="DB23" s="25">
-        <v>778827.55687577662</v>
-      </c>
-      <c r="DC23" s="8"/>
+        <v>778171.00851412956</v>
+      </c>
+      <c r="DC23" s="25">
+        <v>754238.1811308359</v>
+      </c>
       <c r="DD23" s="8"/>
       <c r="DE23" s="8"/>
       <c r="DF23" s="8"/>
@@ -6588,7 +6616,7 @@
       <c r="CZ24" s="26"/>
       <c r="DA24" s="26"/>
       <c r="DB24" s="26"/>
-      <c r="DC24" s="8"/>
+      <c r="DC24" s="26"/>
       <c r="DD24" s="8"/>
       <c r="DE24" s="8"/>
       <c r="DF24" s="8"/>
@@ -6979,9 +7007,11 @@
         <v>6043627.9269005563</v>
       </c>
       <c r="DB25" s="10">
-        <v>5452905.1588575263</v>
-      </c>
-      <c r="DC25" s="8"/>
+        <v>5453720.281844751</v>
+      </c>
+      <c r="DC25" s="10">
+        <v>5487098.6561622685</v>
+      </c>
       <c r="DD25" s="8"/>
       <c r="DE25" s="8"/>
       <c r="DF25" s="8"/>
@@ -7162,6 +7192,7 @@
       <c r="CZ26" s="27"/>
       <c r="DA26" s="27"/>
       <c r="DB26" s="27"/>
+      <c r="DC26" s="27"/>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
@@ -7274,7 +7305,7 @@
       <c r="CZ28" s="15"/>
       <c r="DA28" s="15"/>
       <c r="DB28" s="15"/>
-      <c r="DC28" s="8"/>
+      <c r="DC28" s="15"/>
       <c r="DD28" s="8"/>
       <c r="DE28" s="8"/>
       <c r="DF28" s="8"/>
@@ -7454,7 +7485,7 @@
       <c r="CZ29" s="17"/>
       <c r="DA29" s="17"/>
       <c r="DB29" s="17"/>
-      <c r="DC29" s="8"/>
+      <c r="DC29" s="17"/>
       <c r="DD29" s="8"/>
       <c r="DE29" s="8"/>
       <c r="DF29" s="8"/>
@@ -7540,7 +7571,7 @@
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:179" x14ac:dyDescent="0.2">
@@ -7550,7 +7581,7 @@
     </row>
     <row r="35" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:179" x14ac:dyDescent="0.2">
@@ -7719,6 +7750,7 @@
       <c r="DB38" s="23">
         <v>2026</v>
       </c>
+      <c r="DC38" s="23"/>
     </row>
     <row r="39" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
@@ -8038,6 +8070,9 @@
       </c>
       <c r="DB39" s="24" t="s">
         <v>2</v>
+      </c>
+      <c r="DC39" s="24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -8360,9 +8395,11 @@
         <v>1712013.4937564556</v>
       </c>
       <c r="DB41" s="25">
-        <v>1336154.8218690488</v>
-      </c>
-      <c r="DC41" s="18"/>
+        <v>1337829.1474887312</v>
+      </c>
+      <c r="DC41" s="25">
+        <v>1474396.4868965195</v>
+      </c>
       <c r="DD41" s="18"/>
       <c r="DE41" s="8"/>
       <c r="DF41" s="8"/>
@@ -8753,9 +8790,11 @@
         <v>66940.263586569476</v>
       </c>
       <c r="DB42" s="25">
-        <v>54688.87528240637</v>
-      </c>
-      <c r="DC42" s="18"/>
+        <v>54721.553436421556</v>
+      </c>
+      <c r="DC42" s="25">
+        <v>44521.969899765572</v>
+      </c>
       <c r="DD42" s="18"/>
       <c r="DE42" s="8"/>
       <c r="DF42" s="8"/>
@@ -9146,9 +9185,11 @@
         <v>80447.531696095204</v>
       </c>
       <c r="DB43" s="25">
-        <v>62434.382449917008</v>
-      </c>
-      <c r="DC43" s="18"/>
+        <v>62149.40706611178</v>
+      </c>
+      <c r="DC43" s="25">
+        <v>43943.727905410917</v>
+      </c>
       <c r="DD43" s="18"/>
       <c r="DE43" s="8"/>
       <c r="DF43" s="8"/>
@@ -9539,9 +9580,11 @@
         <v>501771.40644787182</v>
       </c>
       <c r="DB44" s="25">
-        <v>497262.88891400094</v>
-      </c>
-      <c r="DC44" s="18"/>
+        <v>496706.48334973835</v>
+      </c>
+      <c r="DC44" s="25">
+        <v>609382.27496379381</v>
+      </c>
       <c r="DD44" s="18"/>
       <c r="DE44" s="8"/>
       <c r="DF44" s="8"/>
@@ -9932,9 +9975,11 @@
         <v>120110.55217656854</v>
       </c>
       <c r="DB45" s="25">
-        <v>100491.98654809655</v>
-      </c>
-      <c r="DC45" s="18"/>
+        <v>100874.73641806586</v>
+      </c>
+      <c r="DC45" s="25">
+        <v>100045.44612950395</v>
+      </c>
       <c r="DD45" s="18"/>
       <c r="DE45" s="8"/>
       <c r="DF45" s="8"/>
@@ -10325,9 +10370,11 @@
         <v>215584.36277543131</v>
       </c>
       <c r="DB46" s="25">
-        <v>204006.31705912558</v>
-      </c>
-      <c r="DC46" s="18"/>
+        <v>204587.55142267546</v>
+      </c>
+      <c r="DC46" s="25">
+        <v>181823.8324297306</v>
+      </c>
       <c r="DD46" s="18"/>
       <c r="DE46" s="8"/>
       <c r="DF46" s="8"/>
@@ -10718,9 +10765,11 @@
         <v>391363.50081725052</v>
       </c>
       <c r="DB47" s="25">
-        <v>432120.48511203448</v>
-      </c>
-      <c r="DC47" s="18"/>
+        <v>430971.58666893281</v>
+      </c>
+      <c r="DC47" s="25">
+        <v>356283.62200209987</v>
+      </c>
       <c r="DD47" s="18"/>
       <c r="DE47" s="8"/>
       <c r="DF47" s="8"/>
@@ -11111,9 +11160,11 @@
         <v>146789.74867700256</v>
       </c>
       <c r="DB48" s="25">
-        <v>141552.55683161606</v>
-      </c>
-      <c r="DC48" s="18"/>
+        <v>141349.27849503219</v>
+      </c>
+      <c r="DC48" s="25">
+        <v>153529.31980295136</v>
+      </c>
       <c r="DD48" s="18"/>
       <c r="DE48" s="8"/>
       <c r="DF48" s="8"/>
@@ -11504,9 +11555,11 @@
         <v>98793.237167360829</v>
       </c>
       <c r="DB49" s="25">
-        <v>86892.299465529941</v>
-      </c>
-      <c r="DC49" s="18"/>
+        <v>86959.330126304252</v>
+      </c>
+      <c r="DC49" s="25">
+        <v>59323.875462414973</v>
+      </c>
       <c r="DD49" s="18"/>
       <c r="DE49" s="8"/>
       <c r="DF49" s="8"/>
@@ -11897,9 +11950,11 @@
         <v>262734.49458966724</v>
       </c>
       <c r="DB50" s="25">
-        <v>250320.96917270299</v>
-      </c>
-      <c r="DC50" s="18"/>
+        <v>249693.65325970354</v>
+      </c>
+      <c r="DC50" s="25">
+        <v>233600.03422705273</v>
+      </c>
       <c r="DD50" s="18"/>
       <c r="DE50" s="8"/>
       <c r="DF50" s="8"/>
@@ -12290,9 +12345,11 @@
         <v>420188.94427363185</v>
       </c>
       <c r="DB51" s="25">
-        <v>435387.79461113992</v>
-      </c>
-      <c r="DC51" s="18"/>
+        <v>436465.53116500482</v>
+      </c>
+      <c r="DC51" s="25">
+        <v>246355.58688284273</v>
+      </c>
       <c r="DD51" s="18"/>
       <c r="DE51" s="8"/>
       <c r="DF51" s="8"/>
@@ -12683,9 +12740,11 @@
         <v>789234.57327706018</v>
       </c>
       <c r="DB52" s="25">
-        <v>591202.12934509362</v>
-      </c>
-      <c r="DC52" s="18"/>
+        <v>590703.74843137653</v>
+      </c>
+      <c r="DC52" s="25">
+        <v>558989.98855918273</v>
+      </c>
       <c r="DD52" s="18"/>
       <c r="DE52" s="8"/>
       <c r="DF52" s="8"/>
@@ -12865,7 +12924,7 @@
       <c r="CZ53" s="26"/>
       <c r="DA53" s="26"/>
       <c r="DB53" s="26"/>
-      <c r="DC53" s="8"/>
+      <c r="DC53" s="26"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
       <c r="DF53" s="8"/>
@@ -13256,9 +13315,11 @@
         <v>4805972.1092409659</v>
       </c>
       <c r="DB54" s="10">
-        <v>4192515.5066607129</v>
-      </c>
-      <c r="DC54" s="8"/>
+        <v>4193012.0073280982</v>
+      </c>
+      <c r="DC54" s="10">
+        <v>4062196.1651612697</v>
+      </c>
       <c r="DD54" s="8"/>
       <c r="DE54" s="8"/>
       <c r="DF54" s="8"/>
@@ -13439,6 +13500,7 @@
       <c r="CZ55" s="27"/>
       <c r="DA55" s="27"/>
       <c r="DB55" s="27"/>
+      <c r="DC55" s="27"/>
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
@@ -13551,7 +13613,7 @@
       <c r="CZ57" s="26"/>
       <c r="DA57" s="26"/>
       <c r="DB57" s="26"/>
-      <c r="DC57" s="8"/>
+      <c r="DC57" s="26"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
       <c r="DF57" s="8"/>
@@ -13731,7 +13793,7 @@
       <c r="CZ58" s="17"/>
       <c r="DA58" s="17"/>
       <c r="DB58" s="17"/>
-      <c r="DC58" s="8"/>
+      <c r="DC58" s="17"/>
       <c r="DD58" s="8"/>
       <c r="DE58" s="8"/>
       <c r="DF58" s="8"/>
@@ -13817,7 +13879,7 @@
     </row>
     <row r="61" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="CT61" s="28"/>
       <c r="CU61" s="28"/>
@@ -13827,6 +13889,7 @@
       <c r="CZ61" s="28"/>
       <c r="DA61" s="28"/>
       <c r="DB61" s="28"/>
+      <c r="DC61" s="28"/>
     </row>
     <row r="62" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT62" s="28"/>
@@ -13837,6 +13900,7 @@
       <c r="CZ62" s="28"/>
       <c r="DA62" s="28"/>
       <c r="DB62" s="28"/>
+      <c r="DC62" s="28"/>
     </row>
     <row r="63" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
@@ -13850,16 +13914,18 @@
       <c r="CZ63" s="28"/>
       <c r="DA63" s="28"/>
       <c r="DB63" s="28"/>
+      <c r="DC63" s="28"/>
     </row>
     <row r="64" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CX64" s="28"/>
       <c r="CY64" s="28"/>
       <c r="CZ64" s="28"/>
       <c r="DA64" s="28"/>
       <c r="DB64" s="28"/>
+      <c r="DC64" s="28"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
@@ -13870,12 +13936,13 @@
       <c r="CZ65" s="29"/>
       <c r="DA65" s="29"/>
       <c r="DB65" s="29"/>
+      <c r="DC65" s="29"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY66" s="29"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
       <c r="DB66" s="29"/>
+      <c r="DC66" s="29"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
@@ -14030,12 +14097,13 @@
       <c r="CV67" s="23"/>
       <c r="CW67" s="23"/>
       <c r="CX67" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="CY67" s="30"/>
+        <v>61</v>
+      </c>
+      <c r="CY67" s="23"/>
       <c r="CZ67" s="30"/>
       <c r="DA67" s="30"/>
       <c r="DB67" s="30"/>
+      <c r="DC67" s="30"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
@@ -14344,17 +14412,20 @@
       <c r="CX68" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="CY68" s="31"/>
+      <c r="CY68" s="24" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ68" s="31"/>
       <c r="DA68" s="31"/>
       <c r="DB68" s="31"/>
+      <c r="DC68" s="31"/>
     </row>
     <row r="69" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
-      <c r="CY69" s="29"/>
       <c r="CZ69" s="29"/>
       <c r="DA69" s="29"/>
       <c r="DB69" s="29"/>
+      <c r="DC69" s="29"/>
     </row>
     <row r="70" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
@@ -14661,13 +14732,15 @@
         <v>4.5040021672833319</v>
       </c>
       <c r="CX70" s="32">
-        <v>2.2521765703352798</v>
-      </c>
-      <c r="CY70" s="33"/>
+        <v>2.3803080084724684</v>
+      </c>
+      <c r="CY70" s="32">
+        <v>8.2679705361318412</v>
+      </c>
       <c r="CZ70" s="33"/>
       <c r="DA70" s="33"/>
       <c r="DB70" s="33"/>
-      <c r="DC70" s="8"/>
+      <c r="DC70" s="33"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
       <c r="DF70" s="8"/>
@@ -15042,13 +15115,15 @@
         <v>-2.6867580532877611</v>
       </c>
       <c r="CX71" s="32">
-        <v>6.4741941354012198</v>
-      </c>
-      <c r="CY71" s="33"/>
+        <v>6.5378154861171112</v>
+      </c>
+      <c r="CY71" s="32">
+        <v>3.4416488326083083</v>
+      </c>
       <c r="CZ71" s="33"/>
       <c r="DA71" s="33"/>
       <c r="DB71" s="33"/>
-      <c r="DC71" s="8"/>
+      <c r="DC71" s="33"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
       <c r="DF71" s="8"/>
@@ -15423,13 +15498,15 @@
         <v>0.85425742935640869</v>
       </c>
       <c r="CX72" s="32">
-        <v>15.005754421105095</v>
-      </c>
-      <c r="CY72" s="33"/>
+        <v>14.480822360917671</v>
+      </c>
+      <c r="CY72" s="32">
+        <v>11.067389945595821</v>
+      </c>
       <c r="CZ72" s="33"/>
       <c r="DA72" s="33"/>
       <c r="DB72" s="33"/>
-      <c r="DC72" s="8"/>
+      <c r="DC72" s="33"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
       <c r="DF72" s="8"/>
@@ -15804,13 +15881,15 @@
         <v>2.8177282016049929</v>
       </c>
       <c r="CX73" s="32">
-        <v>6.6055781133850644</v>
-      </c>
-      <c r="CY73" s="33"/>
+        <v>6.4862932478418855</v>
+      </c>
+      <c r="CY73" s="32">
+        <v>11.484260027768144</v>
+      </c>
       <c r="CZ73" s="33"/>
       <c r="DA73" s="33"/>
       <c r="DB73" s="33"/>
-      <c r="DC73" s="8"/>
+      <c r="DC73" s="33"/>
       <c r="DD73" s="8"/>
       <c r="DE73" s="8"/>
       <c r="DF73" s="8"/>
@@ -16185,13 +16264,15 @@
         <v>6.2002573040501829E-2</v>
       </c>
       <c r="CX74" s="32">
-        <v>5.9292585985969453</v>
-      </c>
-      <c r="CY74" s="33"/>
+        <v>6.3327177334718812</v>
+      </c>
+      <c r="CY74" s="32">
+        <v>7.7735951606349403</v>
+      </c>
       <c r="CZ74" s="33"/>
       <c r="DA74" s="33"/>
       <c r="DB74" s="33"/>
-      <c r="DC74" s="8"/>
+      <c r="DC74" s="33"/>
       <c r="DD74" s="8"/>
       <c r="DE74" s="8"/>
       <c r="DF74" s="8"/>
@@ -16566,13 +16647,15 @@
         <v>8.517487380089122</v>
       </c>
       <c r="CX75" s="32">
-        <v>9.0823825021554256</v>
-      </c>
-      <c r="CY75" s="33"/>
+        <v>9.393169099757543</v>
+      </c>
+      <c r="CY75" s="32">
+        <v>14.327210698218011</v>
+      </c>
       <c r="CZ75" s="33"/>
       <c r="DA75" s="33"/>
       <c r="DB75" s="33"/>
-      <c r="DC75" s="8"/>
+      <c r="DC75" s="33"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
       <c r="DF75" s="8"/>
@@ -16947,13 +17030,15 @@
         <v>7.0480931519140881</v>
       </c>
       <c r="CX76" s="32">
-        <v>6.748168166432734</v>
-      </c>
-      <c r="CY76" s="33"/>
+        <v>6.4643519428659033</v>
+      </c>
+      <c r="CY76" s="32">
+        <v>8.0402382831615569</v>
+      </c>
       <c r="CZ76" s="33"/>
       <c r="DA76" s="33"/>
       <c r="DB76" s="33"/>
-      <c r="DC76" s="8"/>
+      <c r="DC76" s="33"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
       <c r="DF76" s="8"/>
@@ -17328,13 +17413,15 @@
         <v>4.245173815947993</v>
       </c>
       <c r="CX77" s="32">
-        <v>6.4283724753448723</v>
-      </c>
-      <c r="CY77" s="33"/>
+        <v>6.275534667209385</v>
+      </c>
+      <c r="CY77" s="32">
+        <v>6.4784458530672282</v>
+      </c>
       <c r="CZ77" s="33"/>
       <c r="DA77" s="33"/>
       <c r="DB77" s="33"/>
-      <c r="DC77" s="8"/>
+      <c r="DC77" s="33"/>
       <c r="DD77" s="8"/>
       <c r="DE77" s="8"/>
       <c r="DF77" s="8"/>
@@ -17709,13 +17796,15 @@
         <v>9.0856460685615872</v>
       </c>
       <c r="CX78" s="32">
-        <v>9.4690483265493128</v>
-      </c>
-      <c r="CY78" s="33"/>
+        <v>9.5534951957056933</v>
+      </c>
+      <c r="CY78" s="32">
+        <v>4.2612368733145161</v>
+      </c>
       <c r="CZ78" s="33"/>
       <c r="DA78" s="33"/>
       <c r="DB78" s="33"/>
-      <c r="DC78" s="8"/>
+      <c r="DC78" s="33"/>
       <c r="DD78" s="8"/>
       <c r="DE78" s="8"/>
       <c r="DF78" s="8"/>
@@ -18090,13 +18179,15 @@
         <v>9.8287101496879643</v>
       </c>
       <c r="CX79" s="32">
-        <v>9.8047587741586</v>
-      </c>
-      <c r="CY79" s="33"/>
+        <v>9.5295829759434412</v>
+      </c>
+      <c r="CY79" s="32">
+        <v>16.606873139897289</v>
+      </c>
       <c r="CZ79" s="33"/>
       <c r="DA79" s="33"/>
       <c r="DB79" s="33"/>
-      <c r="DC79" s="8"/>
+      <c r="DC79" s="33"/>
       <c r="DD79" s="8"/>
       <c r="DE79" s="8"/>
       <c r="DF79" s="8"/>
@@ -18471,13 +18562,15 @@
         <v>9.7353051485010553</v>
       </c>
       <c r="CX80" s="32">
-        <v>8.8971241917830781</v>
-      </c>
-      <c r="CY80" s="33"/>
+        <v>9.1666825321979246</v>
+      </c>
+      <c r="CY80" s="32">
+        <v>6.3842744872892467</v>
+      </c>
       <c r="CZ80" s="33"/>
       <c r="DA80" s="33"/>
       <c r="DB80" s="33"/>
-      <c r="DC80" s="8"/>
+      <c r="DC80" s="33"/>
       <c r="DD80" s="8"/>
       <c r="DE80" s="8"/>
       <c r="DF80" s="8"/>
@@ -18852,13 +18945,15 @@
         <v>6.4151687512959938</v>
       </c>
       <c r="CX81" s="32">
-        <v>6.8926099203904272</v>
-      </c>
-      <c r="CY81" s="33"/>
+        <v>6.8024998988640277</v>
+      </c>
+      <c r="CY81" s="32">
+        <v>9.6601117698580339</v>
+      </c>
       <c r="CZ81" s="33"/>
       <c r="DA81" s="33"/>
       <c r="DB81" s="33"/>
-      <c r="DC81" s="8"/>
+      <c r="DC81" s="33"/>
       <c r="DD81" s="8"/>
       <c r="DE81" s="8"/>
       <c r="DF81" s="8"/>
@@ -19030,11 +19125,11 @@
       <c r="CV82" s="26"/>
       <c r="CW82" s="26"/>
       <c r="CX82" s="26"/>
-      <c r="CY82" s="34"/>
+      <c r="CY82" s="26"/>
       <c r="CZ82" s="34"/>
       <c r="DA82" s="34"/>
       <c r="DB82" s="34"/>
-      <c r="DC82" s="8"/>
+      <c r="DC82" s="34"/>
       <c r="DD82" s="8"/>
       <c r="DE82" s="8"/>
       <c r="DF82" s="8"/>
@@ -19409,13 +19504,15 @@
         <v>5.4505627561364491</v>
       </c>
       <c r="CX83" s="32">
-        <v>5.8501992776329246</v>
-      </c>
-      <c r="CY83" s="33"/>
+        <v>5.8660222065340974</v>
+      </c>
+      <c r="CY83" s="32">
+        <v>9.2548995137978096</v>
+      </c>
       <c r="CZ83" s="33"/>
       <c r="DA83" s="33"/>
       <c r="DB83" s="33"/>
-      <c r="DC83" s="8"/>
+      <c r="DC83" s="33"/>
       <c r="DD83" s="8"/>
       <c r="DE83" s="8"/>
       <c r="DF83" s="8"/>
@@ -19588,19 +19685,20 @@
       <c r="CV84" s="27"/>
       <c r="CW84" s="27"/>
       <c r="CX84" s="27"/>
-      <c r="CY84" s="31"/>
+      <c r="CY84" s="27"/>
       <c r="CZ84" s="31"/>
       <c r="DA84" s="31"/>
       <c r="DB84" s="31"/>
+      <c r="DC84" s="31"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="CY85" s="29"/>
       <c r="CZ85" s="29"/>
       <c r="DA85" s="29"/>
       <c r="DB85" s="29"/>
+      <c r="DC85" s="29"/>
     </row>
     <row r="86" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="8"/>
@@ -19704,11 +19802,11 @@
       <c r="CV86" s="26"/>
       <c r="CW86" s="26"/>
       <c r="CX86" s="26"/>
-      <c r="CY86" s="34"/>
+      <c r="CY86" s="26"/>
       <c r="CZ86" s="34"/>
       <c r="DA86" s="34"/>
       <c r="DB86" s="34"/>
-      <c r="DC86" s="8"/>
+      <c r="DC86" s="34"/>
       <c r="DD86" s="8"/>
       <c r="DE86" s="8"/>
       <c r="DF86" s="8"/>
@@ -19880,11 +19978,11 @@
       <c r="CV87" s="26"/>
       <c r="CW87" s="26"/>
       <c r="CX87" s="26"/>
-      <c r="CY87" s="34"/>
+      <c r="CY87" s="26"/>
       <c r="CZ87" s="34"/>
       <c r="DA87" s="34"/>
       <c r="DB87" s="34"/>
-      <c r="DC87" s="8"/>
+      <c r="DC87" s="34"/>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
       <c r="DF87" s="8"/>
@@ -19958,67 +20056,67 @@
       <c r="A88" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CY88" s="29"/>
       <c r="CZ88" s="29"/>
       <c r="DA88" s="29"/>
       <c r="DB88" s="29"/>
+      <c r="DC88" s="29"/>
     </row>
     <row r="89" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CY89" s="29"/>
       <c r="CZ89" s="29"/>
       <c r="DA89" s="29"/>
       <c r="DB89" s="29"/>
+      <c r="DC89" s="29"/>
     </row>
     <row r="90" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="CY90" s="29"/>
+        <v>63</v>
+      </c>
       <c r="CZ90" s="29"/>
       <c r="DA90" s="29"/>
       <c r="DB90" s="29"/>
+      <c r="DC90" s="29"/>
     </row>
     <row r="91" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY91" s="29"/>
       <c r="CZ91" s="29"/>
       <c r="DA91" s="29"/>
       <c r="DB91" s="29"/>
+      <c r="DC91" s="29"/>
     </row>
     <row r="92" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CY92" s="29"/>
       <c r="CZ92" s="29"/>
       <c r="DA92" s="29"/>
       <c r="DB92" s="29"/>
+      <c r="DC92" s="29"/>
     </row>
     <row r="93" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="CY93" s="29"/>
+        <v>62</v>
+      </c>
       <c r="CZ93" s="29"/>
       <c r="DA93" s="29"/>
       <c r="DB93" s="29"/>
+      <c r="DC93" s="29"/>
     </row>
     <row r="94" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CY94" s="29"/>
       <c r="CZ94" s="29"/>
       <c r="DA94" s="29"/>
       <c r="DB94" s="29"/>
+      <c r="DC94" s="29"/>
     </row>
     <row r="95" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY95" s="29"/>
       <c r="CZ95" s="29"/>
       <c r="DA95" s="29"/>
       <c r="DB95" s="29"/>
+      <c r="DC95" s="29"/>
     </row>
     <row r="96" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
@@ -20173,12 +20271,13 @@
       <c r="CV96" s="23"/>
       <c r="CW96" s="23"/>
       <c r="CX96" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="CY96" s="30"/>
+        <v>61</v>
+      </c>
+      <c r="CY96" s="23"/>
       <c r="CZ96" s="30"/>
       <c r="DA96" s="30"/>
       <c r="DB96" s="30"/>
+      <c r="DC96" s="30"/>
     </row>
     <row r="97" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
@@ -20487,17 +20586,20 @@
       <c r="CX97" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="CY97" s="31"/>
+      <c r="CY97" s="24" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ97" s="31"/>
       <c r="DA97" s="31"/>
       <c r="DB97" s="31"/>
+      <c r="DC97" s="31"/>
     </row>
     <row r="98" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
-      <c r="CY98" s="29"/>
       <c r="CZ98" s="29"/>
       <c r="DA98" s="29"/>
       <c r="DB98" s="29"/>
+      <c r="DC98" s="29"/>
     </row>
     <row r="99" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
@@ -20804,13 +20906,15 @@
         <v>3.7927321752196548</v>
       </c>
       <c r="CX99" s="32">
-        <v>0.28772588745691507</v>
-      </c>
-      <c r="CY99" s="33"/>
+        <v>0.41339568712741936</v>
+      </c>
+      <c r="CY99" s="32">
+        <v>2.4303226745777238</v>
+      </c>
       <c r="CZ99" s="33"/>
       <c r="DA99" s="33"/>
       <c r="DB99" s="33"/>
-      <c r="DC99" s="8"/>
+      <c r="DC99" s="33"/>
       <c r="DD99" s="8"/>
       <c r="DE99" s="8"/>
       <c r="DF99" s="8"/>
@@ -21185,13 +21289,15 @@
         <v>-6.1365886567613046</v>
       </c>
       <c r="CX100" s="32">
-        <v>3.0541712181860277</v>
-      </c>
-      <c r="CY100" s="33"/>
+        <v>3.1157490082134558</v>
+      </c>
+      <c r="CY100" s="32">
+        <v>-1.8543638726639813</v>
+      </c>
       <c r="CZ100" s="33"/>
       <c r="DA100" s="33"/>
       <c r="DB100" s="33"/>
-      <c r="DC100" s="8"/>
+      <c r="DC100" s="33"/>
       <c r="DD100" s="8"/>
       <c r="DE100" s="8"/>
       <c r="DF100" s="8"/>
@@ -21566,13 +21672,15 @@
         <v>-1.0533477687317543</v>
       </c>
       <c r="CX101" s="32">
-        <v>12.25860284969977</v>
-      </c>
-      <c r="CY101" s="33"/>
+        <v>11.74620988324105</v>
+      </c>
+      <c r="CY101" s="32">
+        <v>7.8692708056122882</v>
+      </c>
       <c r="CZ101" s="33"/>
       <c r="DA101" s="33"/>
       <c r="DB101" s="33"/>
-      <c r="DC101" s="8"/>
+      <c r="DC101" s="33"/>
       <c r="DD101" s="8"/>
       <c r="DE101" s="8"/>
       <c r="DF101" s="8"/>
@@ -21947,13 +22055,15 @@
         <v>0.11345086296911688</v>
       </c>
       <c r="CX102" s="32">
-        <v>2.7208224282392734</v>
-      </c>
-      <c r="CY102" s="33"/>
+        <v>2.6058843573739381</v>
+      </c>
+      <c r="CY102" s="32">
+        <v>3.2240855196623528</v>
+      </c>
       <c r="CZ102" s="33"/>
       <c r="DA102" s="33"/>
       <c r="DB102" s="33"/>
-      <c r="DC102" s="8"/>
+      <c r="DC102" s="33"/>
       <c r="DD102" s="8"/>
       <c r="DE102" s="8"/>
       <c r="DF102" s="8"/>
@@ -22328,13 +22438,15 @@
         <v>-1.9626811850934303</v>
       </c>
       <c r="CX103" s="32">
-        <v>3.0911224344107495</v>
-      </c>
-      <c r="CY103" s="33"/>
+        <v>3.4837717894702536</v>
+      </c>
+      <c r="CY103" s="32">
+        <v>3.9445021790459833</v>
+      </c>
       <c r="CZ103" s="33"/>
       <c r="DA103" s="33"/>
       <c r="DB103" s="33"/>
-      <c r="DC103" s="8"/>
+      <c r="DC103" s="33"/>
       <c r="DD103" s="8"/>
       <c r="DE103" s="8"/>
       <c r="DF103" s="8"/>
@@ -22709,13 +22821,15 @@
         <v>5.6483077399349497</v>
       </c>
       <c r="CX104" s="32">
-        <v>5.6947308716537322</v>
-      </c>
-      <c r="CY104" s="33"/>
+        <v>5.9958657115663385</v>
+      </c>
+      <c r="CY104" s="32">
+        <v>9.7564513196541753</v>
+      </c>
       <c r="CZ104" s="33"/>
       <c r="DA104" s="33"/>
       <c r="DB104" s="33"/>
-      <c r="DC104" s="8"/>
+      <c r="DC104" s="33"/>
       <c r="DD104" s="8"/>
       <c r="DE104" s="8"/>
       <c r="DF104" s="8"/>
@@ -23090,13 +23204,15 @@
         <v>6.0058621655516049</v>
       </c>
       <c r="CX105" s="32">
-        <v>3.5374974360975955</v>
-      </c>
-      <c r="CY105" s="33"/>
+        <v>3.2622175692425657</v>
+      </c>
+      <c r="CY105" s="32">
+        <v>-7.490095902398437</v>
+      </c>
       <c r="CZ105" s="33"/>
       <c r="DA105" s="33"/>
       <c r="DB105" s="33"/>
-      <c r="DC105" s="8"/>
+      <c r="DC105" s="33"/>
       <c r="DD105" s="8"/>
       <c r="DE105" s="8"/>
       <c r="DF105" s="8"/>
@@ -23471,13 +23587,15 @@
         <v>3.5428482945700779</v>
       </c>
       <c r="CX106" s="32">
-        <v>5.6788768945325927</v>
-      </c>
-      <c r="CY106" s="33"/>
+        <v>5.5271154089896299</v>
+      </c>
+      <c r="CY106" s="32">
+        <v>5.5274421899457451</v>
+      </c>
       <c r="CZ106" s="33"/>
       <c r="DA106" s="33"/>
       <c r="DB106" s="33"/>
-      <c r="DC106" s="8"/>
+      <c r="DC106" s="33"/>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
       <c r="DF106" s="8"/>
@@ -23852,13 +23970,15 @@
         <v>6.9813940197132212</v>
       </c>
       <c r="CX107" s="32">
-        <v>5.4334607994919395</v>
-      </c>
-      <c r="CY107" s="33"/>
+        <v>5.514794526284561</v>
+      </c>
+      <c r="CY107" s="32">
+        <v>-0.80896298538239364</v>
+      </c>
       <c r="CZ107" s="33"/>
       <c r="DA107" s="33"/>
       <c r="DB107" s="33"/>
-      <c r="DC107" s="8"/>
+      <c r="DC107" s="33"/>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
       <c r="DF107" s="8"/>
@@ -24233,13 +24353,15 @@
         <v>6.6324016893898374</v>
       </c>
       <c r="CX108" s="32">
-        <v>6.7004239138229451</v>
-      </c>
-      <c r="CY108" s="33"/>
+        <v>6.4330277221809098</v>
+      </c>
+      <c r="CY108" s="32">
+        <v>12.957059293624411</v>
+      </c>
       <c r="CZ108" s="33"/>
       <c r="DA108" s="33"/>
       <c r="DB108" s="33"/>
-      <c r="DC108" s="8"/>
+      <c r="DC108" s="33"/>
       <c r="DD108" s="8"/>
       <c r="DE108" s="8"/>
       <c r="DF108" s="8"/>
@@ -24614,13 +24736,15 @@
         <v>7.0804187336179751</v>
       </c>
       <c r="CX109" s="32">
-        <v>4.2472837968456076</v>
-      </c>
-      <c r="CY109" s="33"/>
+        <v>4.5053321614979325</v>
+      </c>
+      <c r="CY109" s="32">
+        <v>-0.17575008673574644</v>
+      </c>
       <c r="CZ109" s="33"/>
       <c r="DA109" s="33"/>
       <c r="DB109" s="33"/>
-      <c r="DC109" s="8"/>
+      <c r="DC109" s="33"/>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
       <c r="DF109" s="8"/>
@@ -24995,13 +25119,15 @@
         <v>3.9744610163546525</v>
       </c>
       <c r="CX110" s="32">
-        <v>4.0446280596069926</v>
-      </c>
-      <c r="CY110" s="33"/>
+        <v>3.9569188748360489</v>
+      </c>
+      <c r="CY110" s="32">
+        <v>5.7629819871159782</v>
+      </c>
       <c r="CZ110" s="33"/>
       <c r="DA110" s="33"/>
       <c r="DB110" s="33"/>
-      <c r="DC110" s="8"/>
+      <c r="DC110" s="33"/>
       <c r="DD110" s="8"/>
       <c r="DE110" s="8"/>
       <c r="DF110" s="8"/>
@@ -25173,11 +25299,11 @@
       <c r="CV111" s="26"/>
       <c r="CW111" s="26"/>
       <c r="CX111" s="26"/>
-      <c r="CY111" s="34"/>
+      <c r="CY111" s="26"/>
       <c r="CZ111" s="34"/>
       <c r="DA111" s="34"/>
       <c r="DB111" s="34"/>
-      <c r="DC111" s="8"/>
+      <c r="DC111" s="34"/>
       <c r="DD111" s="8"/>
       <c r="DE111" s="8"/>
       <c r="DF111" s="8"/>
@@ -25552,13 +25678,15 @@
         <v>3.7778645631406675</v>
       </c>
       <c r="CX112" s="32">
-        <v>3.0158187478206173</v>
-      </c>
-      <c r="CY112" s="33"/>
+        <v>3.0280184457533608</v>
+      </c>
+      <c r="CY112" s="32">
+        <v>2.8319698099088129</v>
+      </c>
       <c r="CZ112" s="33"/>
       <c r="DA112" s="33"/>
       <c r="DB112" s="33"/>
-      <c r="DC112" s="8"/>
+      <c r="DC112" s="33"/>
       <c r="DD112" s="8"/>
       <c r="DE112" s="8"/>
       <c r="DF112" s="8"/>
@@ -25731,19 +25859,20 @@
       <c r="CV113" s="27"/>
       <c r="CW113" s="27"/>
       <c r="CX113" s="27"/>
-      <c r="CY113" s="31"/>
+      <c r="CY113" s="27"/>
       <c r="CZ113" s="31"/>
       <c r="DA113" s="31"/>
       <c r="DB113" s="31"/>
+      <c r="DC113" s="31"/>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A114" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="CY114" s="29"/>
       <c r="CZ114" s="29"/>
       <c r="DA114" s="29"/>
       <c r="DB114" s="29"/>
+      <c r="DC114" s="29"/>
     </row>
     <row r="115" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="8"/>
@@ -25851,7 +25980,7 @@
       <c r="CZ115" s="35"/>
       <c r="DA115" s="35"/>
       <c r="DB115" s="26"/>
-      <c r="DC115" s="8"/>
+      <c r="DC115" s="26"/>
       <c r="DD115" s="8"/>
       <c r="DE115" s="8"/>
       <c r="DF115" s="8"/>
@@ -26027,7 +26156,7 @@
       <c r="CZ116" s="35"/>
       <c r="DA116" s="35"/>
       <c r="DB116" s="26"/>
-      <c r="DC116" s="8"/>
+      <c r="DC116" s="26"/>
       <c r="DD116" s="8"/>
       <c r="DE116" s="8"/>
       <c r="DF116" s="8"/>
@@ -26104,7 +26233,7 @@
     </row>
     <row r="118" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="120" spans="1:179" x14ac:dyDescent="0.2">
@@ -26114,7 +26243,7 @@
     </row>
     <row r="121" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
@@ -26283,6 +26412,7 @@
       <c r="DB124" s="23">
         <v>2026</v>
       </c>
+      <c r="DC124" s="23"/>
     </row>
     <row r="125" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
@@ -26602,6 +26732,9 @@
       </c>
       <c r="DB125" s="24" t="s">
         <v>2</v>
+      </c>
+      <c r="DC125" s="24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -26926,7 +27059,9 @@
       <c r="DB127" s="32">
         <v>133.11486788395311</v>
       </c>
-      <c r="DC127" s="8"/>
+      <c r="DC127" s="32">
+        <v>139.5972850202061</v>
+      </c>
       <c r="DD127" s="8"/>
       <c r="DE127" s="8"/>
       <c r="DF127" s="8"/>
@@ -27319,7 +27454,9 @@
       <c r="DB128" s="32">
         <v>179.82769105344306</v>
       </c>
-      <c r="DC128" s="8"/>
+      <c r="DC128" s="32">
+        <v>198.96518710056446</v>
+      </c>
       <c r="DD128" s="8"/>
       <c r="DE128" s="8"/>
       <c r="DF128" s="8"/>
@@ -27712,7 +27849,9 @@
       <c r="DB129" s="32">
         <v>120.13131886305874</v>
       </c>
-      <c r="DC129" s="8"/>
+      <c r="DC129" s="32">
+        <v>131.92034314191818</v>
+      </c>
       <c r="DD129" s="8"/>
       <c r="DE129" s="8"/>
       <c r="DF129" s="8"/>
@@ -28105,7 +28244,9 @@
       <c r="DB130" s="32">
         <v>120.18253008179754</v>
       </c>
-      <c r="DC130" s="8"/>
+      <c r="DC130" s="32">
+        <v>130.65607510578528</v>
+      </c>
       <c r="DD130" s="8"/>
       <c r="DE130" s="8"/>
       <c r="DF130" s="8"/>
@@ -28498,7 +28639,9 @@
       <c r="DB131" s="32">
         <v>128.86312316991368</v>
       </c>
-      <c r="DC131" s="8"/>
+      <c r="DC131" s="32">
+        <v>129.57998189279871</v>
+      </c>
       <c r="DD131" s="8"/>
       <c r="DE131" s="8"/>
       <c r="DF131" s="8"/>
@@ -28891,7 +29034,9 @@
       <c r="DB132" s="32">
         <v>122.77660735459482</v>
       </c>
-      <c r="DC132" s="8"/>
+      <c r="DC132" s="32">
+        <v>124.76083295503024</v>
+      </c>
       <c r="DD132" s="8"/>
       <c r="DE132" s="8"/>
       <c r="DF132" s="8"/>
@@ -29284,7 +29429,9 @@
       <c r="DB133" s="32">
         <v>137.80396639177681</v>
       </c>
-      <c r="DC133" s="8"/>
+      <c r="DC133" s="32">
+        <v>146.62817973403767</v>
+      </c>
       <c r="DD133" s="8"/>
       <c r="DE133" s="8"/>
       <c r="DF133" s="8"/>
@@ -29677,7 +29824,9 @@
       <c r="DB134" s="32">
         <v>107.18399324950228</v>
       </c>
-      <c r="DC134" s="8"/>
+      <c r="DC134" s="32">
+        <v>104.57676040538495</v>
+      </c>
       <c r="DD134" s="8"/>
       <c r="DE134" s="8"/>
       <c r="DF134" s="8"/>
@@ -30070,7 +30219,9 @@
       <c r="DB135" s="32">
         <v>120.35498636349908</v>
       </c>
-      <c r="DC135" s="8"/>
+      <c r="DC135" s="32">
+        <v>120.31810970100733</v>
+      </c>
       <c r="DD135" s="8"/>
       <c r="DE135" s="8"/>
       <c r="DF135" s="8"/>
@@ -30463,7 +30614,9 @@
       <c r="DB136" s="32">
         <v>120.37896764805924</v>
       </c>
-      <c r="DC136" s="8"/>
+      <c r="DC136" s="32">
+        <v>123.81360627057323</v>
+      </c>
       <c r="DD136" s="8"/>
       <c r="DE136" s="8"/>
       <c r="DF136" s="8"/>
@@ -30856,7 +31009,9 @@
       <c r="DB137" s="32">
         <v>135.83333333333334</v>
       </c>
-      <c r="DC137" s="8"/>
+      <c r="DC137" s="32">
+        <v>134.69803681330998</v>
+      </c>
       <c r="DD137" s="8"/>
       <c r="DE137" s="8"/>
       <c r="DF137" s="8"/>
@@ -31249,7 +31404,9 @@
       <c r="DB138" s="32">
         <v>131.73625706296522</v>
       </c>
-      <c r="DC138" s="8"/>
+      <c r="DC138" s="32">
+        <v>134.92874587520117</v>
+      </c>
       <c r="DD138" s="8"/>
       <c r="DE138" s="8"/>
       <c r="DF138" s="8"/>
@@ -31429,7 +31586,7 @@
       <c r="CZ139" s="26"/>
       <c r="DA139" s="26"/>
       <c r="DB139" s="26"/>
-      <c r="DC139" s="8"/>
+      <c r="DC139" s="26"/>
       <c r="DD139" s="8"/>
       <c r="DE139" s="8"/>
       <c r="DF139" s="8"/>
@@ -31820,9 +31977,11 @@
         <v>125.75245526872317</v>
       </c>
       <c r="DB140" s="32">
-        <v>130.06285010024203</v>
-      </c>
-      <c r="DC140" s="8"/>
+        <v>130.06688920311512</v>
+      </c>
+      <c r="DC140" s="32">
+        <v>135.07714627918344</v>
+      </c>
       <c r="DD140" s="8"/>
       <c r="DE140" s="8"/>
       <c r="DF140" s="8"/>
@@ -32003,6 +32162,7 @@
       <c r="CZ141" s="27"/>
       <c r="DA141" s="27"/>
       <c r="DB141" s="27"/>
+      <c r="DC141" s="27"/>
     </row>
     <row r="142" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A142" s="12" t="s">
@@ -32021,7 +32181,7 @@
     </row>
     <row r="147" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="149" spans="1:179" x14ac:dyDescent="0.2">
@@ -32031,7 +32191,7 @@
     </row>
     <row r="150" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:179" x14ac:dyDescent="0.2">
@@ -32200,6 +32360,7 @@
       <c r="DB153" s="23">
         <v>2026</v>
       </c>
+      <c r="DC153" s="23"/>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
@@ -32519,6 +32680,9 @@
       </c>
       <c r="DB154" s="24" t="s">
         <v>2</v>
+      </c>
+      <c r="DC154" s="24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -32841,9 +33005,11 @@
         <v>37.35495101165894</v>
       </c>
       <c r="DB156" s="32">
-        <v>32.617855510780672</v>
-      </c>
-      <c r="DC156" s="8"/>
+        <v>32.653847468507472</v>
+      </c>
+      <c r="DC156" s="32">
+        <v>37.510123201983355</v>
+      </c>
       <c r="DD156" s="8"/>
       <c r="DE156" s="8"/>
       <c r="DF156" s="8"/>
@@ -33234,9 +33400,11 @@
         <v>1.9897456335966761</v>
       </c>
       <c r="DB157" s="32">
-        <v>1.8035476286195591</v>
-      </c>
-      <c r="DC157" s="8"/>
+        <v>1.8043555768871784</v>
+      </c>
+      <c r="DC157" s="32">
+        <v>1.6143908878409261</v>
+      </c>
       <c r="DD157" s="8"/>
       <c r="DE157" s="8"/>
       <c r="DF157" s="8"/>
@@ -33627,9 +33795,11 @@
         <v>1.5676254952267776</v>
       </c>
       <c r="DB158" s="32">
-        <v>1.3754731629479835</v>
-      </c>
-      <c r="DC158" s="8"/>
+        <v>1.3689903133212518</v>
+      </c>
+      <c r="DC158" s="32">
+        <v>1.0564912401759921</v>
+      </c>
       <c r="DD158" s="8"/>
       <c r="DE158" s="8"/>
       <c r="DF158" s="8"/>
@@ -34020,9 +34190,11 @@
         <v>10.450112164051506</v>
       </c>
       <c r="DB159" s="32">
-        <v>10.959719702513523</v>
-      </c>
-      <c r="DC159" s="8"/>
+        <v>10.945820245993893</v>
+      </c>
+      <c r="DC159" s="32">
+        <v>14.510308867216617</v>
+      </c>
       <c r="DD159" s="8"/>
       <c r="DE159" s="8"/>
       <c r="DF159" s="8"/>
@@ -34413,9 +34585,11 @@
         <v>2.4403664072674704</v>
       </c>
       <c r="DB160" s="32">
-        <v>2.3748278876814086</v>
-      </c>
-      <c r="DC160" s="8"/>
+        <v>2.3835167393984507</v>
+      </c>
+      <c r="DC160" s="32">
+        <v>2.3626123586021253</v>
+      </c>
       <c r="DD160" s="8"/>
       <c r="DE160" s="8"/>
       <c r="DF160" s="8"/>
@@ -34806,9 +34980,11 @@
         <v>4.4588421426957927</v>
       </c>
       <c r="DB161" s="32">
-        <v>4.5933686278660755</v>
-      </c>
-      <c r="DC161" s="8"/>
+        <v>4.6057671043890256</v>
+      </c>
+      <c r="DC161" s="32">
+        <v>4.1341507063178611</v>
+      </c>
       <c r="DD161" s="8"/>
       <c r="DE161" s="8"/>
       <c r="DF161" s="8"/>
@@ -35199,9 +35375,11 @@
         <v>8.2180309363383532</v>
       </c>
       <c r="DB162" s="32">
-        <v>10.920402074268493</v>
-      </c>
-      <c r="DC162" s="8"/>
+        <v>10.889739659520545</v>
+      </c>
+      <c r="DC162" s="32">
+        <v>9.5207362281610344</v>
+      </c>
       <c r="DD162" s="8"/>
       <c r="DE162" s="8"/>
       <c r="DF162" s="8"/>
@@ -35592,9 +35770,11 @@
         <v>2.4102637552467896</v>
       </c>
       <c r="DB163" s="32">
-        <v>2.7824009136202443</v>
-      </c>
-      <c r="DC163" s="8"/>
+        <v>2.7779899461416542</v>
+      </c>
+      <c r="DC163" s="32">
+        <v>2.9260634623734672</v>
+      </c>
       <c r="DD163" s="8"/>
       <c r="DE163" s="8"/>
       <c r="DF163" s="8"/>
@@ -35985,9 +36165,11 @@
         <v>1.9207835906935355</v>
       </c>
       <c r="DB164" s="32">
-        <v>1.917862352745934</v>
-      </c>
-      <c r="DC164" s="8"/>
+        <v>1.9190549662716081</v>
+      </c>
+      <c r="DC164" s="32">
+        <v>1.3008216186818018</v>
+      </c>
       <c r="DD164" s="8"/>
       <c r="DE164" s="8"/>
       <c r="DF164" s="8"/>
@@ -36378,9 +36560,11 @@
         <v>4.9640629602150677</v>
       </c>
       <c r="DB165" s="32">
-        <v>5.5261147905211487</v>
-      </c>
-      <c r="DC165" s="8"/>
+        <v>5.511442218211517</v>
+      </c>
+      <c r="DC165" s="32">
+        <v>5.2710666373929707</v>
+      </c>
       <c r="DD165" s="8"/>
       <c r="DE165" s="8"/>
       <c r="DF165" s="8"/>
@@ -36771,9 +36955,11 @@
         <v>9.1027974592063732</v>
       </c>
       <c r="DB166" s="32">
-        <v>10.845627002812328</v>
-      </c>
-      <c r="DC166" s="8"/>
+        <v>10.870848690316857</v>
+      </c>
+      <c r="DC166" s="32">
+        <v>6.0475701259431496</v>
+      </c>
       <c r="DD166" s="8"/>
       <c r="DE166" s="8"/>
       <c r="DF166" s="8"/>
@@ -37164,9 +37350,11 @@
         <v>15.122418443802719</v>
       </c>
       <c r="DB167" s="32">
-        <v>14.282800345622624</v>
-      </c>
-      <c r="DC167" s="8"/>
+        <v>14.268627071040557</v>
+      </c>
+      <c r="DC167" s="32">
+        <v>13.745664665310715</v>
+      </c>
       <c r="DD167" s="8"/>
       <c r="DE167" s="8"/>
       <c r="DF167" s="8"/>
@@ -37346,7 +37534,7 @@
       <c r="CZ168" s="26"/>
       <c r="DA168" s="26"/>
       <c r="DB168" s="26"/>
-      <c r="DC168" s="8"/>
+      <c r="DC168" s="26"/>
       <c r="DD168" s="8"/>
       <c r="DE168" s="8"/>
       <c r="DF168" s="8"/>
@@ -37739,7 +37927,9 @@
       <c r="DB169" s="32">
         <v>100</v>
       </c>
-      <c r="DC169" s="8"/>
+      <c r="DC169" s="32">
+        <v>100</v>
+      </c>
       <c r="DD169" s="8"/>
       <c r="DE169" s="8"/>
       <c r="DF169" s="8"/>
@@ -37920,6 +38110,7 @@
       <c r="CZ170" s="27"/>
       <c r="DA170" s="27"/>
       <c r="DB170" s="27"/>
+      <c r="DC170" s="27"/>
     </row>
     <row r="171" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A171" s="12" t="s">
@@ -38032,7 +38223,7 @@
       <c r="CZ172" s="26"/>
       <c r="DA172" s="26"/>
       <c r="DB172" s="26"/>
-      <c r="DC172" s="8"/>
+      <c r="DC172" s="26"/>
       <c r="DD172" s="8"/>
       <c r="DE172" s="8"/>
       <c r="DF172" s="8"/>
@@ -38212,7 +38403,7 @@
       <c r="CZ173" s="26"/>
       <c r="DA173" s="26"/>
       <c r="DB173" s="26"/>
-      <c r="DC173" s="8"/>
+      <c r="DC173" s="26"/>
       <c r="DD173" s="8"/>
       <c r="DE173" s="8"/>
       <c r="DF173" s="8"/>
@@ -38298,7 +38489,7 @@
     </row>
     <row r="176" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="178" spans="1:179" x14ac:dyDescent="0.2">
@@ -38308,7 +38499,7 @@
     </row>
     <row r="179" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="180" spans="1:179" x14ac:dyDescent="0.2">
@@ -38477,6 +38668,7 @@
       <c r="DB182" s="23">
         <v>2026</v>
       </c>
+      <c r="DC182" s="23"/>
     </row>
     <row r="183" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
@@ -38796,6 +38988,9 @@
       </c>
       <c r="DB183" s="24" t="s">
         <v>2</v>
+      </c>
+      <c r="DC183" s="24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -39118,9 +39313,11 @@
         <v>35.622626491414316</v>
       </c>
       <c r="DB185" s="32">
-        <v>31.870003098289786</v>
-      </c>
-      <c r="DC185" s="8"/>
+        <v>31.906160658510313</v>
+      </c>
+      <c r="DC185" s="32">
+        <v>36.295551148943247</v>
+      </c>
       <c r="DD185" s="8"/>
       <c r="DE185" s="8"/>
       <c r="DF185" s="8"/>
@@ -39511,9 +39708,11 @@
         <v>1.3928558482030335</v>
       </c>
       <c r="DB186" s="32">
-        <v>1.3044406203273744</v>
-      </c>
-      <c r="DC186" s="8"/>
+        <v>1.3050655075822601</v>
+      </c>
+      <c r="DC186" s="32">
+        <v>1.0960073834346216</v>
+      </c>
       <c r="DD186" s="8"/>
       <c r="DE186" s="8"/>
       <c r="DF186" s="8"/>
@@ -39904,9 +40103,11 @@
         <v>1.6739075855519421</v>
       </c>
       <c r="DB187" s="32">
-        <v>1.4891866792317539</v>
-      </c>
-      <c r="DC187" s="8"/>
+        <v>1.4822139063158819</v>
+      </c>
+      <c r="DC187" s="32">
+        <v>1.0817726697269516</v>
+      </c>
       <c r="DD187" s="8"/>
       <c r="DE187" s="8"/>
       <c r="DF187" s="8"/>
@@ -40297,9 +40498,11 @@
         <v>10.440580907306169</v>
       </c>
       <c r="DB188" s="32">
-        <v>11.860728675278406</v>
-      </c>
-      <c r="DC188" s="8"/>
+        <v>11.846054399120439</v>
+      </c>
+      <c r="DC188" s="32">
+        <v>15.001301025047894</v>
+      </c>
       <c r="DD188" s="8"/>
       <c r="DE188" s="8"/>
       <c r="DF188" s="8"/>
@@ -40690,9 +40893,11 @@
         <v>2.4991936999721429</v>
       </c>
       <c r="DB189" s="32">
-        <v>2.3969377427094405</v>
-      </c>
-      <c r="DC189" s="8"/>
+        <v>2.405782197660483</v>
+      </c>
+      <c r="DC189" s="32">
+        <v>2.462841331679809</v>
+      </c>
       <c r="DD189" s="8"/>
       <c r="DE189" s="8"/>
       <c r="DF189" s="8"/>
@@ -41083,9 +41288,11 @@
         <v>4.4857597563020342</v>
       </c>
       <c r="DB190" s="32">
-        <v>4.865964520227001</v>
-      </c>
-      <c r="DC190" s="8"/>
+        <v>4.8792503113542063</v>
+      </c>
+      <c r="DC190" s="32">
+        <v>4.4759983279269377</v>
+      </c>
       <c r="DD190" s="8"/>
       <c r="DE190" s="8"/>
       <c r="DF190" s="8"/>
@@ -41476,9 +41683,11 @@
         <v>8.1432744910178165</v>
       </c>
       <c r="DB191" s="32">
-        <v>10.306950193160123</v>
-      </c>
-      <c r="DC191" s="8"/>
+        <v>10.278329418464024</v>
+      </c>
+      <c r="DC191" s="32">
+        <v>8.7707143504714367</v>
+      </c>
       <c r="DD191" s="8"/>
       <c r="DE191" s="8"/>
       <c r="DF191" s="8"/>
@@ -41869,9 +42078,11 @@
         <v>3.0543196119418572</v>
       </c>
       <c r="DB192" s="32">
-        <v>3.3763156416888469</v>
-      </c>
-      <c r="DC192" s="8"/>
+        <v>3.3710678206500968</v>
+      </c>
+      <c r="DC192" s="32">
+        <v>3.7794659233758652</v>
+      </c>
       <c r="DD192" s="8"/>
       <c r="DE192" s="8"/>
       <c r="DF192" s="8"/>
@@ -42262,9 +42473,11 @@
         <v>2.0556348418543737</v>
       </c>
       <c r="DB193" s="32">
-        <v>2.0725576167215798</v>
-      </c>
-      <c r="DC193" s="8"/>
+        <v>2.073910830074563</v>
+      </c>
+      <c r="DC193" s="32">
+        <v>1.4603892340600397</v>
+      </c>
       <c r="DD193" s="8"/>
       <c r="DE193" s="8"/>
       <c r="DF193" s="8"/>
@@ -42655,9 +42868,11 @@
         <v>5.4668335274871662</v>
       </c>
       <c r="DB194" s="32">
-        <v>5.9706629295709055</v>
-      </c>
-      <c r="DC194" s="8"/>
+        <v>5.95499494929458</v>
+      </c>
+      <c r="DC194" s="32">
+        <v>5.7505847755577006</v>
+      </c>
       <c r="DD194" s="8"/>
       <c r="DE194" s="8"/>
       <c r="DF194" s="8"/>
@@ -43048,9 +43263,11 @@
         <v>8.7430583183304122</v>
       </c>
       <c r="DB195" s="32">
-        <v>10.384882152956447</v>
-      </c>
-      <c r="DC195" s="8"/>
+        <v>10.409355623170098</v>
+      </c>
+      <c r="DC195" s="32">
+        <v>6.0645910947302175</v>
+      </c>
       <c r="DD195" s="8"/>
       <c r="DE195" s="8"/>
       <c r="DF195" s="8"/>
@@ -43441,9 +43658,11 @@
         <v>16.421954920618724</v>
       </c>
       <c r="DB196" s="32">
-        <v>14.101370129838322</v>
-      </c>
-      <c r="DC196" s="8"/>
+        <v>14.08781437780306</v>
+      </c>
+      <c r="DC196" s="32">
+        <v>13.760782735045263</v>
+      </c>
       <c r="DD196" s="8"/>
       <c r="DE196" s="8"/>
       <c r="DF196" s="8"/>
@@ -43623,7 +43842,7 @@
       <c r="CZ197" s="26"/>
       <c r="DA197" s="26"/>
       <c r="DB197" s="26"/>
-      <c r="DC197" s="8"/>
+      <c r="DC197" s="26"/>
       <c r="DD197" s="8"/>
       <c r="DE197" s="8"/>
       <c r="DF197" s="8"/>
@@ -44016,7 +44235,9 @@
       <c r="DB198" s="32">
         <v>100</v>
       </c>
-      <c r="DC198" s="8"/>
+      <c r="DC198" s="32">
+        <v>100</v>
+      </c>
       <c r="DD198" s="8"/>
       <c r="DE198" s="8"/>
       <c r="DF198" s="8"/>
@@ -44197,6 +44418,7 @@
       <c r="CZ199" s="27"/>
       <c r="DA199" s="27"/>
       <c r="DB199" s="27"/>
+      <c r="DC199" s="27"/>
     </row>
     <row r="200" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A200" s="12" t="s">
@@ -44310,7 +44532,7 @@
       <c r="CZ201" s="36"/>
       <c r="DA201" s="36"/>
       <c r="DB201" s="36"/>
-      <c r="DC201" s="20"/>
+      <c r="DC201" s="36"/>
       <c r="DD201" s="20"/>
       <c r="DE201" s="20"/>
       <c r="DF201" s="20"/>
@@ -44385,25 +44607,30 @@
       <c r="FW201" s="20"/>
     </row>
     <row r="202" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX202" s="29"/>
-      <c r="CY202" s="29"/>
-      <c r="CZ202" s="29"/>
-      <c r="DA202" s="29"/>
+      <c r="CX202" s="28"/>
+      <c r="CZ202" s="28"/>
+      <c r="DA202" s="28"/>
       <c r="DB202" s="28"/>
     </row>
     <row r="203" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT203" s="28"/>
       <c r="CV203" s="28"/>
       <c r="CX203" s="28"/>
+      <c r="CY203" s="28"/>
       <c r="CZ203" s="28"/>
       <c r="DA203" s="28"/>
+      <c r="DB203" s="28"/>
+      <c r="DC203" s="28"/>
     </row>
     <row r="204" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT204" s="28"/>
       <c r="CV204" s="28"/>
       <c r="CX204" s="28"/>
+      <c r="CY204" s="28"/>
       <c r="CZ204" s="28"/>
       <c r="DA204" s="28"/>
+      <c r="DB204" s="28"/>
+      <c r="DC204" s="28"/>
     </row>
     <row r="205" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT205" s="28"/>
@@ -44413,24 +44640,18 @@
       <c r="CY205" s="28"/>
       <c r="CZ205" s="28"/>
       <c r="DA205" s="28"/>
+      <c r="DB205" s="28"/>
+      <c r="DC205" s="28"/>
     </row>
     <row r="206" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT206" s="28"/>
       <c r="CU206" s="28"/>
       <c r="CV206" s="28"/>
-      <c r="CX206" s="28"/>
-      <c r="CY206" s="28"/>
-      <c r="CZ206" s="28"/>
-      <c r="DA206" s="28"/>
     </row>
     <row r="207" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT207" s="28"/>
       <c r="CU207" s="28"/>
       <c r="CV207" s="28"/>
-      <c r="CX207" s="28"/>
-      <c r="CY207" s="28"/>
-      <c r="CZ207" s="28"/>
-      <c r="DA207" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
